--- a/packages/server/src/arpa_reporter/data/treasury/project4142BulkUpload.xlsx
+++ b/packages/server/src/arpa_reporter/data/treasury/project4142BulkUpload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JohnsonTa\Desktop\SLFRF Templates\SLFRF Q2 2026 Updates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mac\Home\Documents\Projects\arpa-reporter\packages\server\src\arpa_reporter\data\treasury\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407520C6-4757-46A0-B530-FC6CBDA46B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B4EEA9-1EA1-437B-AA4C-325083730D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="90" windowWidth="28800" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="1545" windowWidth="22747" windowHeight="12277" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -361,10 +361,10 @@
 "No"</t>
   </si>
   <si>
-    <t>Q2_2026_Obligations__c</t>
+    <t>Q3_2026_Obligations__c</t>
   </si>
   <si>
-    <t>Q2_2026_Expenditures__c</t>
+    <t>Q3_2026_Expenditures__c</t>
   </si>
 </sst>
 </file>
@@ -859,7 +859,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI1000"/>
-  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45.5" style="8" customWidth="1"/>
     <col min="2" max="2" width="41.875" style="8" customWidth="1"/>
@@ -878,7 +878,7 @@
     <col min="36" max="16384" width="12.5" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
@@ -917,7 +917,7 @@
       <c r="AH1" s="6"/>
       <c r="AI1" s="6"/>
     </row>
-    <row r="2" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
@@ -956,7 +956,7 @@
       <c r="AH2" s="6"/>
       <c r="AI2" s="6"/>
     </row>
-    <row r="3" spans="1:35" ht="225" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" ht="225" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="26" t="s">
         <v>37</v>
       </c>
@@ -995,7 +995,7 @@
       <c r="AH3" s="6"/>
       <c r="AI3" s="6"/>
     </row>
-    <row r="4" spans="1:35" ht="41.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" ht="41.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1084,7 +1084,7 @@
       <c r="AH4" s="6"/>
       <c r="AI4" s="6"/>
     </row>
-    <row r="5" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>13</v>
       </c>
@@ -1173,7 +1173,7 @@
       <c r="AH5" s="6"/>
       <c r="AI5" s="6"/>
     </row>
-    <row r="6" spans="1:35" ht="56.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="56.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -1262,7 +1262,7 @@
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
     </row>
-    <row r="7" spans="1:35" ht="228" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" ht="228" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
         <v>25</v>
       </c>
@@ -1351,7 +1351,7 @@
       <c r="AH7" s="14"/>
       <c r="AI7" s="14"/>
     </row>
-    <row r="8" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -1386,7 +1386,7 @@
       <c r="AH8" s="6"/>
       <c r="AI8" s="6"/>
     </row>
-    <row r="9" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -1421,7 +1421,7 @@
       <c r="AH9" s="6"/>
       <c r="AI9" s="6"/>
     </row>
-    <row r="10" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -1456,7 +1456,7 @@
       <c r="AH10" s="6"/>
       <c r="AI10" s="6"/>
     </row>
-    <row r="11" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -1491,7 +1491,7 @@
       <c r="AH11" s="6"/>
       <c r="AI11" s="6"/>
     </row>
-    <row r="12" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -1527,7 +1527,7 @@
       <c r="AH12" s="6"/>
       <c r="AI12" s="6"/>
     </row>
-    <row r="13" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -1563,7 +1563,7 @@
       <c r="AH13" s="6"/>
       <c r="AI13" s="6"/>
     </row>
-    <row r="14" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -1599,7 +1599,7 @@
       <c r="AH14" s="6"/>
       <c r="AI14" s="6"/>
     </row>
-    <row r="15" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -1635,7 +1635,7 @@
       <c r="AH15" s="6"/>
       <c r="AI15" s="6"/>
     </row>
-    <row r="16" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1671,7 +1671,7 @@
       <c r="AH16" s="6"/>
       <c r="AI16" s="6"/>
     </row>
-    <row r="17" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -1707,7 +1707,7 @@
       <c r="AH17" s="6"/>
       <c r="AI17" s="6"/>
     </row>
-    <row r="18" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -1743,7 +1743,7 @@
       <c r="AH18" s="6"/>
       <c r="AI18" s="6"/>
     </row>
-    <row r="19" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -1779,7 +1779,7 @@
       <c r="AH19" s="6"/>
       <c r="AI19" s="6"/>
     </row>
-    <row r="20" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -1815,7 +1815,7 @@
       <c r="AH20" s="6"/>
       <c r="AI20" s="6"/>
     </row>
-    <row r="21" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -1851,7 +1851,7 @@
       <c r="AH21" s="6"/>
       <c r="AI21" s="6"/>
     </row>
-    <row r="22" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -1887,7 +1887,7 @@
       <c r="AH22" s="6"/>
       <c r="AI22" s="6"/>
     </row>
-    <row r="23" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -1923,7 +1923,7 @@
       <c r="AH23" s="6"/>
       <c r="AI23" s="6"/>
     </row>
-    <row r="24" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -1959,7 +1959,7 @@
       <c r="AH24" s="6"/>
       <c r="AI24" s="6"/>
     </row>
-    <row r="25" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -1995,7 +1995,7 @@
       <c r="AH25" s="6"/>
       <c r="AI25" s="6"/>
     </row>
-    <row r="26" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -2031,7 +2031,7 @@
       <c r="AH26" s="6"/>
       <c r="AI26" s="6"/>
     </row>
-    <row r="27" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -2067,7 +2067,7 @@
       <c r="AH27" s="6"/>
       <c r="AI27" s="6"/>
     </row>
-    <row r="28" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -2104,7 +2104,7 @@
       <c r="AH28" s="6"/>
       <c r="AI28" s="6"/>
     </row>
-    <row r="29" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -2141,7 +2141,7 @@
       <c r="AH29" s="6"/>
       <c r="AI29" s="6"/>
     </row>
-    <row r="30" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2178,7 +2178,7 @@
       <c r="AH30" s="6"/>
       <c r="AI30" s="6"/>
     </row>
-    <row r="31" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2215,7 +2215,7 @@
       <c r="AH31" s="6"/>
       <c r="AI31" s="6"/>
     </row>
-    <row r="32" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -2252,7 +2252,7 @@
       <c r="AH32" s="6"/>
       <c r="AI32" s="6"/>
     </row>
-    <row r="33" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -2289,7 +2289,7 @@
       <c r="AH33" s="6"/>
       <c r="AI33" s="6"/>
     </row>
-    <row r="34" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -2326,7 +2326,7 @@
       <c r="AH34" s="6"/>
       <c r="AI34" s="6"/>
     </row>
-    <row r="35" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -2363,7 +2363,7 @@
       <c r="AH35" s="6"/>
       <c r="AI35" s="6"/>
     </row>
-    <row r="36" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -2400,7 +2400,7 @@
       <c r="AH36" s="6"/>
       <c r="AI36" s="6"/>
     </row>
-    <row r="37" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -2437,7 +2437,7 @@
       <c r="AH37" s="6"/>
       <c r="AI37" s="6"/>
     </row>
-    <row r="38" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -2474,7 +2474,7 @@
       <c r="AH38" s="6"/>
       <c r="AI38" s="6"/>
     </row>
-    <row r="39" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -2511,7 +2511,7 @@
       <c r="AH39" s="6"/>
       <c r="AI39" s="6"/>
     </row>
-    <row r="40" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -2548,7 +2548,7 @@
       <c r="AH40" s="6"/>
       <c r="AI40" s="6"/>
     </row>
-    <row r="41" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2585,7 +2585,7 @@
       <c r="AH41" s="6"/>
       <c r="AI41" s="6"/>
     </row>
-    <row r="42" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -2622,7 +2622,7 @@
       <c r="AH42" s="6"/>
       <c r="AI42" s="6"/>
     </row>
-    <row r="43" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -2659,7 +2659,7 @@
       <c r="AH43" s="6"/>
       <c r="AI43" s="6"/>
     </row>
-    <row r="44" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -2696,7 +2696,7 @@
       <c r="AH44" s="6"/>
       <c r="AI44" s="6"/>
     </row>
-    <row r="45" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -2733,7 +2733,7 @@
       <c r="AH45" s="6"/>
       <c r="AI45" s="6"/>
     </row>
-    <row r="46" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -2770,7 +2770,7 @@
       <c r="AH46" s="6"/>
       <c r="AI46" s="6"/>
     </row>
-    <row r="47" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -2807,7 +2807,7 @@
       <c r="AH47" s="6"/>
       <c r="AI47" s="6"/>
     </row>
-    <row r="48" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2844,7 +2844,7 @@
       <c r="AH48" s="6"/>
       <c r="AI48" s="6"/>
     </row>
-    <row r="49" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2881,7 +2881,7 @@
       <c r="AH49" s="6"/>
       <c r="AI49" s="6"/>
     </row>
-    <row r="50" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -2918,7 +2918,7 @@
       <c r="AH50" s="6"/>
       <c r="AI50" s="6"/>
     </row>
-    <row r="51" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -2955,7 +2955,7 @@
       <c r="AH51" s="6"/>
       <c r="AI51" s="6"/>
     </row>
-    <row r="52" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -2992,7 +2992,7 @@
       <c r="AH52" s="6"/>
       <c r="AI52" s="6"/>
     </row>
-    <row r="53" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -3029,7 +3029,7 @@
       <c r="AH53" s="6"/>
       <c r="AI53" s="6"/>
     </row>
-    <row r="54" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -3066,7 +3066,7 @@
       <c r="AH54" s="6"/>
       <c r="AI54" s="6"/>
     </row>
-    <row r="55" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -3103,7 +3103,7 @@
       <c r="AH55" s="6"/>
       <c r="AI55" s="6"/>
     </row>
-    <row r="56" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -3140,7 +3140,7 @@
       <c r="AH56" s="6"/>
       <c r="AI56" s="6"/>
     </row>
-    <row r="57" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -3177,7 +3177,7 @@
       <c r="AH57" s="6"/>
       <c r="AI57" s="6"/>
     </row>
-    <row r="58" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -3214,7 +3214,7 @@
       <c r="AH58" s="6"/>
       <c r="AI58" s="6"/>
     </row>
-    <row r="59" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -3251,7 +3251,7 @@
       <c r="AH59" s="6"/>
       <c r="AI59" s="6"/>
     </row>
-    <row r="60" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -3288,7 +3288,7 @@
       <c r="AH60" s="6"/>
       <c r="AI60" s="6"/>
     </row>
-    <row r="61" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -3325,7 +3325,7 @@
       <c r="AH61" s="6"/>
       <c r="AI61" s="6"/>
     </row>
-    <row r="62" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -3362,7 +3362,7 @@
       <c r="AH62" s="6"/>
       <c r="AI62" s="6"/>
     </row>
-    <row r="63" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -3399,7 +3399,7 @@
       <c r="AH63" s="6"/>
       <c r="AI63" s="6"/>
     </row>
-    <row r="64" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -3436,7 +3436,7 @@
       <c r="AH64" s="6"/>
       <c r="AI64" s="6"/>
     </row>
-    <row r="65" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -3473,7 +3473,7 @@
       <c r="AH65" s="6"/>
       <c r="AI65" s="6"/>
     </row>
-    <row r="66" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -3510,7 +3510,7 @@
       <c r="AH66" s="6"/>
       <c r="AI66" s="6"/>
     </row>
-    <row r="67" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -3547,7 +3547,7 @@
       <c r="AH67" s="6"/>
       <c r="AI67" s="6"/>
     </row>
-    <row r="68" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -3584,7 +3584,7 @@
       <c r="AH68" s="6"/>
       <c r="AI68" s="6"/>
     </row>
-    <row r="69" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -3621,7 +3621,7 @@
       <c r="AH69" s="6"/>
       <c r="AI69" s="6"/>
     </row>
-    <row r="70" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -3658,7 +3658,7 @@
       <c r="AH70" s="6"/>
       <c r="AI70" s="6"/>
     </row>
-    <row r="71" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -3695,7 +3695,7 @@
       <c r="AH71" s="6"/>
       <c r="AI71" s="6"/>
     </row>
-    <row r="72" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -3732,7 +3732,7 @@
       <c r="AH72" s="6"/>
       <c r="AI72" s="6"/>
     </row>
-    <row r="73" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -3769,7 +3769,7 @@
       <c r="AH73" s="6"/>
       <c r="AI73" s="6"/>
     </row>
-    <row r="74" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -3806,7 +3806,7 @@
       <c r="AH74" s="6"/>
       <c r="AI74" s="6"/>
     </row>
-    <row r="75" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -3843,7 +3843,7 @@
       <c r="AH75" s="6"/>
       <c r="AI75" s="6"/>
     </row>
-    <row r="76" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -3880,7 +3880,7 @@
       <c r="AH76" s="6"/>
       <c r="AI76" s="6"/>
     </row>
-    <row r="77" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -3917,7 +3917,7 @@
       <c r="AH77" s="6"/>
       <c r="AI77" s="6"/>
     </row>
-    <row r="78" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -3954,7 +3954,7 @@
       <c r="AH78" s="6"/>
       <c r="AI78" s="6"/>
     </row>
-    <row r="79" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -3991,7 +3991,7 @@
       <c r="AH79" s="6"/>
       <c r="AI79" s="6"/>
     </row>
-    <row r="80" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -4028,7 +4028,7 @@
       <c r="AH80" s="6"/>
       <c r="AI80" s="6"/>
     </row>
-    <row r="81" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -4065,7 +4065,7 @@
       <c r="AH81" s="6"/>
       <c r="AI81" s="6"/>
     </row>
-    <row r="82" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -4102,7 +4102,7 @@
       <c r="AH82" s="6"/>
       <c r="AI82" s="6"/>
     </row>
-    <row r="83" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -4139,7 +4139,7 @@
       <c r="AH83" s="6"/>
       <c r="AI83" s="6"/>
     </row>
-    <row r="84" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -4176,7 +4176,7 @@
       <c r="AH84" s="6"/>
       <c r="AI84" s="6"/>
     </row>
-    <row r="85" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -4213,7 +4213,7 @@
       <c r="AH85" s="6"/>
       <c r="AI85" s="6"/>
     </row>
-    <row r="86" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -4250,7 +4250,7 @@
       <c r="AH86" s="6"/>
       <c r="AI86" s="6"/>
     </row>
-    <row r="87" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -4287,7 +4287,7 @@
       <c r="AH87" s="6"/>
       <c r="AI87" s="6"/>
     </row>
-    <row r="88" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -4324,7 +4324,7 @@
       <c r="AH88" s="6"/>
       <c r="AI88" s="6"/>
     </row>
-    <row r="89" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -4361,7 +4361,7 @@
       <c r="AH89" s="6"/>
       <c r="AI89" s="6"/>
     </row>
-    <row r="90" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -4398,7 +4398,7 @@
       <c r="AH90" s="6"/>
       <c r="AI90" s="6"/>
     </row>
-    <row r="91" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -4435,7 +4435,7 @@
       <c r="AH91" s="6"/>
       <c r="AI91" s="6"/>
     </row>
-    <row r="92" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -4472,7 +4472,7 @@
       <c r="AH92" s="6"/>
       <c r="AI92" s="6"/>
     </row>
-    <row r="93" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -4509,7 +4509,7 @@
       <c r="AH93" s="6"/>
       <c r="AI93" s="6"/>
     </row>
-    <row r="94" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -4546,7 +4546,7 @@
       <c r="AH94" s="6"/>
       <c r="AI94" s="6"/>
     </row>
-    <row r="95" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -4583,7 +4583,7 @@
       <c r="AH95" s="6"/>
       <c r="AI95" s="6"/>
     </row>
-    <row r="96" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -4620,7 +4620,7 @@
       <c r="AH96" s="6"/>
       <c r="AI96" s="6"/>
     </row>
-    <row r="97" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -4657,7 +4657,7 @@
       <c r="AH97" s="6"/>
       <c r="AI97" s="6"/>
     </row>
-    <row r="98" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -4694,7 +4694,7 @@
       <c r="AH98" s="6"/>
       <c r="AI98" s="6"/>
     </row>
-    <row r="99" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -4731,7 +4731,7 @@
       <c r="AH99" s="6"/>
       <c r="AI99" s="6"/>
     </row>
-    <row r="100" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -4768,7 +4768,7 @@
       <c r="AH100" s="6"/>
       <c r="AI100" s="6"/>
     </row>
-    <row r="101" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -4805,7 +4805,7 @@
       <c r="AH101" s="6"/>
       <c r="AI101" s="6"/>
     </row>
-    <row r="102" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -4842,7 +4842,7 @@
       <c r="AH102" s="6"/>
       <c r="AI102" s="6"/>
     </row>
-    <row r="103" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -4879,7 +4879,7 @@
       <c r="AH103" s="6"/>
       <c r="AI103" s="6"/>
     </row>
-    <row r="104" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -4916,7 +4916,7 @@
       <c r="AH104" s="6"/>
       <c r="AI104" s="6"/>
     </row>
-    <row r="105" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -4953,7 +4953,7 @@
       <c r="AH105" s="6"/>
       <c r="AI105" s="6"/>
     </row>
-    <row r="106" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -4990,7 +4990,7 @@
       <c r="AH106" s="6"/>
       <c r="AI106" s="6"/>
     </row>
-    <row r="107" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -5027,7 +5027,7 @@
       <c r="AH107" s="6"/>
       <c r="AI107" s="6"/>
     </row>
-    <row r="108" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -5064,7 +5064,7 @@
       <c r="AH108" s="6"/>
       <c r="AI108" s="6"/>
     </row>
-    <row r="109" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -5101,7 +5101,7 @@
       <c r="AH109" s="6"/>
       <c r="AI109" s="6"/>
     </row>
-    <row r="110" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -5138,7 +5138,7 @@
       <c r="AH110" s="6"/>
       <c r="AI110" s="6"/>
     </row>
-    <row r="111" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="6"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -5175,7 +5175,7 @@
       <c r="AH111" s="6"/>
       <c r="AI111" s="6"/>
     </row>
-    <row r="112" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="6"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -5212,7 +5212,7 @@
       <c r="AH112" s="6"/>
       <c r="AI112" s="6"/>
     </row>
-    <row r="113" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -5249,7 +5249,7 @@
       <c r="AH113" s="6"/>
       <c r="AI113" s="6"/>
     </row>
-    <row r="114" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="6"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -5286,7 +5286,7 @@
       <c r="AH114" s="6"/>
       <c r="AI114" s="6"/>
     </row>
-    <row r="115" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -5323,7 +5323,7 @@
       <c r="AH115" s="6"/>
       <c r="AI115" s="6"/>
     </row>
-    <row r="116" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="6"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
@@ -5360,7 +5360,7 @@
       <c r="AH116" s="6"/>
       <c r="AI116" s="6"/>
     </row>
-    <row r="117" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="6"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
@@ -5397,7 +5397,7 @@
       <c r="AH117" s="6"/>
       <c r="AI117" s="6"/>
     </row>
-    <row r="118" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -5434,7 +5434,7 @@
       <c r="AH118" s="6"/>
       <c r="AI118" s="6"/>
     </row>
-    <row r="119" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="6"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -5471,7 +5471,7 @@
       <c r="AH119" s="6"/>
       <c r="AI119" s="6"/>
     </row>
-    <row r="120" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="6"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
@@ -5508,7 +5508,7 @@
       <c r="AH120" s="6"/>
       <c r="AI120" s="6"/>
     </row>
-    <row r="121" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="6"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -5545,7 +5545,7 @@
       <c r="AH121" s="6"/>
       <c r="AI121" s="6"/>
     </row>
-    <row r="122" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -5582,7 +5582,7 @@
       <c r="AH122" s="6"/>
       <c r="AI122" s="6"/>
     </row>
-    <row r="123" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="6"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
@@ -5619,7 +5619,7 @@
       <c r="AH123" s="6"/>
       <c r="AI123" s="6"/>
     </row>
-    <row r="124" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="6"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
@@ -5656,7 +5656,7 @@
       <c r="AH124" s="6"/>
       <c r="AI124" s="6"/>
     </row>
-    <row r="125" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="6"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -5693,7 +5693,7 @@
       <c r="AH125" s="6"/>
       <c r="AI125" s="6"/>
     </row>
-    <row r="126" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="6"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
@@ -5730,7 +5730,7 @@
       <c r="AH126" s="6"/>
       <c r="AI126" s="6"/>
     </row>
-    <row r="127" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="6"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
@@ -5767,7 +5767,7 @@
       <c r="AH127" s="6"/>
       <c r="AI127" s="6"/>
     </row>
-    <row r="128" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
@@ -5804,7 +5804,7 @@
       <c r="AH128" s="6"/>
       <c r="AI128" s="6"/>
     </row>
-    <row r="129" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="6"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
@@ -5841,7 +5841,7 @@
       <c r="AH129" s="6"/>
       <c r="AI129" s="6"/>
     </row>
-    <row r="130" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="6"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
@@ -5878,7 +5878,7 @@
       <c r="AH130" s="6"/>
       <c r="AI130" s="6"/>
     </row>
-    <row r="131" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
@@ -5915,7 +5915,7 @@
       <c r="AH131" s="6"/>
       <c r="AI131" s="6"/>
     </row>
-    <row r="132" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="6"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
@@ -5952,7 +5952,7 @@
       <c r="AH132" s="6"/>
       <c r="AI132" s="6"/>
     </row>
-    <row r="133" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
@@ -5989,7 +5989,7 @@
       <c r="AH133" s="6"/>
       <c r="AI133" s="6"/>
     </row>
-    <row r="134" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="6"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -6026,7 +6026,7 @@
       <c r="AH134" s="6"/>
       <c r="AI134" s="6"/>
     </row>
-    <row r="135" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="6"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
@@ -6063,7 +6063,7 @@
       <c r="AH135" s="6"/>
       <c r="AI135" s="6"/>
     </row>
-    <row r="136" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -6100,7 +6100,7 @@
       <c r="AH136" s="6"/>
       <c r="AI136" s="6"/>
     </row>
-    <row r="137" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="6"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -6137,7 +6137,7 @@
       <c r="AH137" s="6"/>
       <c r="AI137" s="6"/>
     </row>
-    <row r="138" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="6"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
@@ -6174,7 +6174,7 @@
       <c r="AH138" s="6"/>
       <c r="AI138" s="6"/>
     </row>
-    <row r="139" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="6"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -6211,7 +6211,7 @@
       <c r="AH139" s="6"/>
       <c r="AI139" s="6"/>
     </row>
-    <row r="140" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="6"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
@@ -6248,7 +6248,7 @@
       <c r="AH140" s="6"/>
       <c r="AI140" s="6"/>
     </row>
-    <row r="141" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="6"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
@@ -6285,7 +6285,7 @@
       <c r="AH141" s="6"/>
       <c r="AI141" s="6"/>
     </row>
-    <row r="142" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="6"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
@@ -6322,7 +6322,7 @@
       <c r="AH142" s="6"/>
       <c r="AI142" s="6"/>
     </row>
-    <row r="143" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="6"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
@@ -6359,7 +6359,7 @@
       <c r="AH143" s="6"/>
       <c r="AI143" s="6"/>
     </row>
-    <row r="144" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="6"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
@@ -6396,7 +6396,7 @@
       <c r="AH144" s="6"/>
       <c r="AI144" s="6"/>
     </row>
-    <row r="145" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -6433,7 +6433,7 @@
       <c r="AH145" s="6"/>
       <c r="AI145" s="6"/>
     </row>
-    <row r="146" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="6"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
@@ -6470,7 +6470,7 @@
       <c r="AH146" s="6"/>
       <c r="AI146" s="6"/>
     </row>
-    <row r="147" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="6"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -6507,7 +6507,7 @@
       <c r="AH147" s="6"/>
       <c r="AI147" s="6"/>
     </row>
-    <row r="148" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="6"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -6544,7 +6544,7 @@
       <c r="AH148" s="6"/>
       <c r="AI148" s="6"/>
     </row>
-    <row r="149" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="6"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
@@ -6581,7 +6581,7 @@
       <c r="AH149" s="6"/>
       <c r="AI149" s="6"/>
     </row>
-    <row r="150" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="6"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
@@ -6618,7 +6618,7 @@
       <c r="AH150" s="6"/>
       <c r="AI150" s="6"/>
     </row>
-    <row r="151" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="6"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
@@ -6655,7 +6655,7 @@
       <c r="AH151" s="6"/>
       <c r="AI151" s="6"/>
     </row>
-    <row r="152" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="6"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
@@ -6692,7 +6692,7 @@
       <c r="AH152" s="6"/>
       <c r="AI152" s="6"/>
     </row>
-    <row r="153" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="6"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
@@ -6729,7 +6729,7 @@
       <c r="AH153" s="6"/>
       <c r="AI153" s="6"/>
     </row>
-    <row r="154" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -6766,7 +6766,7 @@
       <c r="AH154" s="6"/>
       <c r="AI154" s="6"/>
     </row>
-    <row r="155" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="6"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -6803,7 +6803,7 @@
       <c r="AH155" s="6"/>
       <c r="AI155" s="6"/>
     </row>
-    <row r="156" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="6"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -6840,7 +6840,7 @@
       <c r="AH156" s="6"/>
       <c r="AI156" s="6"/>
     </row>
-    <row r="157" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="6"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
@@ -6877,7 +6877,7 @@
       <c r="AH157" s="6"/>
       <c r="AI157" s="6"/>
     </row>
-    <row r="158" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="6"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
@@ -6914,7 +6914,7 @@
       <c r="AH158" s="6"/>
       <c r="AI158" s="6"/>
     </row>
-    <row r="159" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="6"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
@@ -6951,7 +6951,7 @@
       <c r="AH159" s="6"/>
       <c r="AI159" s="6"/>
     </row>
-    <row r="160" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="6"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -6988,7 +6988,7 @@
       <c r="AH160" s="6"/>
       <c r="AI160" s="6"/>
     </row>
-    <row r="161" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="6"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
@@ -7025,7 +7025,7 @@
       <c r="AH161" s="6"/>
       <c r="AI161" s="6"/>
     </row>
-    <row r="162" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="6"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
@@ -7062,7 +7062,7 @@
       <c r="AH162" s="6"/>
       <c r="AI162" s="6"/>
     </row>
-    <row r="163" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="6"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
@@ -7099,7 +7099,7 @@
       <c r="AH163" s="6"/>
       <c r="AI163" s="6"/>
     </row>
-    <row r="164" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="6"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
@@ -7136,7 +7136,7 @@
       <c r="AH164" s="6"/>
       <c r="AI164" s="6"/>
     </row>
-    <row r="165" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="6"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
@@ -7173,7 +7173,7 @@
       <c r="AH165" s="6"/>
       <c r="AI165" s="6"/>
     </row>
-    <row r="166" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="6"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
@@ -7210,7 +7210,7 @@
       <c r="AH166" s="6"/>
       <c r="AI166" s="6"/>
     </row>
-    <row r="167" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="6"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
@@ -7247,7 +7247,7 @@
       <c r="AH167" s="6"/>
       <c r="AI167" s="6"/>
     </row>
-    <row r="168" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="6"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
@@ -7284,7 +7284,7 @@
       <c r="AH168" s="6"/>
       <c r="AI168" s="6"/>
     </row>
-    <row r="169" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="6"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
@@ -7321,7 +7321,7 @@
       <c r="AH169" s="6"/>
       <c r="AI169" s="6"/>
     </row>
-    <row r="170" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
@@ -7358,7 +7358,7 @@
       <c r="AH170" s="6"/>
       <c r="AI170" s="6"/>
     </row>
-    <row r="171" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
@@ -7395,7 +7395,7 @@
       <c r="AH171" s="6"/>
       <c r="AI171" s="6"/>
     </row>
-    <row r="172" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -7432,7 +7432,7 @@
       <c r="AH172" s="6"/>
       <c r="AI172" s="6"/>
     </row>
-    <row r="173" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
@@ -7469,7 +7469,7 @@
       <c r="AH173" s="6"/>
       <c r="AI173" s="6"/>
     </row>
-    <row r="174" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
@@ -7506,7 +7506,7 @@
       <c r="AH174" s="6"/>
       <c r="AI174" s="6"/>
     </row>
-    <row r="175" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
@@ -7543,7 +7543,7 @@
       <c r="AH175" s="6"/>
       <c r="AI175" s="6"/>
     </row>
-    <row r="176" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
@@ -7580,7 +7580,7 @@
       <c r="AH176" s="6"/>
       <c r="AI176" s="6"/>
     </row>
-    <row r="177" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
@@ -7617,7 +7617,7 @@
       <c r="AH177" s="6"/>
       <c r="AI177" s="6"/>
     </row>
-    <row r="178" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
@@ -7654,7 +7654,7 @@
       <c r="AH178" s="6"/>
       <c r="AI178" s="6"/>
     </row>
-    <row r="179" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
@@ -7691,7 +7691,7 @@
       <c r="AH179" s="6"/>
       <c r="AI179" s="6"/>
     </row>
-    <row r="180" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
@@ -7728,7 +7728,7 @@
       <c r="AH180" s="6"/>
       <c r="AI180" s="6"/>
     </row>
-    <row r="181" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -7765,7 +7765,7 @@
       <c r="AH181" s="6"/>
       <c r="AI181" s="6"/>
     </row>
-    <row r="182" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
@@ -7802,7 +7802,7 @@
       <c r="AH182" s="6"/>
       <c r="AI182" s="6"/>
     </row>
-    <row r="183" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
@@ -7839,7 +7839,7 @@
       <c r="AH183" s="6"/>
       <c r="AI183" s="6"/>
     </row>
-    <row r="184" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
@@ -7876,7 +7876,7 @@
       <c r="AH184" s="6"/>
       <c r="AI184" s="6"/>
     </row>
-    <row r="185" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
@@ -7913,7 +7913,7 @@
       <c r="AH185" s="6"/>
       <c r="AI185" s="6"/>
     </row>
-    <row r="186" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
@@ -7950,7 +7950,7 @@
       <c r="AH186" s="6"/>
       <c r="AI186" s="6"/>
     </row>
-    <row r="187" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -7987,7 +7987,7 @@
       <c r="AH187" s="6"/>
       <c r="AI187" s="6"/>
     </row>
-    <row r="188" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="6"/>
       <c r="B188" s="6"/>
       <c r="C188" s="6"/>
@@ -8024,7 +8024,7 @@
       <c r="AH188" s="6"/>
       <c r="AI188" s="6"/>
     </row>
-    <row r="189" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="6"/>
       <c r="B189" s="6"/>
       <c r="C189" s="6"/>
@@ -8061,7 +8061,7 @@
       <c r="AH189" s="6"/>
       <c r="AI189" s="6"/>
     </row>
-    <row r="190" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="6"/>
       <c r="B190" s="6"/>
       <c r="C190" s="6"/>
@@ -8098,7 +8098,7 @@
       <c r="AH190" s="6"/>
       <c r="AI190" s="6"/>
     </row>
-    <row r="191" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="6"/>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
@@ -8135,7 +8135,7 @@
       <c r="AH191" s="6"/>
       <c r="AI191" s="6"/>
     </row>
-    <row r="192" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="6"/>
       <c r="B192" s="6"/>
       <c r="C192" s="6"/>
@@ -8172,7 +8172,7 @@
       <c r="AH192" s="6"/>
       <c r="AI192" s="6"/>
     </row>
-    <row r="193" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="6"/>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
@@ -8209,7 +8209,7 @@
       <c r="AH193" s="6"/>
       <c r="AI193" s="6"/>
     </row>
-    <row r="194" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="6"/>
       <c r="B194" s="6"/>
       <c r="C194" s="6"/>
@@ -8246,7 +8246,7 @@
       <c r="AH194" s="6"/>
       <c r="AI194" s="6"/>
     </row>
-    <row r="195" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="6"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
@@ -8283,7 +8283,7 @@
       <c r="AH195" s="6"/>
       <c r="AI195" s="6"/>
     </row>
-    <row r="196" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="6"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
@@ -8320,7 +8320,7 @@
       <c r="AH196" s="6"/>
       <c r="AI196" s="6"/>
     </row>
-    <row r="197" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="6"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
@@ -8357,7 +8357,7 @@
       <c r="AH197" s="6"/>
       <c r="AI197" s="6"/>
     </row>
-    <row r="198" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="6"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
@@ -8394,7 +8394,7 @@
       <c r="AH198" s="6"/>
       <c r="AI198" s="6"/>
     </row>
-    <row r="199" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="6"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
@@ -8431,7 +8431,7 @@
       <c r="AH199" s="6"/>
       <c r="AI199" s="6"/>
     </row>
-    <row r="200" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="6"/>
       <c r="B200" s="6"/>
       <c r="C200" s="6"/>
@@ -8468,7 +8468,7 @@
       <c r="AH200" s="6"/>
       <c r="AI200" s="6"/>
     </row>
-    <row r="201" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="6"/>
       <c r="B201" s="6"/>
       <c r="C201" s="6"/>
@@ -8505,7 +8505,7 @@
       <c r="AH201" s="6"/>
       <c r="AI201" s="6"/>
     </row>
-    <row r="202" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="6"/>
       <c r="B202" s="6"/>
       <c r="C202" s="6"/>
@@ -8542,7 +8542,7 @@
       <c r="AH202" s="6"/>
       <c r="AI202" s="6"/>
     </row>
-    <row r="203" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="6"/>
       <c r="B203" s="6"/>
       <c r="C203" s="6"/>
@@ -8579,7 +8579,7 @@
       <c r="AH203" s="6"/>
       <c r="AI203" s="6"/>
     </row>
-    <row r="204" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="6"/>
       <c r="B204" s="6"/>
       <c r="C204" s="6"/>
@@ -8616,7 +8616,7 @@
       <c r="AH204" s="6"/>
       <c r="AI204" s="6"/>
     </row>
-    <row r="205" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="6"/>
       <c r="B205" s="6"/>
       <c r="C205" s="6"/>
@@ -8653,7 +8653,7 @@
       <c r="AH205" s="6"/>
       <c r="AI205" s="6"/>
     </row>
-    <row r="206" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="6"/>
       <c r="B206" s="6"/>
       <c r="C206" s="6"/>
@@ -8690,7 +8690,7 @@
       <c r="AH206" s="6"/>
       <c r="AI206" s="6"/>
     </row>
-    <row r="207" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="6"/>
       <c r="B207" s="6"/>
       <c r="C207" s="6"/>
@@ -8727,7 +8727,7 @@
       <c r="AH207" s="6"/>
       <c r="AI207" s="6"/>
     </row>
-    <row r="208" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="6"/>
       <c r="B208" s="6"/>
       <c r="C208" s="6"/>
@@ -8764,7 +8764,7 @@
       <c r="AH208" s="6"/>
       <c r="AI208" s="6"/>
     </row>
-    <row r="209" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="6"/>
       <c r="B209" s="6"/>
       <c r="C209" s="6"/>
@@ -8801,7 +8801,7 @@
       <c r="AH209" s="6"/>
       <c r="AI209" s="6"/>
     </row>
-    <row r="210" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="6"/>
       <c r="B210" s="6"/>
       <c r="C210" s="6"/>
@@ -8838,7 +8838,7 @@
       <c r="AH210" s="6"/>
       <c r="AI210" s="6"/>
     </row>
-    <row r="211" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="6"/>
       <c r="B211" s="6"/>
       <c r="C211" s="6"/>
@@ -8875,7 +8875,7 @@
       <c r="AH211" s="6"/>
       <c r="AI211" s="6"/>
     </row>
-    <row r="212" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="6"/>
       <c r="B212" s="6"/>
       <c r="C212" s="6"/>
@@ -8912,7 +8912,7 @@
       <c r="AH212" s="6"/>
       <c r="AI212" s="6"/>
     </row>
-    <row r="213" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="6"/>
       <c r="B213" s="6"/>
       <c r="C213" s="6"/>
@@ -8949,7 +8949,7 @@
       <c r="AH213" s="6"/>
       <c r="AI213" s="6"/>
     </row>
-    <row r="214" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="6"/>
       <c r="B214" s="6"/>
       <c r="C214" s="6"/>
@@ -8986,7 +8986,7 @@
       <c r="AH214" s="6"/>
       <c r="AI214" s="6"/>
     </row>
-    <row r="215" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="6"/>
       <c r="B215" s="6"/>
       <c r="C215" s="6"/>
@@ -9023,7 +9023,7 @@
       <c r="AH215" s="6"/>
       <c r="AI215" s="6"/>
     </row>
-    <row r="216" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="6"/>
       <c r="B216" s="6"/>
       <c r="C216" s="6"/>
@@ -9060,7 +9060,7 @@
       <c r="AH216" s="6"/>
       <c r="AI216" s="6"/>
     </row>
-    <row r="217" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="6"/>
       <c r="B217" s="6"/>
       <c r="C217" s="6"/>
@@ -9097,7 +9097,7 @@
       <c r="AH217" s="6"/>
       <c r="AI217" s="6"/>
     </row>
-    <row r="218" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="6"/>
       <c r="B218" s="6"/>
       <c r="C218" s="6"/>
@@ -9134,7 +9134,7 @@
       <c r="AH218" s="6"/>
       <c r="AI218" s="6"/>
     </row>
-    <row r="219" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="6"/>
       <c r="B219" s="6"/>
       <c r="C219" s="6"/>
@@ -9171,7 +9171,7 @@
       <c r="AH219" s="6"/>
       <c r="AI219" s="6"/>
     </row>
-    <row r="220" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="6"/>
       <c r="B220" s="6"/>
       <c r="C220" s="6"/>
@@ -9208,7 +9208,7 @@
       <c r="AH220" s="6"/>
       <c r="AI220" s="6"/>
     </row>
-    <row r="221" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="6"/>
       <c r="B221" s="6"/>
       <c r="C221" s="6"/>
@@ -9245,7 +9245,7 @@
       <c r="AH221" s="6"/>
       <c r="AI221" s="6"/>
     </row>
-    <row r="222" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="6"/>
       <c r="B222" s="6"/>
       <c r="C222" s="6"/>
@@ -9282,7 +9282,7 @@
       <c r="AH222" s="6"/>
       <c r="AI222" s="6"/>
     </row>
-    <row r="223" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="6"/>
       <c r="B223" s="6"/>
       <c r="C223" s="6"/>
@@ -9319,7 +9319,7 @@
       <c r="AH223" s="6"/>
       <c r="AI223" s="6"/>
     </row>
-    <row r="224" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="6"/>
       <c r="B224" s="6"/>
       <c r="C224" s="6"/>
@@ -9356,7 +9356,7 @@
       <c r="AH224" s="6"/>
       <c r="AI224" s="6"/>
     </row>
-    <row r="225" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="6"/>
       <c r="B225" s="6"/>
       <c r="C225" s="6"/>
@@ -9393,7 +9393,7 @@
       <c r="AH225" s="6"/>
       <c r="AI225" s="6"/>
     </row>
-    <row r="226" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="6"/>
       <c r="B226" s="6"/>
       <c r="C226" s="6"/>
@@ -9430,7 +9430,7 @@
       <c r="AH226" s="6"/>
       <c r="AI226" s="6"/>
     </row>
-    <row r="227" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="6"/>
       <c r="B227" s="6"/>
       <c r="C227" s="6"/>
@@ -9467,7 +9467,7 @@
       <c r="AH227" s="6"/>
       <c r="AI227" s="6"/>
     </row>
-    <row r="228" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="6"/>
       <c r="B228" s="6"/>
       <c r="C228" s="6"/>
@@ -9504,7 +9504,7 @@
       <c r="AH228" s="6"/>
       <c r="AI228" s="6"/>
     </row>
-    <row r="229" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="6"/>
       <c r="B229" s="6"/>
       <c r="C229" s="6"/>
@@ -9541,7 +9541,7 @@
       <c r="AH229" s="6"/>
       <c r="AI229" s="6"/>
     </row>
-    <row r="230" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="6"/>
       <c r="B230" s="6"/>
       <c r="C230" s="6"/>
@@ -9578,7 +9578,7 @@
       <c r="AH230" s="6"/>
       <c r="AI230" s="6"/>
     </row>
-    <row r="231" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="6"/>
       <c r="B231" s="6"/>
       <c r="C231" s="6"/>
@@ -9615,7 +9615,7 @@
       <c r="AH231" s="6"/>
       <c r="AI231" s="6"/>
     </row>
-    <row r="232" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="6"/>
       <c r="B232" s="6"/>
       <c r="C232" s="6"/>
@@ -9652,7 +9652,7 @@
       <c r="AH232" s="6"/>
       <c r="AI232" s="6"/>
     </row>
-    <row r="233" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="6"/>
       <c r="B233" s="6"/>
       <c r="C233" s="6"/>
@@ -9689,7 +9689,7 @@
       <c r="AH233" s="6"/>
       <c r="AI233" s="6"/>
     </row>
-    <row r="234" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="6"/>
       <c r="B234" s="6"/>
       <c r="C234" s="6"/>
@@ -9726,7 +9726,7 @@
       <c r="AH234" s="6"/>
       <c r="AI234" s="6"/>
     </row>
-    <row r="235" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="6"/>
       <c r="B235" s="6"/>
       <c r="C235" s="6"/>
@@ -9763,7 +9763,7 @@
       <c r="AH235" s="6"/>
       <c r="AI235" s="6"/>
     </row>
-    <row r="236" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="6"/>
       <c r="B236" s="6"/>
       <c r="C236" s="6"/>
@@ -9800,7 +9800,7 @@
       <c r="AH236" s="6"/>
       <c r="AI236" s="6"/>
     </row>
-    <row r="237" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="6"/>
       <c r="B237" s="6"/>
       <c r="C237" s="6"/>
@@ -9837,7 +9837,7 @@
       <c r="AH237" s="6"/>
       <c r="AI237" s="6"/>
     </row>
-    <row r="238" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="6"/>
       <c r="B238" s="6"/>
       <c r="C238" s="6"/>
@@ -9874,7 +9874,7 @@
       <c r="AH238" s="6"/>
       <c r="AI238" s="6"/>
     </row>
-    <row r="239" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="6"/>
       <c r="B239" s="6"/>
       <c r="C239" s="6"/>
@@ -9911,7 +9911,7 @@
       <c r="AH239" s="6"/>
       <c r="AI239" s="6"/>
     </row>
-    <row r="240" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="6"/>
       <c r="B240" s="6"/>
       <c r="C240" s="6"/>
@@ -9948,7 +9948,7 @@
       <c r="AH240" s="6"/>
       <c r="AI240" s="6"/>
     </row>
-    <row r="241" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="6"/>
       <c r="B241" s="6"/>
       <c r="C241" s="6"/>
@@ -9985,7 +9985,7 @@
       <c r="AH241" s="6"/>
       <c r="AI241" s="6"/>
     </row>
-    <row r="242" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="6"/>
       <c r="B242" s="6"/>
       <c r="C242" s="6"/>
@@ -10022,7 +10022,7 @@
       <c r="AH242" s="6"/>
       <c r="AI242" s="6"/>
     </row>
-    <row r="243" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="6"/>
       <c r="B243" s="6"/>
       <c r="C243" s="6"/>
@@ -10059,7 +10059,7 @@
       <c r="AH243" s="6"/>
       <c r="AI243" s="6"/>
     </row>
-    <row r="244" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="6"/>
       <c r="B244" s="6"/>
       <c r="C244" s="6"/>
@@ -10096,7 +10096,7 @@
       <c r="AH244" s="6"/>
       <c r="AI244" s="6"/>
     </row>
-    <row r="245" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="6"/>
       <c r="B245" s="6"/>
       <c r="C245" s="6"/>
@@ -10133,7 +10133,7 @@
       <c r="AH245" s="6"/>
       <c r="AI245" s="6"/>
     </row>
-    <row r="246" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="6"/>
       <c r="B246" s="6"/>
       <c r="C246" s="6"/>
@@ -10170,7 +10170,7 @@
       <c r="AH246" s="6"/>
       <c r="AI246" s="6"/>
     </row>
-    <row r="247" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="6"/>
       <c r="B247" s="6"/>
       <c r="C247" s="6"/>
@@ -10207,7 +10207,7 @@
       <c r="AH247" s="6"/>
       <c r="AI247" s="6"/>
     </row>
-    <row r="248" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="6"/>
       <c r="B248" s="6"/>
       <c r="C248" s="6"/>
@@ -10244,7 +10244,7 @@
       <c r="AH248" s="6"/>
       <c r="AI248" s="6"/>
     </row>
-    <row r="249" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="6"/>
       <c r="B249" s="6"/>
       <c r="C249" s="6"/>
@@ -10281,7 +10281,7 @@
       <c r="AH249" s="6"/>
       <c r="AI249" s="6"/>
     </row>
-    <row r="250" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="6"/>
       <c r="B250" s="6"/>
       <c r="C250" s="6"/>
@@ -10318,7 +10318,7 @@
       <c r="AH250" s="6"/>
       <c r="AI250" s="6"/>
     </row>
-    <row r="251" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="6"/>
       <c r="B251" s="6"/>
       <c r="C251" s="6"/>
@@ -10355,7 +10355,7 @@
       <c r="AH251" s="6"/>
       <c r="AI251" s="6"/>
     </row>
-    <row r="252" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="6"/>
       <c r="B252" s="6"/>
       <c r="C252" s="6"/>
@@ -10392,7 +10392,7 @@
       <c r="AH252" s="6"/>
       <c r="AI252" s="6"/>
     </row>
-    <row r="253" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="6"/>
       <c r="B253" s="6"/>
       <c r="C253" s="6"/>
@@ -10429,7 +10429,7 @@
       <c r="AH253" s="6"/>
       <c r="AI253" s="6"/>
     </row>
-    <row r="254" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="6"/>
       <c r="B254" s="6"/>
       <c r="C254" s="6"/>
@@ -10466,7 +10466,7 @@
       <c r="AH254" s="6"/>
       <c r="AI254" s="6"/>
     </row>
-    <row r="255" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="6"/>
       <c r="B255" s="6"/>
       <c r="C255" s="6"/>
@@ -10503,7 +10503,7 @@
       <c r="AH255" s="6"/>
       <c r="AI255" s="6"/>
     </row>
-    <row r="256" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="6"/>
       <c r="B256" s="6"/>
       <c r="C256" s="6"/>
@@ -10540,7 +10540,7 @@
       <c r="AH256" s="6"/>
       <c r="AI256" s="6"/>
     </row>
-    <row r="257" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="6"/>
       <c r="B257" s="6"/>
       <c r="C257" s="6"/>
@@ -10577,7 +10577,7 @@
       <c r="AH257" s="6"/>
       <c r="AI257" s="6"/>
     </row>
-    <row r="258" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="6"/>
       <c r="B258" s="6"/>
       <c r="C258" s="6"/>
@@ -10614,7 +10614,7 @@
       <c r="AH258" s="6"/>
       <c r="AI258" s="6"/>
     </row>
-    <row r="259" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="6"/>
       <c r="B259" s="6"/>
       <c r="C259" s="6"/>
@@ -10651,7 +10651,7 @@
       <c r="AH259" s="6"/>
       <c r="AI259" s="6"/>
     </row>
-    <row r="260" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="6"/>
       <c r="B260" s="6"/>
       <c r="C260" s="6"/>
@@ -10688,7 +10688,7 @@
       <c r="AH260" s="6"/>
       <c r="AI260" s="6"/>
     </row>
-    <row r="261" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="6"/>
       <c r="B261" s="6"/>
       <c r="C261" s="6"/>
@@ -10725,7 +10725,7 @@
       <c r="AH261" s="6"/>
       <c r="AI261" s="6"/>
     </row>
-    <row r="262" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="6"/>
       <c r="B262" s="6"/>
       <c r="C262" s="6"/>
@@ -10762,7 +10762,7 @@
       <c r="AH262" s="6"/>
       <c r="AI262" s="6"/>
     </row>
-    <row r="263" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="6"/>
       <c r="B263" s="6"/>
       <c r="C263" s="6"/>
@@ -10799,7 +10799,7 @@
       <c r="AH263" s="6"/>
       <c r="AI263" s="6"/>
     </row>
-    <row r="264" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="6"/>
       <c r="B264" s="6"/>
       <c r="C264" s="6"/>
@@ -10836,7 +10836,7 @@
       <c r="AH264" s="6"/>
       <c r="AI264" s="6"/>
     </row>
-    <row r="265" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="6"/>
       <c r="B265" s="6"/>
       <c r="C265" s="6"/>
@@ -10873,7 +10873,7 @@
       <c r="AH265" s="6"/>
       <c r="AI265" s="6"/>
     </row>
-    <row r="266" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="6"/>
       <c r="B266" s="6"/>
       <c r="C266" s="6"/>
@@ -10910,7 +10910,7 @@
       <c r="AH266" s="6"/>
       <c r="AI266" s="6"/>
     </row>
-    <row r="267" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="6"/>
       <c r="B267" s="6"/>
       <c r="C267" s="6"/>
@@ -10947,7 +10947,7 @@
       <c r="AH267" s="6"/>
       <c r="AI267" s="6"/>
     </row>
-    <row r="268" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="6"/>
       <c r="B268" s="6"/>
       <c r="C268" s="6"/>
@@ -10984,7 +10984,7 @@
       <c r="AH268" s="6"/>
       <c r="AI268" s="6"/>
     </row>
-    <row r="269" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="6"/>
       <c r="B269" s="6"/>
       <c r="C269" s="6"/>
@@ -11021,7 +11021,7 @@
       <c r="AH269" s="6"/>
       <c r="AI269" s="6"/>
     </row>
-    <row r="270" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="6"/>
       <c r="B270" s="6"/>
       <c r="C270" s="6"/>
@@ -11058,7 +11058,7 @@
       <c r="AH270" s="6"/>
       <c r="AI270" s="6"/>
     </row>
-    <row r="271" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="6"/>
       <c r="B271" s="6"/>
       <c r="C271" s="6"/>
@@ -11095,7 +11095,7 @@
       <c r="AH271" s="6"/>
       <c r="AI271" s="6"/>
     </row>
-    <row r="272" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="6"/>
       <c r="B272" s="6"/>
       <c r="C272" s="6"/>
@@ -11132,7 +11132,7 @@
       <c r="AH272" s="6"/>
       <c r="AI272" s="6"/>
     </row>
-    <row r="273" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="6"/>
       <c r="B273" s="6"/>
       <c r="C273" s="6"/>
@@ -11169,7 +11169,7 @@
       <c r="AH273" s="6"/>
       <c r="AI273" s="6"/>
     </row>
-    <row r="274" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="6"/>
       <c r="B274" s="6"/>
       <c r="C274" s="6"/>
@@ -11206,7 +11206,7 @@
       <c r="AH274" s="6"/>
       <c r="AI274" s="6"/>
     </row>
-    <row r="275" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="6"/>
       <c r="B275" s="6"/>
       <c r="C275" s="6"/>
@@ -11243,7 +11243,7 @@
       <c r="AH275" s="6"/>
       <c r="AI275" s="6"/>
     </row>
-    <row r="276" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="6"/>
       <c r="B276" s="6"/>
       <c r="C276" s="6"/>
@@ -11280,7 +11280,7 @@
       <c r="AH276" s="6"/>
       <c r="AI276" s="6"/>
     </row>
-    <row r="277" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="6"/>
       <c r="B277" s="6"/>
       <c r="C277" s="6"/>
@@ -11317,7 +11317,7 @@
       <c r="AH277" s="6"/>
       <c r="AI277" s="6"/>
     </row>
-    <row r="278" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="6"/>
       <c r="B278" s="6"/>
       <c r="C278" s="6"/>
@@ -11354,7 +11354,7 @@
       <c r="AH278" s="6"/>
       <c r="AI278" s="6"/>
     </row>
-    <row r="279" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="6"/>
       <c r="B279" s="6"/>
       <c r="C279" s="6"/>
@@ -11391,7 +11391,7 @@
       <c r="AH279" s="6"/>
       <c r="AI279" s="6"/>
     </row>
-    <row r="280" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="6"/>
       <c r="B280" s="6"/>
       <c r="C280" s="6"/>
@@ -11428,7 +11428,7 @@
       <c r="AH280" s="6"/>
       <c r="AI280" s="6"/>
     </row>
-    <row r="281" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="6"/>
       <c r="B281" s="6"/>
       <c r="C281" s="6"/>
@@ -11465,7 +11465,7 @@
       <c r="AH281" s="6"/>
       <c r="AI281" s="6"/>
     </row>
-    <row r="282" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="6"/>
       <c r="B282" s="6"/>
       <c r="C282" s="6"/>
@@ -11502,7 +11502,7 @@
       <c r="AH282" s="6"/>
       <c r="AI282" s="6"/>
     </row>
-    <row r="283" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="6"/>
       <c r="B283" s="6"/>
       <c r="C283" s="6"/>
@@ -11539,7 +11539,7 @@
       <c r="AH283" s="6"/>
       <c r="AI283" s="6"/>
     </row>
-    <row r="284" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="6"/>
       <c r="B284" s="6"/>
       <c r="C284" s="6"/>
@@ -11576,7 +11576,7 @@
       <c r="AH284" s="6"/>
       <c r="AI284" s="6"/>
     </row>
-    <row r="285" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="6"/>
       <c r="B285" s="6"/>
       <c r="C285" s="6"/>
@@ -11613,7 +11613,7 @@
       <c r="AH285" s="6"/>
       <c r="AI285" s="6"/>
     </row>
-    <row r="286" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="6"/>
       <c r="B286" s="6"/>
       <c r="C286" s="6"/>
@@ -11650,7 +11650,7 @@
       <c r="AH286" s="6"/>
       <c r="AI286" s="6"/>
     </row>
-    <row r="287" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="6"/>
       <c r="B287" s="6"/>
       <c r="C287" s="6"/>
@@ -11687,7 +11687,7 @@
       <c r="AH287" s="6"/>
       <c r="AI287" s="6"/>
     </row>
-    <row r="288" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="6"/>
       <c r="B288" s="6"/>
       <c r="C288" s="6"/>
@@ -11724,7 +11724,7 @@
       <c r="AH288" s="6"/>
       <c r="AI288" s="6"/>
     </row>
-    <row r="289" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="6"/>
       <c r="B289" s="6"/>
       <c r="C289" s="6"/>
@@ -11761,7 +11761,7 @@
       <c r="AH289" s="6"/>
       <c r="AI289" s="6"/>
     </row>
-    <row r="290" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="6"/>
       <c r="B290" s="6"/>
       <c r="C290" s="6"/>
@@ -11798,7 +11798,7 @@
       <c r="AH290" s="6"/>
       <c r="AI290" s="6"/>
     </row>
-    <row r="291" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="6"/>
       <c r="B291" s="6"/>
       <c r="C291" s="6"/>
@@ -11835,7 +11835,7 @@
       <c r="AH291" s="6"/>
       <c r="AI291" s="6"/>
     </row>
-    <row r="292" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="6"/>
       <c r="B292" s="6"/>
       <c r="C292" s="6"/>
@@ -11872,7 +11872,7 @@
       <c r="AH292" s="6"/>
       <c r="AI292" s="6"/>
     </row>
-    <row r="293" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="6"/>
       <c r="B293" s="6"/>
       <c r="C293" s="6"/>
@@ -11909,7 +11909,7 @@
       <c r="AH293" s="6"/>
       <c r="AI293" s="6"/>
     </row>
-    <row r="294" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="6"/>
       <c r="B294" s="6"/>
       <c r="C294" s="6"/>
@@ -11946,7 +11946,7 @@
       <c r="AH294" s="6"/>
       <c r="AI294" s="6"/>
     </row>
-    <row r="295" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="6"/>
       <c r="B295" s="6"/>
       <c r="C295" s="6"/>
@@ -11983,7 +11983,7 @@
       <c r="AH295" s="6"/>
       <c r="AI295" s="6"/>
     </row>
-    <row r="296" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="6"/>
       <c r="B296" s="6"/>
       <c r="C296" s="6"/>
@@ -12020,7 +12020,7 @@
       <c r="AH296" s="6"/>
       <c r="AI296" s="6"/>
     </row>
-    <row r="297" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="6"/>
       <c r="B297" s="6"/>
       <c r="C297" s="6"/>
@@ -12057,7 +12057,7 @@
       <c r="AH297" s="6"/>
       <c r="AI297" s="6"/>
     </row>
-    <row r="298" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="6"/>
       <c r="B298" s="6"/>
       <c r="C298" s="6"/>
@@ -12094,7 +12094,7 @@
       <c r="AH298" s="6"/>
       <c r="AI298" s="6"/>
     </row>
-    <row r="299" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="6"/>
       <c r="B299" s="6"/>
       <c r="C299" s="6"/>
@@ -12131,7 +12131,7 @@
       <c r="AH299" s="6"/>
       <c r="AI299" s="6"/>
     </row>
-    <row r="300" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="6"/>
       <c r="B300" s="6"/>
       <c r="C300" s="6"/>
@@ -12168,7 +12168,7 @@
       <c r="AH300" s="6"/>
       <c r="AI300" s="6"/>
     </row>
-    <row r="301" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="6"/>
       <c r="B301" s="6"/>
       <c r="C301" s="6"/>
@@ -12205,7 +12205,7 @@
       <c r="AH301" s="6"/>
       <c r="AI301" s="6"/>
     </row>
-    <row r="302" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="6"/>
       <c r="B302" s="6"/>
       <c r="C302" s="6"/>
@@ -12242,7 +12242,7 @@
       <c r="AH302" s="6"/>
       <c r="AI302" s="6"/>
     </row>
-    <row r="303" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="6"/>
       <c r="B303" s="6"/>
       <c r="C303" s="6"/>
@@ -12279,7 +12279,7 @@
       <c r="AH303" s="6"/>
       <c r="AI303" s="6"/>
     </row>
-    <row r="304" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="6"/>
       <c r="B304" s="6"/>
       <c r="C304" s="6"/>
@@ -12316,7 +12316,7 @@
       <c r="AH304" s="6"/>
       <c r="AI304" s="6"/>
     </row>
-    <row r="305" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="6"/>
       <c r="B305" s="6"/>
       <c r="C305" s="6"/>
@@ -12353,7 +12353,7 @@
       <c r="AH305" s="6"/>
       <c r="AI305" s="6"/>
     </row>
-    <row r="306" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="6"/>
       <c r="B306" s="6"/>
       <c r="C306" s="6"/>
@@ -12390,7 +12390,7 @@
       <c r="AH306" s="6"/>
       <c r="AI306" s="6"/>
     </row>
-    <row r="307" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="6"/>
       <c r="B307" s="6"/>
       <c r="C307" s="6"/>
@@ -12427,7 +12427,7 @@
       <c r="AH307" s="6"/>
       <c r="AI307" s="6"/>
     </row>
-    <row r="308" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="6"/>
       <c r="B308" s="6"/>
       <c r="C308" s="6"/>
@@ -12464,7 +12464,7 @@
       <c r="AH308" s="6"/>
       <c r="AI308" s="6"/>
     </row>
-    <row r="309" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="6"/>
       <c r="B309" s="6"/>
       <c r="C309" s="6"/>
@@ -12501,7 +12501,7 @@
       <c r="AH309" s="6"/>
       <c r="AI309" s="6"/>
     </row>
-    <row r="310" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="6"/>
       <c r="B310" s="6"/>
       <c r="C310" s="6"/>
@@ -12538,7 +12538,7 @@
       <c r="AH310" s="6"/>
       <c r="AI310" s="6"/>
     </row>
-    <row r="311" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="6"/>
       <c r="B311" s="6"/>
       <c r="C311" s="6"/>
@@ -12575,7 +12575,7 @@
       <c r="AH311" s="6"/>
       <c r="AI311" s="6"/>
     </row>
-    <row r="312" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="6"/>
       <c r="B312" s="6"/>
       <c r="C312" s="6"/>
@@ -12612,7 +12612,7 @@
       <c r="AH312" s="6"/>
       <c r="AI312" s="6"/>
     </row>
-    <row r="313" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="6"/>
       <c r="B313" s="6"/>
       <c r="C313" s="6"/>
@@ -12649,7 +12649,7 @@
       <c r="AH313" s="6"/>
       <c r="AI313" s="6"/>
     </row>
-    <row r="314" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="6"/>
       <c r="B314" s="6"/>
       <c r="C314" s="6"/>
@@ -12686,7 +12686,7 @@
       <c r="AH314" s="6"/>
       <c r="AI314" s="6"/>
     </row>
-    <row r="315" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="6"/>
       <c r="B315" s="6"/>
       <c r="C315" s="6"/>
@@ -12723,7 +12723,7 @@
       <c r="AH315" s="6"/>
       <c r="AI315" s="6"/>
     </row>
-    <row r="316" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="6"/>
       <c r="B316" s="6"/>
       <c r="C316" s="6"/>
@@ -12760,7 +12760,7 @@
       <c r="AH316" s="6"/>
       <c r="AI316" s="6"/>
     </row>
-    <row r="317" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="6"/>
       <c r="B317" s="6"/>
       <c r="C317" s="6"/>
@@ -12797,7 +12797,7 @@
       <c r="AH317" s="6"/>
       <c r="AI317" s="6"/>
     </row>
-    <row r="318" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="6"/>
       <c r="B318" s="6"/>
       <c r="C318" s="6"/>
@@ -12834,7 +12834,7 @@
       <c r="AH318" s="6"/>
       <c r="AI318" s="6"/>
     </row>
-    <row r="319" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="6"/>
       <c r="B319" s="6"/>
       <c r="C319" s="6"/>
@@ -12871,7 +12871,7 @@
       <c r="AH319" s="6"/>
       <c r="AI319" s="6"/>
     </row>
-    <row r="320" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="6"/>
       <c r="B320" s="6"/>
       <c r="C320" s="6"/>
@@ -12908,7 +12908,7 @@
       <c r="AH320" s="6"/>
       <c r="AI320" s="6"/>
     </row>
-    <row r="321" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="6"/>
       <c r="B321" s="6"/>
       <c r="C321" s="6"/>
@@ -12945,7 +12945,7 @@
       <c r="AH321" s="6"/>
       <c r="AI321" s="6"/>
     </row>
-    <row r="322" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="6"/>
       <c r="B322" s="6"/>
       <c r="C322" s="6"/>
@@ -12982,7 +12982,7 @@
       <c r="AH322" s="6"/>
       <c r="AI322" s="6"/>
     </row>
-    <row r="323" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="6"/>
       <c r="B323" s="6"/>
       <c r="C323" s="6"/>
@@ -13019,7 +13019,7 @@
       <c r="AH323" s="6"/>
       <c r="AI323" s="6"/>
     </row>
-    <row r="324" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="6"/>
       <c r="B324" s="6"/>
       <c r="C324" s="6"/>
@@ -13056,7 +13056,7 @@
       <c r="AH324" s="6"/>
       <c r="AI324" s="6"/>
     </row>
-    <row r="325" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="6"/>
       <c r="B325" s="6"/>
       <c r="C325" s="6"/>
@@ -13093,7 +13093,7 @@
       <c r="AH325" s="6"/>
       <c r="AI325" s="6"/>
     </row>
-    <row r="326" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="6"/>
       <c r="B326" s="6"/>
       <c r="C326" s="6"/>
@@ -13130,7 +13130,7 @@
       <c r="AH326" s="6"/>
       <c r="AI326" s="6"/>
     </row>
-    <row r="327" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="6"/>
       <c r="B327" s="6"/>
       <c r="C327" s="6"/>
@@ -13167,7 +13167,7 @@
       <c r="AH327" s="6"/>
       <c r="AI327" s="6"/>
     </row>
-    <row r="328" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="6"/>
       <c r="B328" s="6"/>
       <c r="C328" s="6"/>
@@ -13204,7 +13204,7 @@
       <c r="AH328" s="6"/>
       <c r="AI328" s="6"/>
     </row>
-    <row r="329" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="6"/>
       <c r="B329" s="6"/>
       <c r="C329" s="6"/>
@@ -13241,7 +13241,7 @@
       <c r="AH329" s="6"/>
       <c r="AI329" s="6"/>
     </row>
-    <row r="330" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="6"/>
       <c r="B330" s="6"/>
       <c r="C330" s="6"/>
@@ -13278,7 +13278,7 @@
       <c r="AH330" s="6"/>
       <c r="AI330" s="6"/>
     </row>
-    <row r="331" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="6"/>
       <c r="B331" s="6"/>
       <c r="C331" s="6"/>
@@ -13315,7 +13315,7 @@
       <c r="AH331" s="6"/>
       <c r="AI331" s="6"/>
     </row>
-    <row r="332" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="6"/>
       <c r="B332" s="6"/>
       <c r="C332" s="6"/>
@@ -13352,7 +13352,7 @@
       <c r="AH332" s="6"/>
       <c r="AI332" s="6"/>
     </row>
-    <row r="333" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="6"/>
       <c r="B333" s="6"/>
       <c r="C333" s="6"/>
@@ -13389,7 +13389,7 @@
       <c r="AH333" s="6"/>
       <c r="AI333" s="6"/>
     </row>
-    <row r="334" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="6"/>
       <c r="B334" s="6"/>
       <c r="C334" s="6"/>
@@ -13426,7 +13426,7 @@
       <c r="AH334" s="6"/>
       <c r="AI334" s="6"/>
     </row>
-    <row r="335" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="6"/>
       <c r="B335" s="6"/>
       <c r="C335" s="6"/>
@@ -13463,7 +13463,7 @@
       <c r="AH335" s="6"/>
       <c r="AI335" s="6"/>
     </row>
-    <row r="336" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="6"/>
       <c r="B336" s="6"/>
       <c r="C336" s="6"/>
@@ -13500,7 +13500,7 @@
       <c r="AH336" s="6"/>
       <c r="AI336" s="6"/>
     </row>
-    <row r="337" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="6"/>
       <c r="B337" s="6"/>
       <c r="C337" s="6"/>
@@ -13537,7 +13537,7 @@
       <c r="AH337" s="6"/>
       <c r="AI337" s="6"/>
     </row>
-    <row r="338" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="6"/>
       <c r="B338" s="6"/>
       <c r="C338" s="6"/>
@@ -13574,7 +13574,7 @@
       <c r="AH338" s="6"/>
       <c r="AI338" s="6"/>
     </row>
-    <row r="339" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="6"/>
       <c r="B339" s="6"/>
       <c r="C339" s="6"/>
@@ -13611,7 +13611,7 @@
       <c r="AH339" s="6"/>
       <c r="AI339" s="6"/>
     </row>
-    <row r="340" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="6"/>
       <c r="B340" s="6"/>
       <c r="C340" s="6"/>
@@ -13648,7 +13648,7 @@
       <c r="AH340" s="6"/>
       <c r="AI340" s="6"/>
     </row>
-    <row r="341" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="6"/>
       <c r="B341" s="6"/>
       <c r="C341" s="6"/>
@@ -13685,7 +13685,7 @@
       <c r="AH341" s="6"/>
       <c r="AI341" s="6"/>
     </row>
-    <row r="342" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="6"/>
       <c r="B342" s="6"/>
       <c r="C342" s="6"/>
@@ -13722,7 +13722,7 @@
       <c r="AH342" s="6"/>
       <c r="AI342" s="6"/>
     </row>
-    <row r="343" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="6"/>
       <c r="B343" s="6"/>
       <c r="C343" s="6"/>
@@ -13759,7 +13759,7 @@
       <c r="AH343" s="6"/>
       <c r="AI343" s="6"/>
     </row>
-    <row r="344" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="6"/>
       <c r="B344" s="6"/>
       <c r="C344" s="6"/>
@@ -13796,7 +13796,7 @@
       <c r="AH344" s="6"/>
       <c r="AI344" s="6"/>
     </row>
-    <row r="345" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="6"/>
       <c r="B345" s="6"/>
       <c r="C345" s="6"/>
@@ -13833,7 +13833,7 @@
       <c r="AH345" s="6"/>
       <c r="AI345" s="6"/>
     </row>
-    <row r="346" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="6"/>
       <c r="B346" s="6"/>
       <c r="C346" s="6"/>
@@ -13870,7 +13870,7 @@
       <c r="AH346" s="6"/>
       <c r="AI346" s="6"/>
     </row>
-    <row r="347" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="6"/>
       <c r="B347" s="6"/>
       <c r="C347" s="6"/>
@@ -13907,7 +13907,7 @@
       <c r="AH347" s="6"/>
       <c r="AI347" s="6"/>
     </row>
-    <row r="348" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="6"/>
       <c r="B348" s="6"/>
       <c r="C348" s="6"/>
@@ -13944,7 +13944,7 @@
       <c r="AH348" s="6"/>
       <c r="AI348" s="6"/>
     </row>
-    <row r="349" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="6"/>
       <c r="B349" s="6"/>
       <c r="C349" s="6"/>
@@ -13981,7 +13981,7 @@
       <c r="AH349" s="6"/>
       <c r="AI349" s="6"/>
     </row>
-    <row r="350" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="6"/>
       <c r="B350" s="6"/>
       <c r="C350" s="6"/>
@@ -14018,7 +14018,7 @@
       <c r="AH350" s="6"/>
       <c r="AI350" s="6"/>
     </row>
-    <row r="351" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="6"/>
       <c r="B351" s="6"/>
       <c r="C351" s="6"/>
@@ -14055,7 +14055,7 @@
       <c r="AH351" s="6"/>
       <c r="AI351" s="6"/>
     </row>
-    <row r="352" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="6"/>
       <c r="B352" s="6"/>
       <c r="C352" s="6"/>
@@ -14092,7 +14092,7 @@
       <c r="AH352" s="6"/>
       <c r="AI352" s="6"/>
     </row>
-    <row r="353" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="6"/>
       <c r="B353" s="6"/>
       <c r="C353" s="6"/>
@@ -14129,7 +14129,7 @@
       <c r="AH353" s="6"/>
       <c r="AI353" s="6"/>
     </row>
-    <row r="354" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="6"/>
       <c r="B354" s="6"/>
       <c r="C354" s="6"/>
@@ -14166,7 +14166,7 @@
       <c r="AH354" s="6"/>
       <c r="AI354" s="6"/>
     </row>
-    <row r="355" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="6"/>
       <c r="B355" s="6"/>
       <c r="C355" s="6"/>
@@ -14203,7 +14203,7 @@
       <c r="AH355" s="6"/>
       <c r="AI355" s="6"/>
     </row>
-    <row r="356" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="6"/>
       <c r="B356" s="6"/>
       <c r="C356" s="6"/>
@@ -14240,7 +14240,7 @@
       <c r="AH356" s="6"/>
       <c r="AI356" s="6"/>
     </row>
-    <row r="357" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="6"/>
       <c r="B357" s="6"/>
       <c r="C357" s="6"/>
@@ -14277,7 +14277,7 @@
       <c r="AH357" s="6"/>
       <c r="AI357" s="6"/>
     </row>
-    <row r="358" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="6"/>
       <c r="B358" s="6"/>
       <c r="C358" s="6"/>
@@ -14314,7 +14314,7 @@
       <c r="AH358" s="6"/>
       <c r="AI358" s="6"/>
     </row>
-    <row r="359" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="6"/>
       <c r="B359" s="6"/>
       <c r="C359" s="6"/>
@@ -14351,7 +14351,7 @@
       <c r="AH359" s="6"/>
       <c r="AI359" s="6"/>
     </row>
-    <row r="360" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="6"/>
       <c r="B360" s="6"/>
       <c r="C360" s="6"/>
@@ -14388,7 +14388,7 @@
       <c r="AH360" s="6"/>
       <c r="AI360" s="6"/>
     </row>
-    <row r="361" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="6"/>
       <c r="B361" s="6"/>
       <c r="C361" s="6"/>
@@ -14425,7 +14425,7 @@
       <c r="AH361" s="6"/>
       <c r="AI361" s="6"/>
     </row>
-    <row r="362" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="6"/>
       <c r="B362" s="6"/>
       <c r="C362" s="6"/>
@@ -14462,7 +14462,7 @@
       <c r="AH362" s="6"/>
       <c r="AI362" s="6"/>
     </row>
-    <row r="363" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="6"/>
       <c r="B363" s="6"/>
       <c r="C363" s="6"/>
@@ -14499,7 +14499,7 @@
       <c r="AH363" s="6"/>
       <c r="AI363" s="6"/>
     </row>
-    <row r="364" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="6"/>
       <c r="B364" s="6"/>
       <c r="C364" s="6"/>
@@ -14536,7 +14536,7 @@
       <c r="AH364" s="6"/>
       <c r="AI364" s="6"/>
     </row>
-    <row r="365" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="6"/>
       <c r="B365" s="6"/>
       <c r="C365" s="6"/>
@@ -14573,7 +14573,7 @@
       <c r="AH365" s="6"/>
       <c r="AI365" s="6"/>
     </row>
-    <row r="366" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="6"/>
       <c r="B366" s="6"/>
       <c r="C366" s="6"/>
@@ -14610,7 +14610,7 @@
       <c r="AH366" s="6"/>
       <c r="AI366" s="6"/>
     </row>
-    <row r="367" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="6"/>
       <c r="B367" s="6"/>
       <c r="C367" s="6"/>
@@ -14647,7 +14647,7 @@
       <c r="AH367" s="6"/>
       <c r="AI367" s="6"/>
     </row>
-    <row r="368" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="6"/>
       <c r="B368" s="6"/>
       <c r="C368" s="6"/>
@@ -14684,7 +14684,7 @@
       <c r="AH368" s="6"/>
       <c r="AI368" s="6"/>
     </row>
-    <row r="369" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="6"/>
       <c r="B369" s="6"/>
       <c r="C369" s="6"/>
@@ -14721,7 +14721,7 @@
       <c r="AH369" s="6"/>
       <c r="AI369" s="6"/>
     </row>
-    <row r="370" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="6"/>
       <c r="B370" s="6"/>
       <c r="C370" s="6"/>
@@ -14758,7 +14758,7 @@
       <c r="AH370" s="6"/>
       <c r="AI370" s="6"/>
     </row>
-    <row r="371" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="6"/>
       <c r="B371" s="6"/>
       <c r="C371" s="6"/>
@@ -14795,7 +14795,7 @@
       <c r="AH371" s="6"/>
       <c r="AI371" s="6"/>
     </row>
-    <row r="372" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="6"/>
       <c r="B372" s="6"/>
       <c r="C372" s="6"/>
@@ -14832,7 +14832,7 @@
       <c r="AH372" s="6"/>
       <c r="AI372" s="6"/>
     </row>
-    <row r="373" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="6"/>
       <c r="B373" s="6"/>
       <c r="C373" s="6"/>
@@ -14869,7 +14869,7 @@
       <c r="AH373" s="6"/>
       <c r="AI373" s="6"/>
     </row>
-    <row r="374" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="6"/>
       <c r="B374" s="6"/>
       <c r="C374" s="6"/>
@@ -14906,7 +14906,7 @@
       <c r="AH374" s="6"/>
       <c r="AI374" s="6"/>
     </row>
-    <row r="375" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="6"/>
       <c r="B375" s="6"/>
       <c r="C375" s="6"/>
@@ -14943,7 +14943,7 @@
       <c r="AH375" s="6"/>
       <c r="AI375" s="6"/>
     </row>
-    <row r="376" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="6"/>
       <c r="B376" s="6"/>
       <c r="C376" s="6"/>
@@ -14980,7 +14980,7 @@
       <c r="AH376" s="6"/>
       <c r="AI376" s="6"/>
     </row>
-    <row r="377" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="6"/>
       <c r="B377" s="6"/>
       <c r="C377" s="6"/>
@@ -15017,7 +15017,7 @@
       <c r="AH377" s="6"/>
       <c r="AI377" s="6"/>
     </row>
-    <row r="378" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="6"/>
       <c r="B378" s="6"/>
       <c r="C378" s="6"/>
@@ -15054,7 +15054,7 @@
       <c r="AH378" s="6"/>
       <c r="AI378" s="6"/>
     </row>
-    <row r="379" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="6"/>
       <c r="B379" s="6"/>
       <c r="C379" s="6"/>
@@ -15091,7 +15091,7 @@
       <c r="AH379" s="6"/>
       <c r="AI379" s="6"/>
     </row>
-    <row r="380" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="6"/>
       <c r="B380" s="6"/>
       <c r="C380" s="6"/>
@@ -15128,7 +15128,7 @@
       <c r="AH380" s="6"/>
       <c r="AI380" s="6"/>
     </row>
-    <row r="381" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="6"/>
       <c r="B381" s="6"/>
       <c r="C381" s="6"/>
@@ -15165,7 +15165,7 @@
       <c r="AH381" s="6"/>
       <c r="AI381" s="6"/>
     </row>
-    <row r="382" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="6"/>
       <c r="B382" s="6"/>
       <c r="C382" s="6"/>
@@ -15202,7 +15202,7 @@
       <c r="AH382" s="6"/>
       <c r="AI382" s="6"/>
     </row>
-    <row r="383" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="6"/>
       <c r="B383" s="6"/>
       <c r="C383" s="6"/>
@@ -15239,7 +15239,7 @@
       <c r="AH383" s="6"/>
       <c r="AI383" s="6"/>
     </row>
-    <row r="384" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="6"/>
       <c r="B384" s="6"/>
       <c r="C384" s="6"/>
@@ -15276,7 +15276,7 @@
       <c r="AH384" s="6"/>
       <c r="AI384" s="6"/>
     </row>
-    <row r="385" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="6"/>
       <c r="B385" s="6"/>
       <c r="C385" s="6"/>
@@ -15313,7 +15313,7 @@
       <c r="AH385" s="6"/>
       <c r="AI385" s="6"/>
     </row>
-    <row r="386" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="6"/>
       <c r="B386" s="6"/>
       <c r="C386" s="6"/>
@@ -15350,7 +15350,7 @@
       <c r="AH386" s="6"/>
       <c r="AI386" s="6"/>
     </row>
-    <row r="387" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="6"/>
       <c r="B387" s="6"/>
       <c r="C387" s="6"/>
@@ -15387,7 +15387,7 @@
       <c r="AH387" s="6"/>
       <c r="AI387" s="6"/>
     </row>
-    <row r="388" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="6"/>
       <c r="B388" s="6"/>
       <c r="C388" s="6"/>
@@ -15424,7 +15424,7 @@
       <c r="AH388" s="6"/>
       <c r="AI388" s="6"/>
     </row>
-    <row r="389" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="6"/>
       <c r="B389" s="6"/>
       <c r="C389" s="6"/>
@@ -15461,7 +15461,7 @@
       <c r="AH389" s="6"/>
       <c r="AI389" s="6"/>
     </row>
-    <row r="390" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="6"/>
       <c r="B390" s="6"/>
       <c r="C390" s="6"/>
@@ -15498,7 +15498,7 @@
       <c r="AH390" s="6"/>
       <c r="AI390" s="6"/>
     </row>
-    <row r="391" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="6"/>
       <c r="B391" s="6"/>
       <c r="C391" s="6"/>
@@ -15535,7 +15535,7 @@
       <c r="AH391" s="6"/>
       <c r="AI391" s="6"/>
     </row>
-    <row r="392" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="6"/>
       <c r="B392" s="6"/>
       <c r="C392" s="6"/>
@@ -15572,7 +15572,7 @@
       <c r="AH392" s="6"/>
       <c r="AI392" s="6"/>
     </row>
-    <row r="393" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="6"/>
       <c r="B393" s="6"/>
       <c r="C393" s="6"/>
@@ -15609,7 +15609,7 @@
       <c r="AH393" s="6"/>
       <c r="AI393" s="6"/>
     </row>
-    <row r="394" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="6"/>
       <c r="B394" s="6"/>
       <c r="C394" s="6"/>
@@ -15646,7 +15646,7 @@
       <c r="AH394" s="6"/>
       <c r="AI394" s="6"/>
     </row>
-    <row r="395" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="6"/>
       <c r="B395" s="6"/>
       <c r="C395" s="6"/>
@@ -15683,7 +15683,7 @@
       <c r="AH395" s="6"/>
       <c r="AI395" s="6"/>
     </row>
-    <row r="396" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="6"/>
       <c r="B396" s="6"/>
       <c r="C396" s="6"/>
@@ -15720,7 +15720,7 @@
       <c r="AH396" s="6"/>
       <c r="AI396" s="6"/>
     </row>
-    <row r="397" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="6"/>
       <c r="B397" s="6"/>
       <c r="C397" s="6"/>
@@ -15757,7 +15757,7 @@
       <c r="AH397" s="6"/>
       <c r="AI397" s="6"/>
     </row>
-    <row r="398" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="6"/>
       <c r="B398" s="6"/>
       <c r="C398" s="6"/>
@@ -15794,7 +15794,7 @@
       <c r="AH398" s="6"/>
       <c r="AI398" s="6"/>
     </row>
-    <row r="399" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="6"/>
       <c r="B399" s="6"/>
       <c r="C399" s="6"/>
@@ -15831,7 +15831,7 @@
       <c r="AH399" s="6"/>
       <c r="AI399" s="6"/>
     </row>
-    <row r="400" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="6"/>
       <c r="B400" s="6"/>
       <c r="C400" s="6"/>
@@ -15868,7 +15868,7 @@
       <c r="AH400" s="6"/>
       <c r="AI400" s="6"/>
     </row>
-    <row r="401" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="6"/>
       <c r="B401" s="6"/>
       <c r="C401" s="6"/>
@@ -15905,7 +15905,7 @@
       <c r="AH401" s="6"/>
       <c r="AI401" s="6"/>
     </row>
-    <row r="402" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="6"/>
       <c r="B402" s="6"/>
       <c r="C402" s="6"/>
@@ -15942,7 +15942,7 @@
       <c r="AH402" s="6"/>
       <c r="AI402" s="6"/>
     </row>
-    <row r="403" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="6"/>
       <c r="B403" s="6"/>
       <c r="C403" s="6"/>
@@ -15979,7 +15979,7 @@
       <c r="AH403" s="6"/>
       <c r="AI403" s="6"/>
     </row>
-    <row r="404" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="6"/>
       <c r="B404" s="6"/>
       <c r="C404" s="6"/>
@@ -16016,7 +16016,7 @@
       <c r="AH404" s="6"/>
       <c r="AI404" s="6"/>
     </row>
-    <row r="405" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="6"/>
       <c r="B405" s="6"/>
       <c r="C405" s="6"/>
@@ -16053,7 +16053,7 @@
       <c r="AH405" s="6"/>
       <c r="AI405" s="6"/>
     </row>
-    <row r="406" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="6"/>
       <c r="B406" s="6"/>
       <c r="C406" s="6"/>
@@ -16090,7 +16090,7 @@
       <c r="AH406" s="6"/>
       <c r="AI406" s="6"/>
     </row>
-    <row r="407" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="6"/>
       <c r="B407" s="6"/>
       <c r="C407" s="6"/>
@@ -16127,7 +16127,7 @@
       <c r="AH407" s="6"/>
       <c r="AI407" s="6"/>
     </row>
-    <row r="408" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="6"/>
       <c r="B408" s="6"/>
       <c r="C408" s="6"/>
@@ -16164,7 +16164,7 @@
       <c r="AH408" s="6"/>
       <c r="AI408" s="6"/>
     </row>
-    <row r="409" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="6"/>
       <c r="B409" s="6"/>
       <c r="C409" s="6"/>
@@ -16201,7 +16201,7 @@
       <c r="AH409" s="6"/>
       <c r="AI409" s="6"/>
     </row>
-    <row r="410" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="6"/>
       <c r="B410" s="6"/>
       <c r="C410" s="6"/>
@@ -16238,7 +16238,7 @@
       <c r="AH410" s="6"/>
       <c r="AI410" s="6"/>
     </row>
-    <row r="411" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="6"/>
       <c r="B411" s="6"/>
       <c r="C411" s="6"/>
@@ -16275,7 +16275,7 @@
       <c r="AH411" s="6"/>
       <c r="AI411" s="6"/>
     </row>
-    <row r="412" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="6"/>
       <c r="B412" s="6"/>
       <c r="C412" s="6"/>
@@ -16312,7 +16312,7 @@
       <c r="AH412" s="6"/>
       <c r="AI412" s="6"/>
     </row>
-    <row r="413" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="6"/>
       <c r="B413" s="6"/>
       <c r="C413" s="6"/>
@@ -16349,7 +16349,7 @@
       <c r="AH413" s="6"/>
       <c r="AI413" s="6"/>
     </row>
-    <row r="414" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="6"/>
       <c r="B414" s="6"/>
       <c r="C414" s="6"/>
@@ -16386,7 +16386,7 @@
       <c r="AH414" s="6"/>
       <c r="AI414" s="6"/>
     </row>
-    <row r="415" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="6"/>
       <c r="B415" s="6"/>
       <c r="C415" s="6"/>
@@ -16423,7 +16423,7 @@
       <c r="AH415" s="6"/>
       <c r="AI415" s="6"/>
     </row>
-    <row r="416" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="6"/>
       <c r="B416" s="6"/>
       <c r="C416" s="6"/>
@@ -16460,7 +16460,7 @@
       <c r="AH416" s="6"/>
       <c r="AI416" s="6"/>
     </row>
-    <row r="417" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="6"/>
       <c r="B417" s="6"/>
       <c r="C417" s="6"/>
@@ -16497,7 +16497,7 @@
       <c r="AH417" s="6"/>
       <c r="AI417" s="6"/>
     </row>
-    <row r="418" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="6"/>
       <c r="B418" s="6"/>
       <c r="C418" s="6"/>
@@ -16534,7 +16534,7 @@
       <c r="AH418" s="6"/>
       <c r="AI418" s="6"/>
     </row>
-    <row r="419" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="6"/>
       <c r="B419" s="6"/>
       <c r="C419" s="6"/>
@@ -16571,7 +16571,7 @@
       <c r="AH419" s="6"/>
       <c r="AI419" s="6"/>
     </row>
-    <row r="420" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="6"/>
       <c r="B420" s="6"/>
       <c r="C420" s="6"/>
@@ -16608,7 +16608,7 @@
       <c r="AH420" s="6"/>
       <c r="AI420" s="6"/>
     </row>
-    <row r="421" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="6"/>
       <c r="B421" s="6"/>
       <c r="C421" s="6"/>
@@ -16645,7 +16645,7 @@
       <c r="AH421" s="6"/>
       <c r="AI421" s="6"/>
     </row>
-    <row r="422" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="6"/>
       <c r="B422" s="6"/>
       <c r="C422" s="6"/>
@@ -16682,7 +16682,7 @@
       <c r="AH422" s="6"/>
       <c r="AI422" s="6"/>
     </row>
-    <row r="423" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="6"/>
       <c r="B423" s="6"/>
       <c r="C423" s="6"/>
@@ -16719,7 +16719,7 @@
       <c r="AH423" s="6"/>
       <c r="AI423" s="6"/>
     </row>
-    <row r="424" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="6"/>
       <c r="B424" s="6"/>
       <c r="C424" s="6"/>
@@ -16756,7 +16756,7 @@
       <c r="AH424" s="6"/>
       <c r="AI424" s="6"/>
     </row>
-    <row r="425" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="6"/>
       <c r="B425" s="6"/>
       <c r="C425" s="6"/>
@@ -16793,7 +16793,7 @@
       <c r="AH425" s="6"/>
       <c r="AI425" s="6"/>
     </row>
-    <row r="426" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="6"/>
       <c r="B426" s="6"/>
       <c r="C426" s="6"/>
@@ -16830,7 +16830,7 @@
       <c r="AH426" s="6"/>
       <c r="AI426" s="6"/>
     </row>
-    <row r="427" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="6"/>
       <c r="B427" s="6"/>
       <c r="C427" s="6"/>
@@ -16867,7 +16867,7 @@
       <c r="AH427" s="6"/>
       <c r="AI427" s="6"/>
     </row>
-    <row r="428" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="6"/>
       <c r="B428" s="6"/>
       <c r="C428" s="6"/>
@@ -16904,7 +16904,7 @@
       <c r="AH428" s="6"/>
       <c r="AI428" s="6"/>
     </row>
-    <row r="429" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="6"/>
       <c r="B429" s="6"/>
       <c r="C429" s="6"/>
@@ -16941,7 +16941,7 @@
       <c r="AH429" s="6"/>
       <c r="AI429" s="6"/>
     </row>
-    <row r="430" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="6"/>
       <c r="B430" s="6"/>
       <c r="C430" s="6"/>
@@ -16978,7 +16978,7 @@
       <c r="AH430" s="6"/>
       <c r="AI430" s="6"/>
     </row>
-    <row r="431" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="6"/>
       <c r="B431" s="6"/>
       <c r="C431" s="6"/>
@@ -17015,7 +17015,7 @@
       <c r="AH431" s="6"/>
       <c r="AI431" s="6"/>
     </row>
-    <row r="432" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="6"/>
       <c r="B432" s="6"/>
       <c r="C432" s="6"/>
@@ -17052,7 +17052,7 @@
       <c r="AH432" s="6"/>
       <c r="AI432" s="6"/>
     </row>
-    <row r="433" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="6"/>
       <c r="B433" s="6"/>
       <c r="C433" s="6"/>
@@ -17089,7 +17089,7 @@
       <c r="AH433" s="6"/>
       <c r="AI433" s="6"/>
     </row>
-    <row r="434" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="6"/>
       <c r="B434" s="6"/>
       <c r="C434" s="6"/>
@@ -17126,7 +17126,7 @@
       <c r="AH434" s="6"/>
       <c r="AI434" s="6"/>
     </row>
-    <row r="435" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="6"/>
       <c r="B435" s="6"/>
       <c r="C435" s="6"/>
@@ -17163,7 +17163,7 @@
       <c r="AH435" s="6"/>
       <c r="AI435" s="6"/>
     </row>
-    <row r="436" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="6"/>
       <c r="B436" s="6"/>
       <c r="C436" s="6"/>
@@ -17200,7 +17200,7 @@
       <c r="AH436" s="6"/>
       <c r="AI436" s="6"/>
     </row>
-    <row r="437" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="6"/>
       <c r="B437" s="6"/>
       <c r="C437" s="6"/>
@@ -17237,7 +17237,7 @@
       <c r="AH437" s="6"/>
       <c r="AI437" s="6"/>
     </row>
-    <row r="438" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="6"/>
       <c r="B438" s="6"/>
       <c r="C438" s="6"/>
@@ -17274,7 +17274,7 @@
       <c r="AH438" s="6"/>
       <c r="AI438" s="6"/>
     </row>
-    <row r="439" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="6"/>
       <c r="B439" s="6"/>
       <c r="C439" s="6"/>
@@ -17311,7 +17311,7 @@
       <c r="AH439" s="6"/>
       <c r="AI439" s="6"/>
     </row>
-    <row r="440" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="6"/>
       <c r="B440" s="6"/>
       <c r="C440" s="6"/>
@@ -17348,7 +17348,7 @@
       <c r="AH440" s="6"/>
       <c r="AI440" s="6"/>
     </row>
-    <row r="441" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="6"/>
       <c r="B441" s="6"/>
       <c r="C441" s="6"/>
@@ -17385,7 +17385,7 @@
       <c r="AH441" s="6"/>
       <c r="AI441" s="6"/>
     </row>
-    <row r="442" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="6"/>
       <c r="B442" s="6"/>
       <c r="C442" s="6"/>
@@ -17422,7 +17422,7 @@
       <c r="AH442" s="6"/>
       <c r="AI442" s="6"/>
     </row>
-    <row r="443" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="6"/>
       <c r="B443" s="6"/>
       <c r="C443" s="6"/>
@@ -17459,7 +17459,7 @@
       <c r="AH443" s="6"/>
       <c r="AI443" s="6"/>
     </row>
-    <row r="444" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="6"/>
       <c r="B444" s="6"/>
       <c r="C444" s="6"/>
@@ -17496,7 +17496,7 @@
       <c r="AH444" s="6"/>
       <c r="AI444" s="6"/>
     </row>
-    <row r="445" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="6"/>
       <c r="B445" s="6"/>
       <c r="C445" s="6"/>
@@ -17533,7 +17533,7 @@
       <c r="AH445" s="6"/>
       <c r="AI445" s="6"/>
     </row>
-    <row r="446" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="6"/>
       <c r="B446" s="6"/>
       <c r="C446" s="6"/>
@@ -17570,7 +17570,7 @@
       <c r="AH446" s="6"/>
       <c r="AI446" s="6"/>
     </row>
-    <row r="447" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="6"/>
       <c r="B447" s="6"/>
       <c r="C447" s="6"/>
@@ -17607,7 +17607,7 @@
       <c r="AH447" s="6"/>
       <c r="AI447" s="6"/>
     </row>
-    <row r="448" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="6"/>
       <c r="B448" s="6"/>
       <c r="C448" s="6"/>
@@ -17644,7 +17644,7 @@
       <c r="AH448" s="6"/>
       <c r="AI448" s="6"/>
     </row>
-    <row r="449" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="6"/>
       <c r="B449" s="6"/>
       <c r="C449" s="6"/>
@@ -17681,7 +17681,7 @@
       <c r="AH449" s="6"/>
       <c r="AI449" s="6"/>
     </row>
-    <row r="450" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="6"/>
       <c r="B450" s="6"/>
       <c r="C450" s="6"/>
@@ -17718,7 +17718,7 @@
       <c r="AH450" s="6"/>
       <c r="AI450" s="6"/>
     </row>
-    <row r="451" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="6"/>
       <c r="B451" s="6"/>
       <c r="C451" s="6"/>
@@ -17755,7 +17755,7 @@
       <c r="AH451" s="6"/>
       <c r="AI451" s="6"/>
     </row>
-    <row r="452" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="6"/>
       <c r="B452" s="6"/>
       <c r="C452" s="6"/>
@@ -17792,7 +17792,7 @@
       <c r="AH452" s="6"/>
       <c r="AI452" s="6"/>
     </row>
-    <row r="453" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="6"/>
       <c r="B453" s="6"/>
       <c r="C453" s="6"/>
@@ -17829,7 +17829,7 @@
       <c r="AH453" s="6"/>
       <c r="AI453" s="6"/>
     </row>
-    <row r="454" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="6"/>
       <c r="B454" s="6"/>
       <c r="C454" s="6"/>
@@ -17866,7 +17866,7 @@
       <c r="AH454" s="6"/>
       <c r="AI454" s="6"/>
     </row>
-    <row r="455" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="6"/>
       <c r="B455" s="6"/>
       <c r="C455" s="6"/>
@@ -17903,7 +17903,7 @@
       <c r="AH455" s="6"/>
       <c r="AI455" s="6"/>
     </row>
-    <row r="456" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="6"/>
       <c r="B456" s="6"/>
       <c r="C456" s="6"/>
@@ -17940,7 +17940,7 @@
       <c r="AH456" s="6"/>
       <c r="AI456" s="6"/>
     </row>
-    <row r="457" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="6"/>
       <c r="B457" s="6"/>
       <c r="C457" s="6"/>
@@ -17977,7 +17977,7 @@
       <c r="AH457" s="6"/>
       <c r="AI457" s="6"/>
     </row>
-    <row r="458" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="6"/>
       <c r="B458" s="6"/>
       <c r="C458" s="6"/>
@@ -18014,7 +18014,7 @@
       <c r="AH458" s="6"/>
       <c r="AI458" s="6"/>
     </row>
-    <row r="459" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="6"/>
       <c r="B459" s="6"/>
       <c r="C459" s="6"/>
@@ -18051,7 +18051,7 @@
       <c r="AH459" s="6"/>
       <c r="AI459" s="6"/>
     </row>
-    <row r="460" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="6"/>
       <c r="B460" s="6"/>
       <c r="C460" s="6"/>
@@ -18088,7 +18088,7 @@
       <c r="AH460" s="6"/>
       <c r="AI460" s="6"/>
     </row>
-    <row r="461" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="6"/>
       <c r="B461" s="6"/>
       <c r="C461" s="6"/>
@@ -18125,7 +18125,7 @@
       <c r="AH461" s="6"/>
       <c r="AI461" s="6"/>
     </row>
-    <row r="462" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="6"/>
       <c r="B462" s="6"/>
       <c r="C462" s="6"/>
@@ -18162,7 +18162,7 @@
       <c r="AH462" s="6"/>
       <c r="AI462" s="6"/>
     </row>
-    <row r="463" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="6"/>
       <c r="B463" s="6"/>
       <c r="C463" s="6"/>
@@ -18199,7 +18199,7 @@
       <c r="AH463" s="6"/>
       <c r="AI463" s="6"/>
     </row>
-    <row r="464" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="6"/>
       <c r="B464" s="6"/>
       <c r="C464" s="6"/>
@@ -18236,7 +18236,7 @@
       <c r="AH464" s="6"/>
       <c r="AI464" s="6"/>
     </row>
-    <row r="465" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="6"/>
       <c r="B465" s="6"/>
       <c r="C465" s="6"/>
@@ -18273,7 +18273,7 @@
       <c r="AH465" s="6"/>
       <c r="AI465" s="6"/>
     </row>
-    <row r="466" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="6"/>
       <c r="B466" s="6"/>
       <c r="C466" s="6"/>
@@ -18310,7 +18310,7 @@
       <c r="AH466" s="6"/>
       <c r="AI466" s="6"/>
     </row>
-    <row r="467" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="6"/>
       <c r="B467" s="6"/>
       <c r="C467" s="6"/>
@@ -18347,7 +18347,7 @@
       <c r="AH467" s="6"/>
       <c r="AI467" s="6"/>
     </row>
-    <row r="468" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="6"/>
       <c r="B468" s="6"/>
       <c r="C468" s="6"/>
@@ -18384,7 +18384,7 @@
       <c r="AH468" s="6"/>
       <c r="AI468" s="6"/>
     </row>
-    <row r="469" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="6"/>
       <c r="B469" s="6"/>
       <c r="C469" s="6"/>
@@ -18421,7 +18421,7 @@
       <c r="AH469" s="6"/>
       <c r="AI469" s="6"/>
     </row>
-    <row r="470" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="6"/>
       <c r="B470" s="6"/>
       <c r="C470" s="6"/>
@@ -18458,7 +18458,7 @@
       <c r="AH470" s="6"/>
       <c r="AI470" s="6"/>
     </row>
-    <row r="471" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="6"/>
       <c r="B471" s="6"/>
       <c r="C471" s="6"/>
@@ -18495,7 +18495,7 @@
       <c r="AH471" s="6"/>
       <c r="AI471" s="6"/>
     </row>
-    <row r="472" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="6"/>
       <c r="B472" s="6"/>
       <c r="C472" s="6"/>
@@ -18532,7 +18532,7 @@
       <c r="AH472" s="6"/>
       <c r="AI472" s="6"/>
     </row>
-    <row r="473" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="6"/>
       <c r="B473" s="6"/>
       <c r="C473" s="6"/>
@@ -18569,7 +18569,7 @@
       <c r="AH473" s="6"/>
       <c r="AI473" s="6"/>
     </row>
-    <row r="474" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="6"/>
       <c r="B474" s="6"/>
       <c r="C474" s="6"/>
@@ -18606,7 +18606,7 @@
       <c r="AH474" s="6"/>
       <c r="AI474" s="6"/>
     </row>
-    <row r="475" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="6"/>
       <c r="B475" s="6"/>
       <c r="C475" s="6"/>
@@ -18643,7 +18643,7 @@
       <c r="AH475" s="6"/>
       <c r="AI475" s="6"/>
     </row>
-    <row r="476" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="6"/>
       <c r="B476" s="6"/>
       <c r="C476" s="6"/>
@@ -18680,7 +18680,7 @@
       <c r="AH476" s="6"/>
       <c r="AI476" s="6"/>
     </row>
-    <row r="477" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="6"/>
       <c r="B477" s="6"/>
       <c r="C477" s="6"/>
@@ -18717,7 +18717,7 @@
       <c r="AH477" s="6"/>
       <c r="AI477" s="6"/>
     </row>
-    <row r="478" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="6"/>
       <c r="B478" s="6"/>
       <c r="C478" s="6"/>
@@ -18754,7 +18754,7 @@
       <c r="AH478" s="6"/>
       <c r="AI478" s="6"/>
     </row>
-    <row r="479" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="6"/>
       <c r="B479" s="6"/>
       <c r="C479" s="6"/>
@@ -18791,7 +18791,7 @@
       <c r="AH479" s="6"/>
       <c r="AI479" s="6"/>
     </row>
-    <row r="480" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="6"/>
       <c r="B480" s="6"/>
       <c r="C480" s="6"/>
@@ -18828,7 +18828,7 @@
       <c r="AH480" s="6"/>
       <c r="AI480" s="6"/>
     </row>
-    <row r="481" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="6"/>
       <c r="B481" s="6"/>
       <c r="C481" s="6"/>
@@ -18865,7 +18865,7 @@
       <c r="AH481" s="6"/>
       <c r="AI481" s="6"/>
     </row>
-    <row r="482" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="6"/>
       <c r="B482" s="6"/>
       <c r="C482" s="6"/>
@@ -18902,7 +18902,7 @@
       <c r="AH482" s="6"/>
       <c r="AI482" s="6"/>
     </row>
-    <row r="483" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="6"/>
       <c r="B483" s="6"/>
       <c r="C483" s="6"/>
@@ -18939,7 +18939,7 @@
       <c r="AH483" s="6"/>
       <c r="AI483" s="6"/>
     </row>
-    <row r="484" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="6"/>
       <c r="B484" s="6"/>
       <c r="C484" s="6"/>
@@ -18976,7 +18976,7 @@
       <c r="AH484" s="6"/>
       <c r="AI484" s="6"/>
     </row>
-    <row r="485" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="6"/>
       <c r="B485" s="6"/>
       <c r="C485" s="6"/>
@@ -19013,7 +19013,7 @@
       <c r="AH485" s="6"/>
       <c r="AI485" s="6"/>
     </row>
-    <row r="486" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="6"/>
       <c r="B486" s="6"/>
       <c r="C486" s="6"/>
@@ -19050,7 +19050,7 @@
       <c r="AH486" s="6"/>
       <c r="AI486" s="6"/>
     </row>
-    <row r="487" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="6"/>
       <c r="B487" s="6"/>
       <c r="C487" s="6"/>
@@ -19087,7 +19087,7 @@
       <c r="AH487" s="6"/>
       <c r="AI487" s="6"/>
     </row>
-    <row r="488" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="6"/>
       <c r="B488" s="6"/>
       <c r="C488" s="6"/>
@@ -19124,7 +19124,7 @@
       <c r="AH488" s="6"/>
       <c r="AI488" s="6"/>
     </row>
-    <row r="489" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="6"/>
       <c r="B489" s="6"/>
       <c r="C489" s="6"/>
@@ -19161,7 +19161,7 @@
       <c r="AH489" s="6"/>
       <c r="AI489" s="6"/>
     </row>
-    <row r="490" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="6"/>
       <c r="B490" s="6"/>
       <c r="C490" s="6"/>
@@ -19198,7 +19198,7 @@
       <c r="AH490" s="6"/>
       <c r="AI490" s="6"/>
     </row>
-    <row r="491" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="6"/>
       <c r="B491" s="6"/>
       <c r="C491" s="6"/>
@@ -19235,7 +19235,7 @@
       <c r="AH491" s="6"/>
       <c r="AI491" s="6"/>
     </row>
-    <row r="492" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="6"/>
       <c r="B492" s="6"/>
       <c r="C492" s="6"/>
@@ -19272,7 +19272,7 @@
       <c r="AH492" s="6"/>
       <c r="AI492" s="6"/>
     </row>
-    <row r="493" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="6"/>
       <c r="B493" s="6"/>
       <c r="C493" s="6"/>
@@ -19309,7 +19309,7 @@
       <c r="AH493" s="6"/>
       <c r="AI493" s="6"/>
     </row>
-    <row r="494" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="6"/>
       <c r="B494" s="6"/>
       <c r="C494" s="6"/>
@@ -19346,7 +19346,7 @@
       <c r="AH494" s="6"/>
       <c r="AI494" s="6"/>
     </row>
-    <row r="495" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="6"/>
       <c r="B495" s="6"/>
       <c r="C495" s="6"/>
@@ -19383,7 +19383,7 @@
       <c r="AH495" s="6"/>
       <c r="AI495" s="6"/>
     </row>
-    <row r="496" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="6"/>
       <c r="B496" s="6"/>
       <c r="C496" s="6"/>
@@ -19420,7 +19420,7 @@
       <c r="AH496" s="6"/>
       <c r="AI496" s="6"/>
     </row>
-    <row r="497" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="6"/>
       <c r="B497" s="6"/>
       <c r="C497" s="6"/>
@@ -19457,7 +19457,7 @@
       <c r="AH497" s="6"/>
       <c r="AI497" s="6"/>
     </row>
-    <row r="498" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="6"/>
       <c r="B498" s="6"/>
       <c r="C498" s="6"/>
@@ -19494,7 +19494,7 @@
       <c r="AH498" s="6"/>
       <c r="AI498" s="6"/>
     </row>
-    <row r="499" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="6"/>
       <c r="B499" s="6"/>
       <c r="C499" s="6"/>
@@ -19531,7 +19531,7 @@
       <c r="AH499" s="6"/>
       <c r="AI499" s="6"/>
     </row>
-    <row r="500" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="6"/>
       <c r="B500" s="6"/>
       <c r="C500" s="6"/>
@@ -19568,7 +19568,7 @@
       <c r="AH500" s="6"/>
       <c r="AI500" s="6"/>
     </row>
-    <row r="501" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="6"/>
       <c r="B501" s="6"/>
       <c r="C501" s="6"/>
@@ -19605,7 +19605,7 @@
       <c r="AH501" s="6"/>
       <c r="AI501" s="6"/>
     </row>
-    <row r="502" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="6"/>
       <c r="B502" s="6"/>
       <c r="C502" s="6"/>
@@ -19642,7 +19642,7 @@
       <c r="AH502" s="6"/>
       <c r="AI502" s="6"/>
     </row>
-    <row r="503" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="6"/>
       <c r="B503" s="6"/>
       <c r="C503" s="6"/>
@@ -19679,7 +19679,7 @@
       <c r="AH503" s="6"/>
       <c r="AI503" s="6"/>
     </row>
-    <row r="504" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="6"/>
       <c r="B504" s="6"/>
       <c r="C504" s="6"/>
@@ -19716,7 +19716,7 @@
       <c r="AH504" s="6"/>
       <c r="AI504" s="6"/>
     </row>
-    <row r="505" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="6"/>
       <c r="B505" s="6"/>
       <c r="C505" s="6"/>
@@ -19753,7 +19753,7 @@
       <c r="AH505" s="6"/>
       <c r="AI505" s="6"/>
     </row>
-    <row r="506" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="6"/>
       <c r="B506" s="6"/>
       <c r="C506" s="6"/>
@@ -19790,7 +19790,7 @@
       <c r="AH506" s="6"/>
       <c r="AI506" s="6"/>
     </row>
-    <row r="507" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="6"/>
       <c r="B507" s="6"/>
       <c r="C507" s="6"/>
@@ -19827,7 +19827,7 @@
       <c r="AH507" s="6"/>
       <c r="AI507" s="6"/>
     </row>
-    <row r="508" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="6"/>
       <c r="B508" s="6"/>
       <c r="C508" s="6"/>
@@ -19864,7 +19864,7 @@
       <c r="AH508" s="6"/>
       <c r="AI508" s="6"/>
     </row>
-    <row r="509" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="6"/>
       <c r="B509" s="6"/>
       <c r="C509" s="6"/>
@@ -19901,7 +19901,7 @@
       <c r="AH509" s="6"/>
       <c r="AI509" s="6"/>
     </row>
-    <row r="510" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="6"/>
       <c r="B510" s="6"/>
       <c r="C510" s="6"/>
@@ -19938,7 +19938,7 @@
       <c r="AH510" s="6"/>
       <c r="AI510" s="6"/>
     </row>
-    <row r="511" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="6"/>
       <c r="B511" s="6"/>
       <c r="C511" s="6"/>
@@ -19975,7 +19975,7 @@
       <c r="AH511" s="6"/>
       <c r="AI511" s="6"/>
     </row>
-    <row r="512" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="6"/>
       <c r="B512" s="6"/>
       <c r="C512" s="6"/>
@@ -20012,7 +20012,7 @@
       <c r="AH512" s="6"/>
       <c r="AI512" s="6"/>
     </row>
-    <row r="513" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="6"/>
       <c r="B513" s="6"/>
       <c r="C513" s="6"/>
@@ -20049,7 +20049,7 @@
       <c r="AH513" s="6"/>
       <c r="AI513" s="6"/>
     </row>
-    <row r="514" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="6"/>
       <c r="B514" s="6"/>
       <c r="C514" s="6"/>
@@ -20086,7 +20086,7 @@
       <c r="AH514" s="6"/>
       <c r="AI514" s="6"/>
     </row>
-    <row r="515" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="6"/>
       <c r="B515" s="6"/>
       <c r="C515" s="6"/>
@@ -20123,7 +20123,7 @@
       <c r="AH515" s="6"/>
       <c r="AI515" s="6"/>
     </row>
-    <row r="516" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="6"/>
       <c r="B516" s="6"/>
       <c r="C516" s="6"/>
@@ -20160,7 +20160,7 @@
       <c r="AH516" s="6"/>
       <c r="AI516" s="6"/>
     </row>
-    <row r="517" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="6"/>
       <c r="B517" s="6"/>
       <c r="C517" s="6"/>
@@ -20197,7 +20197,7 @@
       <c r="AH517" s="6"/>
       <c r="AI517" s="6"/>
     </row>
-    <row r="518" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="6"/>
       <c r="B518" s="6"/>
       <c r="C518" s="6"/>
@@ -20234,7 +20234,7 @@
       <c r="AH518" s="6"/>
       <c r="AI518" s="6"/>
     </row>
-    <row r="519" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="6"/>
       <c r="B519" s="6"/>
       <c r="C519" s="6"/>
@@ -20271,7 +20271,7 @@
       <c r="AH519" s="6"/>
       <c r="AI519" s="6"/>
     </row>
-    <row r="520" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="6"/>
       <c r="B520" s="6"/>
       <c r="C520" s="6"/>
@@ -20308,7 +20308,7 @@
       <c r="AH520" s="6"/>
       <c r="AI520" s="6"/>
     </row>
-    <row r="521" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="6"/>
       <c r="B521" s="6"/>
       <c r="C521" s="6"/>
@@ -20345,7 +20345,7 @@
       <c r="AH521" s="6"/>
       <c r="AI521" s="6"/>
     </row>
-    <row r="522" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="6"/>
       <c r="B522" s="6"/>
       <c r="C522" s="6"/>
@@ -20382,7 +20382,7 @@
       <c r="AH522" s="6"/>
       <c r="AI522" s="6"/>
     </row>
-    <row r="523" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="6"/>
       <c r="B523" s="6"/>
       <c r="C523" s="6"/>
@@ -20419,7 +20419,7 @@
       <c r="AH523" s="6"/>
       <c r="AI523" s="6"/>
     </row>
-    <row r="524" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="6"/>
       <c r="B524" s="6"/>
       <c r="C524" s="6"/>
@@ -20456,7 +20456,7 @@
       <c r="AH524" s="6"/>
       <c r="AI524" s="6"/>
     </row>
-    <row r="525" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="6"/>
       <c r="B525" s="6"/>
       <c r="C525" s="6"/>
@@ -20493,7 +20493,7 @@
       <c r="AH525" s="6"/>
       <c r="AI525" s="6"/>
     </row>
-    <row r="526" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="6"/>
       <c r="B526" s="6"/>
       <c r="C526" s="6"/>
@@ -20530,7 +20530,7 @@
       <c r="AH526" s="6"/>
       <c r="AI526" s="6"/>
     </row>
-    <row r="527" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="6"/>
       <c r="B527" s="6"/>
       <c r="C527" s="6"/>
@@ -20567,7 +20567,7 @@
       <c r="AH527" s="6"/>
       <c r="AI527" s="6"/>
     </row>
-    <row r="528" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="6"/>
       <c r="B528" s="6"/>
       <c r="C528" s="6"/>
@@ -20604,7 +20604,7 @@
       <c r="AH528" s="6"/>
       <c r="AI528" s="6"/>
     </row>
-    <row r="529" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="6"/>
       <c r="B529" s="6"/>
       <c r="C529" s="6"/>
@@ -20641,7 +20641,7 @@
       <c r="AH529" s="6"/>
       <c r="AI529" s="6"/>
     </row>
-    <row r="530" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="6"/>
       <c r="B530" s="6"/>
       <c r="C530" s="6"/>
@@ -20678,7 +20678,7 @@
       <c r="AH530" s="6"/>
       <c r="AI530" s="6"/>
     </row>
-    <row r="531" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="6"/>
       <c r="B531" s="6"/>
       <c r="C531" s="6"/>
@@ -20715,7 +20715,7 @@
       <c r="AH531" s="6"/>
       <c r="AI531" s="6"/>
     </row>
-    <row r="532" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="6"/>
       <c r="B532" s="6"/>
       <c r="C532" s="6"/>
@@ -20752,7 +20752,7 @@
       <c r="AH532" s="6"/>
       <c r="AI532" s="6"/>
     </row>
-    <row r="533" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="6"/>
       <c r="B533" s="6"/>
       <c r="C533" s="6"/>
@@ -20789,7 +20789,7 @@
       <c r="AH533" s="6"/>
       <c r="AI533" s="6"/>
     </row>
-    <row r="534" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="6"/>
       <c r="B534" s="6"/>
       <c r="C534" s="6"/>
@@ -20826,7 +20826,7 @@
       <c r="AH534" s="6"/>
       <c r="AI534" s="6"/>
     </row>
-    <row r="535" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="6"/>
       <c r="B535" s="6"/>
       <c r="C535" s="6"/>
@@ -20863,7 +20863,7 @@
       <c r="AH535" s="6"/>
       <c r="AI535" s="6"/>
     </row>
-    <row r="536" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="6"/>
       <c r="B536" s="6"/>
       <c r="C536" s="6"/>
@@ -20900,7 +20900,7 @@
       <c r="AH536" s="6"/>
       <c r="AI536" s="6"/>
     </row>
-    <row r="537" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="6"/>
       <c r="B537" s="6"/>
       <c r="C537" s="6"/>
@@ -20937,7 +20937,7 @@
       <c r="AH537" s="6"/>
       <c r="AI537" s="6"/>
     </row>
-    <row r="538" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="6"/>
       <c r="B538" s="6"/>
       <c r="C538" s="6"/>
@@ -20974,7 +20974,7 @@
       <c r="AH538" s="6"/>
       <c r="AI538" s="6"/>
     </row>
-    <row r="539" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="6"/>
       <c r="B539" s="6"/>
       <c r="C539" s="6"/>
@@ -21011,7 +21011,7 @@
       <c r="AH539" s="6"/>
       <c r="AI539" s="6"/>
     </row>
-    <row r="540" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="6"/>
       <c r="B540" s="6"/>
       <c r="C540" s="6"/>
@@ -21048,7 +21048,7 @@
       <c r="AH540" s="6"/>
       <c r="AI540" s="6"/>
     </row>
-    <row r="541" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="6"/>
       <c r="B541" s="6"/>
       <c r="C541" s="6"/>
@@ -21085,7 +21085,7 @@
       <c r="AH541" s="6"/>
       <c r="AI541" s="6"/>
     </row>
-    <row r="542" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="6"/>
       <c r="B542" s="6"/>
       <c r="C542" s="6"/>
@@ -21122,7 +21122,7 @@
       <c r="AH542" s="6"/>
       <c r="AI542" s="6"/>
     </row>
-    <row r="543" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="6"/>
       <c r="B543" s="6"/>
       <c r="C543" s="6"/>
@@ -21159,7 +21159,7 @@
       <c r="AH543" s="6"/>
       <c r="AI543" s="6"/>
     </row>
-    <row r="544" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="6"/>
       <c r="B544" s="6"/>
       <c r="C544" s="6"/>
@@ -21196,7 +21196,7 @@
       <c r="AH544" s="6"/>
       <c r="AI544" s="6"/>
     </row>
-    <row r="545" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="6"/>
       <c r="B545" s="6"/>
       <c r="C545" s="6"/>
@@ -21233,7 +21233,7 @@
       <c r="AH545" s="6"/>
       <c r="AI545" s="6"/>
     </row>
-    <row r="546" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="6"/>
       <c r="B546" s="6"/>
       <c r="C546" s="6"/>
@@ -21270,7 +21270,7 @@
       <c r="AH546" s="6"/>
       <c r="AI546" s="6"/>
     </row>
-    <row r="547" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="6"/>
       <c r="B547" s="6"/>
       <c r="C547" s="6"/>
@@ -21307,7 +21307,7 @@
       <c r="AH547" s="6"/>
       <c r="AI547" s="6"/>
     </row>
-    <row r="548" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="6"/>
       <c r="B548" s="6"/>
       <c r="C548" s="6"/>
@@ -21344,7 +21344,7 @@
       <c r="AH548" s="6"/>
       <c r="AI548" s="6"/>
     </row>
-    <row r="549" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="6"/>
       <c r="B549" s="6"/>
       <c r="C549" s="6"/>
@@ -21381,7 +21381,7 @@
       <c r="AH549" s="6"/>
       <c r="AI549" s="6"/>
     </row>
-    <row r="550" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="6"/>
       <c r="B550" s="6"/>
       <c r="C550" s="6"/>
@@ -21418,7 +21418,7 @@
       <c r="AH550" s="6"/>
       <c r="AI550" s="6"/>
     </row>
-    <row r="551" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="6"/>
       <c r="B551" s="6"/>
       <c r="C551" s="6"/>
@@ -21455,7 +21455,7 @@
       <c r="AH551" s="6"/>
       <c r="AI551" s="6"/>
     </row>
-    <row r="552" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="6"/>
       <c r="B552" s="6"/>
       <c r="C552" s="6"/>
@@ -21492,7 +21492,7 @@
       <c r="AH552" s="6"/>
       <c r="AI552" s="6"/>
     </row>
-    <row r="553" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="6"/>
       <c r="B553" s="6"/>
       <c r="C553" s="6"/>
@@ -21529,7 +21529,7 @@
       <c r="AH553" s="6"/>
       <c r="AI553" s="6"/>
     </row>
-    <row r="554" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="6"/>
       <c r="B554" s="6"/>
       <c r="C554" s="6"/>
@@ -21566,7 +21566,7 @@
       <c r="AH554" s="6"/>
       <c r="AI554" s="6"/>
     </row>
-    <row r="555" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="6"/>
       <c r="B555" s="6"/>
       <c r="C555" s="6"/>
@@ -21603,7 +21603,7 @@
       <c r="AH555" s="6"/>
       <c r="AI555" s="6"/>
     </row>
-    <row r="556" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="6"/>
       <c r="B556" s="6"/>
       <c r="C556" s="6"/>
@@ -21640,7 +21640,7 @@
       <c r="AH556" s="6"/>
       <c r="AI556" s="6"/>
     </row>
-    <row r="557" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="6"/>
       <c r="B557" s="6"/>
       <c r="C557" s="6"/>
@@ -21677,7 +21677,7 @@
       <c r="AH557" s="6"/>
       <c r="AI557" s="6"/>
     </row>
-    <row r="558" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="6"/>
       <c r="B558" s="6"/>
       <c r="C558" s="6"/>
@@ -21714,7 +21714,7 @@
       <c r="AH558" s="6"/>
       <c r="AI558" s="6"/>
     </row>
-    <row r="559" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="6"/>
       <c r="B559" s="6"/>
       <c r="C559" s="6"/>
@@ -21751,7 +21751,7 @@
       <c r="AH559" s="6"/>
       <c r="AI559" s="6"/>
     </row>
-    <row r="560" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="6"/>
       <c r="B560" s="6"/>
       <c r="C560" s="6"/>
@@ -21788,7 +21788,7 @@
       <c r="AH560" s="6"/>
       <c r="AI560" s="6"/>
     </row>
-    <row r="561" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="6"/>
       <c r="B561" s="6"/>
       <c r="C561" s="6"/>
@@ -21825,7 +21825,7 @@
       <c r="AH561" s="6"/>
       <c r="AI561" s="6"/>
     </row>
-    <row r="562" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="6"/>
       <c r="B562" s="6"/>
       <c r="C562" s="6"/>
@@ -21862,7 +21862,7 @@
       <c r="AH562" s="6"/>
       <c r="AI562" s="6"/>
     </row>
-    <row r="563" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="6"/>
       <c r="B563" s="6"/>
       <c r="C563" s="6"/>
@@ -21899,7 +21899,7 @@
       <c r="AH563" s="6"/>
       <c r="AI563" s="6"/>
     </row>
-    <row r="564" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="6"/>
       <c r="B564" s="6"/>
       <c r="C564" s="6"/>
@@ -21936,7 +21936,7 @@
       <c r="AH564" s="6"/>
       <c r="AI564" s="6"/>
     </row>
-    <row r="565" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="6"/>
       <c r="B565" s="6"/>
       <c r="C565" s="6"/>
@@ -21973,7 +21973,7 @@
       <c r="AH565" s="6"/>
       <c r="AI565" s="6"/>
     </row>
-    <row r="566" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="6"/>
       <c r="B566" s="6"/>
       <c r="C566" s="6"/>
@@ -22010,7 +22010,7 @@
       <c r="AH566" s="6"/>
       <c r="AI566" s="6"/>
     </row>
-    <row r="567" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="6"/>
       <c r="B567" s="6"/>
       <c r="C567" s="6"/>
@@ -22047,7 +22047,7 @@
       <c r="AH567" s="6"/>
       <c r="AI567" s="6"/>
     </row>
-    <row r="568" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="6"/>
       <c r="B568" s="6"/>
       <c r="C568" s="6"/>
@@ -22084,7 +22084,7 @@
       <c r="AH568" s="6"/>
       <c r="AI568" s="6"/>
     </row>
-    <row r="569" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="6"/>
       <c r="B569" s="6"/>
       <c r="C569" s="6"/>
@@ -22121,7 +22121,7 @@
       <c r="AH569" s="6"/>
       <c r="AI569" s="6"/>
     </row>
-    <row r="570" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="6"/>
       <c r="B570" s="6"/>
       <c r="C570" s="6"/>
@@ -22158,7 +22158,7 @@
       <c r="AH570" s="6"/>
       <c r="AI570" s="6"/>
     </row>
-    <row r="571" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="6"/>
       <c r="B571" s="6"/>
       <c r="C571" s="6"/>
@@ -22195,7 +22195,7 @@
       <c r="AH571" s="6"/>
       <c r="AI571" s="6"/>
     </row>
-    <row r="572" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="6"/>
       <c r="B572" s="6"/>
       <c r="C572" s="6"/>
@@ -22232,7 +22232,7 @@
       <c r="AH572" s="6"/>
       <c r="AI572" s="6"/>
     </row>
-    <row r="573" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="6"/>
       <c r="B573" s="6"/>
       <c r="C573" s="6"/>
@@ -22269,7 +22269,7 @@
       <c r="AH573" s="6"/>
       <c r="AI573" s="6"/>
     </row>
-    <row r="574" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="6"/>
       <c r="B574" s="6"/>
       <c r="C574" s="6"/>
@@ -22306,7 +22306,7 @@
       <c r="AH574" s="6"/>
       <c r="AI574" s="6"/>
     </row>
-    <row r="575" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="6"/>
       <c r="B575" s="6"/>
       <c r="C575" s="6"/>
@@ -22343,7 +22343,7 @@
       <c r="AH575" s="6"/>
       <c r="AI575" s="6"/>
     </row>
-    <row r="576" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="6"/>
       <c r="B576" s="6"/>
       <c r="C576" s="6"/>
@@ -22380,7 +22380,7 @@
       <c r="AH576" s="6"/>
       <c r="AI576" s="6"/>
     </row>
-    <row r="577" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="6"/>
       <c r="B577" s="6"/>
       <c r="C577" s="6"/>
@@ -22417,7 +22417,7 @@
       <c r="AH577" s="6"/>
       <c r="AI577" s="6"/>
     </row>
-    <row r="578" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="6"/>
       <c r="B578" s="6"/>
       <c r="C578" s="6"/>
@@ -22454,7 +22454,7 @@
       <c r="AH578" s="6"/>
       <c r="AI578" s="6"/>
     </row>
-    <row r="579" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="6"/>
       <c r="B579" s="6"/>
       <c r="C579" s="6"/>
@@ -22491,7 +22491,7 @@
       <c r="AH579" s="6"/>
       <c r="AI579" s="6"/>
     </row>
-    <row r="580" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="6"/>
       <c r="B580" s="6"/>
       <c r="C580" s="6"/>
@@ -22528,7 +22528,7 @@
       <c r="AH580" s="6"/>
       <c r="AI580" s="6"/>
     </row>
-    <row r="581" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="6"/>
       <c r="B581" s="6"/>
       <c r="C581" s="6"/>
@@ -22565,7 +22565,7 @@
       <c r="AH581" s="6"/>
       <c r="AI581" s="6"/>
     </row>
-    <row r="582" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="6"/>
       <c r="B582" s="6"/>
       <c r="C582" s="6"/>
@@ -22602,7 +22602,7 @@
       <c r="AH582" s="6"/>
       <c r="AI582" s="6"/>
     </row>
-    <row r="583" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="6"/>
       <c r="B583" s="6"/>
       <c r="C583" s="6"/>
@@ -22639,7 +22639,7 @@
       <c r="AH583" s="6"/>
       <c r="AI583" s="6"/>
     </row>
-    <row r="584" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="6"/>
       <c r="B584" s="6"/>
       <c r="C584" s="6"/>
@@ -22676,7 +22676,7 @@
       <c r="AH584" s="6"/>
       <c r="AI584" s="6"/>
     </row>
-    <row r="585" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="6"/>
       <c r="B585" s="6"/>
       <c r="C585" s="6"/>
@@ -22713,7 +22713,7 @@
       <c r="AH585" s="6"/>
       <c r="AI585" s="6"/>
     </row>
-    <row r="586" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="6"/>
       <c r="B586" s="6"/>
       <c r="C586" s="6"/>
@@ -22750,7 +22750,7 @@
       <c r="AH586" s="6"/>
       <c r="AI586" s="6"/>
     </row>
-    <row r="587" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="6"/>
       <c r="B587" s="6"/>
       <c r="C587" s="6"/>
@@ -22787,7 +22787,7 @@
       <c r="AH587" s="6"/>
       <c r="AI587" s="6"/>
     </row>
-    <row r="588" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="6"/>
       <c r="B588" s="6"/>
       <c r="C588" s="6"/>
@@ -22824,7 +22824,7 @@
       <c r="AH588" s="6"/>
       <c r="AI588" s="6"/>
     </row>
-    <row r="589" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="6"/>
       <c r="B589" s="6"/>
       <c r="C589" s="6"/>
@@ -22861,7 +22861,7 @@
       <c r="AH589" s="6"/>
       <c r="AI589" s="6"/>
     </row>
-    <row r="590" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="6"/>
       <c r="B590" s="6"/>
       <c r="C590" s="6"/>
@@ -22898,7 +22898,7 @@
       <c r="AH590" s="6"/>
       <c r="AI590" s="6"/>
     </row>
-    <row r="591" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A591" s="6"/>
       <c r="B591" s="6"/>
       <c r="C591" s="6"/>
@@ -22935,7 +22935,7 @@
       <c r="AH591" s="6"/>
       <c r="AI591" s="6"/>
     </row>
-    <row r="592" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A592" s="6"/>
       <c r="B592" s="6"/>
       <c r="C592" s="6"/>
@@ -22972,7 +22972,7 @@
       <c r="AH592" s="6"/>
       <c r="AI592" s="6"/>
     </row>
-    <row r="593" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A593" s="6"/>
       <c r="B593" s="6"/>
       <c r="C593" s="6"/>
@@ -23009,7 +23009,7 @@
       <c r="AH593" s="6"/>
       <c r="AI593" s="6"/>
     </row>
-    <row r="594" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" s="6"/>
       <c r="B594" s="6"/>
       <c r="C594" s="6"/>
@@ -23046,7 +23046,7 @@
       <c r="AH594" s="6"/>
       <c r="AI594" s="6"/>
     </row>
-    <row r="595" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A595" s="6"/>
       <c r="B595" s="6"/>
       <c r="C595" s="6"/>
@@ -23083,7 +23083,7 @@
       <c r="AH595" s="6"/>
       <c r="AI595" s="6"/>
     </row>
-    <row r="596" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A596" s="6"/>
       <c r="B596" s="6"/>
       <c r="C596" s="6"/>
@@ -23120,7 +23120,7 @@
       <c r="AH596" s="6"/>
       <c r="AI596" s="6"/>
     </row>
-    <row r="597" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A597" s="6"/>
       <c r="B597" s="6"/>
       <c r="C597" s="6"/>
@@ -23157,7 +23157,7 @@
       <c r="AH597" s="6"/>
       <c r="AI597" s="6"/>
     </row>
-    <row r="598" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A598" s="6"/>
       <c r="B598" s="6"/>
       <c r="C598" s="6"/>
@@ -23194,7 +23194,7 @@
       <c r="AH598" s="6"/>
       <c r="AI598" s="6"/>
     </row>
-    <row r="599" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A599" s="6"/>
       <c r="B599" s="6"/>
       <c r="C599" s="6"/>
@@ -23231,7 +23231,7 @@
       <c r="AH599" s="6"/>
       <c r="AI599" s="6"/>
     </row>
-    <row r="600" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A600" s="6"/>
       <c r="B600" s="6"/>
       <c r="C600" s="6"/>
@@ -23268,7 +23268,7 @@
       <c r="AH600" s="6"/>
       <c r="AI600" s="6"/>
     </row>
-    <row r="601" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A601" s="6"/>
       <c r="B601" s="6"/>
       <c r="C601" s="6"/>
@@ -23305,7 +23305,7 @@
       <c r="AH601" s="6"/>
       <c r="AI601" s="6"/>
     </row>
-    <row r="602" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="6"/>
       <c r="B602" s="6"/>
       <c r="C602" s="6"/>
@@ -23342,7 +23342,7 @@
       <c r="AH602" s="6"/>
       <c r="AI602" s="6"/>
     </row>
-    <row r="603" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A603" s="6"/>
       <c r="B603" s="6"/>
       <c r="C603" s="6"/>
@@ -23379,7 +23379,7 @@
       <c r="AH603" s="6"/>
       <c r="AI603" s="6"/>
     </row>
-    <row r="604" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A604" s="6"/>
       <c r="B604" s="6"/>
       <c r="C604" s="6"/>
@@ -23416,7 +23416,7 @@
       <c r="AH604" s="6"/>
       <c r="AI604" s="6"/>
     </row>
-    <row r="605" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A605" s="6"/>
       <c r="B605" s="6"/>
       <c r="C605" s="6"/>
@@ -23453,7 +23453,7 @@
       <c r="AH605" s="6"/>
       <c r="AI605" s="6"/>
     </row>
-    <row r="606" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A606" s="6"/>
       <c r="B606" s="6"/>
       <c r="C606" s="6"/>
@@ -23490,7 +23490,7 @@
       <c r="AH606" s="6"/>
       <c r="AI606" s="6"/>
     </row>
-    <row r="607" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A607" s="6"/>
       <c r="B607" s="6"/>
       <c r="C607" s="6"/>
@@ -23527,7 +23527,7 @@
       <c r="AH607" s="6"/>
       <c r="AI607" s="6"/>
     </row>
-    <row r="608" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A608" s="6"/>
       <c r="B608" s="6"/>
       <c r="C608" s="6"/>
@@ -23564,7 +23564,7 @@
       <c r="AH608" s="6"/>
       <c r="AI608" s="6"/>
     </row>
-    <row r="609" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A609" s="6"/>
       <c r="B609" s="6"/>
       <c r="C609" s="6"/>
@@ -23601,7 +23601,7 @@
       <c r="AH609" s="6"/>
       <c r="AI609" s="6"/>
     </row>
-    <row r="610" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A610" s="6"/>
       <c r="B610" s="6"/>
       <c r="C610" s="6"/>
@@ -23638,7 +23638,7 @@
       <c r="AH610" s="6"/>
       <c r="AI610" s="6"/>
     </row>
-    <row r="611" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A611" s="6"/>
       <c r="B611" s="6"/>
       <c r="C611" s="6"/>
@@ -23675,7 +23675,7 @@
       <c r="AH611" s="6"/>
       <c r="AI611" s="6"/>
     </row>
-    <row r="612" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A612" s="6"/>
       <c r="B612" s="6"/>
       <c r="C612" s="6"/>
@@ -23712,7 +23712,7 @@
       <c r="AH612" s="6"/>
       <c r="AI612" s="6"/>
     </row>
-    <row r="613" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A613" s="6"/>
       <c r="B613" s="6"/>
       <c r="C613" s="6"/>
@@ -23749,7 +23749,7 @@
       <c r="AH613" s="6"/>
       <c r="AI613" s="6"/>
     </row>
-    <row r="614" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A614" s="6"/>
       <c r="B614" s="6"/>
       <c r="C614" s="6"/>
@@ -23786,7 +23786,7 @@
       <c r="AH614" s="6"/>
       <c r="AI614" s="6"/>
     </row>
-    <row r="615" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A615" s="6"/>
       <c r="B615" s="6"/>
       <c r="C615" s="6"/>
@@ -23823,7 +23823,7 @@
       <c r="AH615" s="6"/>
       <c r="AI615" s="6"/>
     </row>
-    <row r="616" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A616" s="6"/>
       <c r="B616" s="6"/>
       <c r="C616" s="6"/>
@@ -23860,7 +23860,7 @@
       <c r="AH616" s="6"/>
       <c r="AI616" s="6"/>
     </row>
-    <row r="617" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A617" s="6"/>
       <c r="B617" s="6"/>
       <c r="C617" s="6"/>
@@ -23897,7 +23897,7 @@
       <c r="AH617" s="6"/>
       <c r="AI617" s="6"/>
     </row>
-    <row r="618" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A618" s="6"/>
       <c r="B618" s="6"/>
       <c r="C618" s="6"/>
@@ -23934,7 +23934,7 @@
       <c r="AH618" s="6"/>
       <c r="AI618" s="6"/>
     </row>
-    <row r="619" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A619" s="6"/>
       <c r="B619" s="6"/>
       <c r="C619" s="6"/>
@@ -23971,7 +23971,7 @@
       <c r="AH619" s="6"/>
       <c r="AI619" s="6"/>
     </row>
-    <row r="620" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A620" s="6"/>
       <c r="B620" s="6"/>
       <c r="C620" s="6"/>
@@ -24008,7 +24008,7 @@
       <c r="AH620" s="6"/>
       <c r="AI620" s="6"/>
     </row>
-    <row r="621" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A621" s="6"/>
       <c r="B621" s="6"/>
       <c r="C621" s="6"/>
@@ -24045,7 +24045,7 @@
       <c r="AH621" s="6"/>
       <c r="AI621" s="6"/>
     </row>
-    <row r="622" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A622" s="6"/>
       <c r="B622" s="6"/>
       <c r="C622" s="6"/>
@@ -24082,7 +24082,7 @@
       <c r="AH622" s="6"/>
       <c r="AI622" s="6"/>
     </row>
-    <row r="623" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A623" s="6"/>
       <c r="B623" s="6"/>
       <c r="C623" s="6"/>
@@ -24119,7 +24119,7 @@
       <c r="AH623" s="6"/>
       <c r="AI623" s="6"/>
     </row>
-    <row r="624" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A624" s="6"/>
       <c r="B624" s="6"/>
       <c r="C624" s="6"/>
@@ -24156,7 +24156,7 @@
       <c r="AH624" s="6"/>
       <c r="AI624" s="6"/>
     </row>
-    <row r="625" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A625" s="6"/>
       <c r="B625" s="6"/>
       <c r="C625" s="6"/>
@@ -24193,7 +24193,7 @@
       <c r="AH625" s="6"/>
       <c r="AI625" s="6"/>
     </row>
-    <row r="626" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A626" s="6"/>
       <c r="B626" s="6"/>
       <c r="C626" s="6"/>
@@ -24230,7 +24230,7 @@
       <c r="AH626" s="6"/>
       <c r="AI626" s="6"/>
     </row>
-    <row r="627" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A627" s="6"/>
       <c r="B627" s="6"/>
       <c r="C627" s="6"/>
@@ -24267,7 +24267,7 @@
       <c r="AH627" s="6"/>
       <c r="AI627" s="6"/>
     </row>
-    <row r="628" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A628" s="6"/>
       <c r="B628" s="6"/>
       <c r="C628" s="6"/>
@@ -24304,7 +24304,7 @@
       <c r="AH628" s="6"/>
       <c r="AI628" s="6"/>
     </row>
-    <row r="629" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A629" s="6"/>
       <c r="B629" s="6"/>
       <c r="C629" s="6"/>
@@ -24341,7 +24341,7 @@
       <c r="AH629" s="6"/>
       <c r="AI629" s="6"/>
     </row>
-    <row r="630" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A630" s="6"/>
       <c r="B630" s="6"/>
       <c r="C630" s="6"/>
@@ -24378,7 +24378,7 @@
       <c r="AH630" s="6"/>
       <c r="AI630" s="6"/>
     </row>
-    <row r="631" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A631" s="6"/>
       <c r="B631" s="6"/>
       <c r="C631" s="6"/>
@@ -24415,7 +24415,7 @@
       <c r="AH631" s="6"/>
       <c r="AI631" s="6"/>
     </row>
-    <row r="632" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A632" s="6"/>
       <c r="B632" s="6"/>
       <c r="C632" s="6"/>
@@ -24452,7 +24452,7 @@
       <c r="AH632" s="6"/>
       <c r="AI632" s="6"/>
     </row>
-    <row r="633" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A633" s="6"/>
       <c r="B633" s="6"/>
       <c r="C633" s="6"/>
@@ -24489,7 +24489,7 @@
       <c r="AH633" s="6"/>
       <c r="AI633" s="6"/>
     </row>
-    <row r="634" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A634" s="6"/>
       <c r="B634" s="6"/>
       <c r="C634" s="6"/>
@@ -24526,7 +24526,7 @@
       <c r="AH634" s="6"/>
       <c r="AI634" s="6"/>
     </row>
-    <row r="635" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A635" s="6"/>
       <c r="B635" s="6"/>
       <c r="C635" s="6"/>
@@ -24563,7 +24563,7 @@
       <c r="AH635" s="6"/>
       <c r="AI635" s="6"/>
     </row>
-    <row r="636" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A636" s="6"/>
       <c r="B636" s="6"/>
       <c r="C636" s="6"/>
@@ -24600,7 +24600,7 @@
       <c r="AH636" s="6"/>
       <c r="AI636" s="6"/>
     </row>
-    <row r="637" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A637" s="6"/>
       <c r="B637" s="6"/>
       <c r="C637" s="6"/>
@@ -24637,7 +24637,7 @@
       <c r="AH637" s="6"/>
       <c r="AI637" s="6"/>
     </row>
-    <row r="638" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A638" s="6"/>
       <c r="B638" s="6"/>
       <c r="C638" s="6"/>
@@ -24674,7 +24674,7 @@
       <c r="AH638" s="6"/>
       <c r="AI638" s="6"/>
     </row>
-    <row r="639" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A639" s="6"/>
       <c r="B639" s="6"/>
       <c r="C639" s="6"/>
@@ -24711,7 +24711,7 @@
       <c r="AH639" s="6"/>
       <c r="AI639" s="6"/>
     </row>
-    <row r="640" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A640" s="6"/>
       <c r="B640" s="6"/>
       <c r="C640" s="6"/>
@@ -24748,7 +24748,7 @@
       <c r="AH640" s="6"/>
       <c r="AI640" s="6"/>
     </row>
-    <row r="641" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A641" s="6"/>
       <c r="B641" s="6"/>
       <c r="C641" s="6"/>
@@ -24785,7 +24785,7 @@
       <c r="AH641" s="6"/>
       <c r="AI641" s="6"/>
     </row>
-    <row r="642" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A642" s="6"/>
       <c r="B642" s="6"/>
       <c r="C642" s="6"/>
@@ -24822,7 +24822,7 @@
       <c r="AH642" s="6"/>
       <c r="AI642" s="6"/>
     </row>
-    <row r="643" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A643" s="6"/>
       <c r="B643" s="6"/>
       <c r="C643" s="6"/>
@@ -24859,7 +24859,7 @@
       <c r="AH643" s="6"/>
       <c r="AI643" s="6"/>
     </row>
-    <row r="644" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A644" s="6"/>
       <c r="B644" s="6"/>
       <c r="C644" s="6"/>
@@ -24896,7 +24896,7 @@
       <c r="AH644" s="6"/>
       <c r="AI644" s="6"/>
     </row>
-    <row r="645" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A645" s="6"/>
       <c r="B645" s="6"/>
       <c r="C645" s="6"/>
@@ -24933,7 +24933,7 @@
       <c r="AH645" s="6"/>
       <c r="AI645" s="6"/>
     </row>
-    <row r="646" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A646" s="6"/>
       <c r="B646" s="6"/>
       <c r="C646" s="6"/>
@@ -24970,7 +24970,7 @@
       <c r="AH646" s="6"/>
       <c r="AI646" s="6"/>
     </row>
-    <row r="647" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A647" s="6"/>
       <c r="B647" s="6"/>
       <c r="C647" s="6"/>
@@ -25007,7 +25007,7 @@
       <c r="AH647" s="6"/>
       <c r="AI647" s="6"/>
     </row>
-    <row r="648" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A648" s="6"/>
       <c r="B648" s="6"/>
       <c r="C648" s="6"/>
@@ -25044,7 +25044,7 @@
       <c r="AH648" s="6"/>
       <c r="AI648" s="6"/>
     </row>
-    <row r="649" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A649" s="6"/>
       <c r="B649" s="6"/>
       <c r="C649" s="6"/>
@@ -25081,7 +25081,7 @@
       <c r="AH649" s="6"/>
       <c r="AI649" s="6"/>
     </row>
-    <row r="650" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A650" s="6"/>
       <c r="B650" s="6"/>
       <c r="C650" s="6"/>
@@ -25118,7 +25118,7 @@
       <c r="AH650" s="6"/>
       <c r="AI650" s="6"/>
     </row>
-    <row r="651" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A651" s="6"/>
       <c r="B651" s="6"/>
       <c r="C651" s="6"/>
@@ -25155,7 +25155,7 @@
       <c r="AH651" s="6"/>
       <c r="AI651" s="6"/>
     </row>
-    <row r="652" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A652" s="6"/>
       <c r="B652" s="6"/>
       <c r="C652" s="6"/>
@@ -25192,7 +25192,7 @@
       <c r="AH652" s="6"/>
       <c r="AI652" s="6"/>
     </row>
-    <row r="653" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A653" s="6"/>
       <c r="B653" s="6"/>
       <c r="C653" s="6"/>
@@ -25229,7 +25229,7 @@
       <c r="AH653" s="6"/>
       <c r="AI653" s="6"/>
     </row>
-    <row r="654" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A654" s="6"/>
       <c r="B654" s="6"/>
       <c r="C654" s="6"/>
@@ -25266,7 +25266,7 @@
       <c r="AH654" s="6"/>
       <c r="AI654" s="6"/>
     </row>
-    <row r="655" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A655" s="6"/>
       <c r="B655" s="6"/>
       <c r="C655" s="6"/>
@@ -25303,7 +25303,7 @@
       <c r="AH655" s="6"/>
       <c r="AI655" s="6"/>
     </row>
-    <row r="656" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A656" s="6"/>
       <c r="B656" s="6"/>
       <c r="C656" s="6"/>
@@ -25340,7 +25340,7 @@
       <c r="AH656" s="6"/>
       <c r="AI656" s="6"/>
     </row>
-    <row r="657" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A657" s="6"/>
       <c r="B657" s="6"/>
       <c r="C657" s="6"/>
@@ -25377,7 +25377,7 @@
       <c r="AH657" s="6"/>
       <c r="AI657" s="6"/>
     </row>
-    <row r="658" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A658" s="6"/>
       <c r="B658" s="6"/>
       <c r="C658" s="6"/>
@@ -25414,7 +25414,7 @@
       <c r="AH658" s="6"/>
       <c r="AI658" s="6"/>
     </row>
-    <row r="659" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A659" s="6"/>
       <c r="B659" s="6"/>
       <c r="C659" s="6"/>
@@ -25451,7 +25451,7 @@
       <c r="AH659" s="6"/>
       <c r="AI659" s="6"/>
     </row>
-    <row r="660" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A660" s="6"/>
       <c r="B660" s="6"/>
       <c r="C660" s="6"/>
@@ -25488,7 +25488,7 @@
       <c r="AH660" s="6"/>
       <c r="AI660" s="6"/>
     </row>
-    <row r="661" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A661" s="6"/>
       <c r="B661" s="6"/>
       <c r="C661" s="6"/>
@@ -25525,7 +25525,7 @@
       <c r="AH661" s="6"/>
       <c r="AI661" s="6"/>
     </row>
-    <row r="662" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A662" s="6"/>
       <c r="B662" s="6"/>
       <c r="C662" s="6"/>
@@ -25562,7 +25562,7 @@
       <c r="AH662" s="6"/>
       <c r="AI662" s="6"/>
     </row>
-    <row r="663" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A663" s="6"/>
       <c r="B663" s="6"/>
       <c r="C663" s="6"/>
@@ -25599,7 +25599,7 @@
       <c r="AH663" s="6"/>
       <c r="AI663" s="6"/>
     </row>
-    <row r="664" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A664" s="6"/>
       <c r="B664" s="6"/>
       <c r="C664" s="6"/>
@@ -25636,7 +25636,7 @@
       <c r="AH664" s="6"/>
       <c r="AI664" s="6"/>
     </row>
-    <row r="665" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A665" s="6"/>
       <c r="B665" s="6"/>
       <c r="C665" s="6"/>
@@ -25673,7 +25673,7 @@
       <c r="AH665" s="6"/>
       <c r="AI665" s="6"/>
     </row>
-    <row r="666" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A666" s="6"/>
       <c r="B666" s="6"/>
       <c r="C666" s="6"/>
@@ -25710,7 +25710,7 @@
       <c r="AH666" s="6"/>
       <c r="AI666" s="6"/>
     </row>
-    <row r="667" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A667" s="6"/>
       <c r="B667" s="6"/>
       <c r="C667" s="6"/>
@@ -25747,7 +25747,7 @@
       <c r="AH667" s="6"/>
       <c r="AI667" s="6"/>
     </row>
-    <row r="668" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A668" s="6"/>
       <c r="B668" s="6"/>
       <c r="C668" s="6"/>
@@ -25784,7 +25784,7 @@
       <c r="AH668" s="6"/>
       <c r="AI668" s="6"/>
     </row>
-    <row r="669" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A669" s="6"/>
       <c r="B669" s="6"/>
       <c r="C669" s="6"/>
@@ -25821,7 +25821,7 @@
       <c r="AH669" s="6"/>
       <c r="AI669" s="6"/>
     </row>
-    <row r="670" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A670" s="6"/>
       <c r="B670" s="6"/>
       <c r="C670" s="6"/>
@@ -25858,7 +25858,7 @@
       <c r="AH670" s="6"/>
       <c r="AI670" s="6"/>
     </row>
-    <row r="671" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A671" s="6"/>
       <c r="B671" s="6"/>
       <c r="C671" s="6"/>
@@ -25895,7 +25895,7 @@
       <c r="AH671" s="6"/>
       <c r="AI671" s="6"/>
     </row>
-    <row r="672" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A672" s="6"/>
       <c r="B672" s="6"/>
       <c r="C672" s="6"/>
@@ -25932,7 +25932,7 @@
       <c r="AH672" s="6"/>
       <c r="AI672" s="6"/>
     </row>
-    <row r="673" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A673" s="6"/>
       <c r="B673" s="6"/>
       <c r="C673" s="6"/>
@@ -25969,7 +25969,7 @@
       <c r="AH673" s="6"/>
       <c r="AI673" s="6"/>
     </row>
-    <row r="674" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A674" s="6"/>
       <c r="B674" s="6"/>
       <c r="C674" s="6"/>
@@ -26006,7 +26006,7 @@
       <c r="AH674" s="6"/>
       <c r="AI674" s="6"/>
     </row>
-    <row r="675" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A675" s="6"/>
       <c r="B675" s="6"/>
       <c r="C675" s="6"/>
@@ -26043,7 +26043,7 @@
       <c r="AH675" s="6"/>
       <c r="AI675" s="6"/>
     </row>
-    <row r="676" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A676" s="6"/>
       <c r="B676" s="6"/>
       <c r="C676" s="6"/>
@@ -26080,7 +26080,7 @@
       <c r="AH676" s="6"/>
       <c r="AI676" s="6"/>
     </row>
-    <row r="677" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A677" s="6"/>
       <c r="B677" s="6"/>
       <c r="C677" s="6"/>
@@ -26117,7 +26117,7 @@
       <c r="AH677" s="6"/>
       <c r="AI677" s="6"/>
     </row>
-    <row r="678" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A678" s="6"/>
       <c r="B678" s="6"/>
       <c r="C678" s="6"/>
@@ -26154,7 +26154,7 @@
       <c r="AH678" s="6"/>
       <c r="AI678" s="6"/>
     </row>
-    <row r="679" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A679" s="6"/>
       <c r="B679" s="6"/>
       <c r="C679" s="6"/>
@@ -26191,7 +26191,7 @@
       <c r="AH679" s="6"/>
       <c r="AI679" s="6"/>
     </row>
-    <row r="680" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A680" s="6"/>
       <c r="B680" s="6"/>
       <c r="C680" s="6"/>
@@ -26228,7 +26228,7 @@
       <c r="AH680" s="6"/>
       <c r="AI680" s="6"/>
     </row>
-    <row r="681" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A681" s="6"/>
       <c r="B681" s="6"/>
       <c r="C681" s="6"/>
@@ -26265,7 +26265,7 @@
       <c r="AH681" s="6"/>
       <c r="AI681" s="6"/>
     </row>
-    <row r="682" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A682" s="6"/>
       <c r="B682" s="6"/>
       <c r="C682" s="6"/>
@@ -26302,7 +26302,7 @@
       <c r="AH682" s="6"/>
       <c r="AI682" s="6"/>
     </row>
-    <row r="683" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A683" s="6"/>
       <c r="B683" s="6"/>
       <c r="C683" s="6"/>
@@ -26339,7 +26339,7 @@
       <c r="AH683" s="6"/>
       <c r="AI683" s="6"/>
     </row>
-    <row r="684" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A684" s="6"/>
       <c r="B684" s="6"/>
       <c r="C684" s="6"/>
@@ -26376,7 +26376,7 @@
       <c r="AH684" s="6"/>
       <c r="AI684" s="6"/>
     </row>
-    <row r="685" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A685" s="6"/>
       <c r="B685" s="6"/>
       <c r="C685" s="6"/>
@@ -26413,7 +26413,7 @@
       <c r="AH685" s="6"/>
       <c r="AI685" s="6"/>
     </row>
-    <row r="686" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A686" s="6"/>
       <c r="B686" s="6"/>
       <c r="C686" s="6"/>
@@ -26450,7 +26450,7 @@
       <c r="AH686" s="6"/>
       <c r="AI686" s="6"/>
     </row>
-    <row r="687" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A687" s="6"/>
       <c r="B687" s="6"/>
       <c r="C687" s="6"/>
@@ -26487,7 +26487,7 @@
       <c r="AH687" s="6"/>
       <c r="AI687" s="6"/>
     </row>
-    <row r="688" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A688" s="6"/>
       <c r="B688" s="6"/>
       <c r="C688" s="6"/>
@@ -26524,7 +26524,7 @@
       <c r="AH688" s="6"/>
       <c r="AI688" s="6"/>
     </row>
-    <row r="689" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A689" s="6"/>
       <c r="B689" s="6"/>
       <c r="C689" s="6"/>
@@ -26561,7 +26561,7 @@
       <c r="AH689" s="6"/>
       <c r="AI689" s="6"/>
     </row>
-    <row r="690" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A690" s="6"/>
       <c r="B690" s="6"/>
       <c r="C690" s="6"/>
@@ -26598,7 +26598,7 @@
       <c r="AH690" s="6"/>
       <c r="AI690" s="6"/>
     </row>
-    <row r="691" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A691" s="6"/>
       <c r="B691" s="6"/>
       <c r="C691" s="6"/>
@@ -26635,7 +26635,7 @@
       <c r="AH691" s="6"/>
       <c r="AI691" s="6"/>
     </row>
-    <row r="692" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A692" s="6"/>
       <c r="B692" s="6"/>
       <c r="C692" s="6"/>
@@ -26672,7 +26672,7 @@
       <c r="AH692" s="6"/>
       <c r="AI692" s="6"/>
     </row>
-    <row r="693" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A693" s="6"/>
       <c r="B693" s="6"/>
       <c r="C693" s="6"/>
@@ -26709,7 +26709,7 @@
       <c r="AH693" s="6"/>
       <c r="AI693" s="6"/>
     </row>
-    <row r="694" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A694" s="6"/>
       <c r="B694" s="6"/>
       <c r="C694" s="6"/>
@@ -26746,7 +26746,7 @@
       <c r="AH694" s="6"/>
       <c r="AI694" s="6"/>
     </row>
-    <row r="695" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A695" s="6"/>
       <c r="B695" s="6"/>
       <c r="C695" s="6"/>
@@ -26783,7 +26783,7 @@
       <c r="AH695" s="6"/>
       <c r="AI695" s="6"/>
     </row>
-    <row r="696" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A696" s="6"/>
       <c r="B696" s="6"/>
       <c r="C696" s="6"/>
@@ -26820,7 +26820,7 @@
       <c r="AH696" s="6"/>
       <c r="AI696" s="6"/>
     </row>
-    <row r="697" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A697" s="6"/>
       <c r="B697" s="6"/>
       <c r="C697" s="6"/>
@@ -26857,7 +26857,7 @@
       <c r="AH697" s="6"/>
       <c r="AI697" s="6"/>
     </row>
-    <row r="698" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A698" s="6"/>
       <c r="B698" s="6"/>
       <c r="C698" s="6"/>
@@ -26894,7 +26894,7 @@
       <c r="AH698" s="6"/>
       <c r="AI698" s="6"/>
     </row>
-    <row r="699" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A699" s="6"/>
       <c r="B699" s="6"/>
       <c r="C699" s="6"/>
@@ -26931,7 +26931,7 @@
       <c r="AH699" s="6"/>
       <c r="AI699" s="6"/>
     </row>
-    <row r="700" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A700" s="6"/>
       <c r="B700" s="6"/>
       <c r="C700" s="6"/>
@@ -26968,7 +26968,7 @@
       <c r="AH700" s="6"/>
       <c r="AI700" s="6"/>
     </row>
-    <row r="701" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A701" s="6"/>
       <c r="B701" s="6"/>
       <c r="C701" s="6"/>
@@ -27005,7 +27005,7 @@
       <c r="AH701" s="6"/>
       <c r="AI701" s="6"/>
     </row>
-    <row r="702" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A702" s="6"/>
       <c r="B702" s="6"/>
       <c r="C702" s="6"/>
@@ -27042,7 +27042,7 @@
       <c r="AH702" s="6"/>
       <c r="AI702" s="6"/>
     </row>
-    <row r="703" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A703" s="6"/>
       <c r="B703" s="6"/>
       <c r="C703" s="6"/>
@@ -27079,7 +27079,7 @@
       <c r="AH703" s="6"/>
       <c r="AI703" s="6"/>
     </row>
-    <row r="704" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A704" s="6"/>
       <c r="B704" s="6"/>
       <c r="C704" s="6"/>
@@ -27116,7 +27116,7 @@
       <c r="AH704" s="6"/>
       <c r="AI704" s="6"/>
     </row>
-    <row r="705" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A705" s="6"/>
       <c r="B705" s="6"/>
       <c r="C705" s="6"/>
@@ -27153,7 +27153,7 @@
       <c r="AH705" s="6"/>
       <c r="AI705" s="6"/>
     </row>
-    <row r="706" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A706" s="6"/>
       <c r="B706" s="6"/>
       <c r="C706" s="6"/>
@@ -27190,7 +27190,7 @@
       <c r="AH706" s="6"/>
       <c r="AI706" s="6"/>
     </row>
-    <row r="707" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A707" s="6"/>
       <c r="B707" s="6"/>
       <c r="C707" s="6"/>
@@ -27227,7 +27227,7 @@
       <c r="AH707" s="6"/>
       <c r="AI707" s="6"/>
     </row>
-    <row r="708" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A708" s="6"/>
       <c r="B708" s="6"/>
       <c r="C708" s="6"/>
@@ -27264,7 +27264,7 @@
       <c r="AH708" s="6"/>
       <c r="AI708" s="6"/>
     </row>
-    <row r="709" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A709" s="6"/>
       <c r="B709" s="6"/>
       <c r="C709" s="6"/>
@@ -27301,7 +27301,7 @@
       <c r="AH709" s="6"/>
       <c r="AI709" s="6"/>
     </row>
-    <row r="710" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A710" s="6"/>
       <c r="B710" s="6"/>
       <c r="C710" s="6"/>
@@ -27338,7 +27338,7 @@
       <c r="AH710" s="6"/>
       <c r="AI710" s="6"/>
     </row>
-    <row r="711" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A711" s="6"/>
       <c r="B711" s="6"/>
       <c r="C711" s="6"/>
@@ -27375,7 +27375,7 @@
       <c r="AH711" s="6"/>
       <c r="AI711" s="6"/>
     </row>
-    <row r="712" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A712" s="6"/>
       <c r="B712" s="6"/>
       <c r="C712" s="6"/>
@@ -27412,7 +27412,7 @@
       <c r="AH712" s="6"/>
       <c r="AI712" s="6"/>
     </row>
-    <row r="713" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A713" s="6"/>
       <c r="B713" s="6"/>
       <c r="C713" s="6"/>
@@ -27449,7 +27449,7 @@
       <c r="AH713" s="6"/>
       <c r="AI713" s="6"/>
     </row>
-    <row r="714" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A714" s="6"/>
       <c r="B714" s="6"/>
       <c r="C714" s="6"/>
@@ -27486,7 +27486,7 @@
       <c r="AH714" s="6"/>
       <c r="AI714" s="6"/>
     </row>
-    <row r="715" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A715" s="6"/>
       <c r="B715" s="6"/>
       <c r="C715" s="6"/>
@@ -27523,7 +27523,7 @@
       <c r="AH715" s="6"/>
       <c r="AI715" s="6"/>
     </row>
-    <row r="716" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A716" s="6"/>
       <c r="B716" s="6"/>
       <c r="C716" s="6"/>
@@ -27560,7 +27560,7 @@
       <c r="AH716" s="6"/>
       <c r="AI716" s="6"/>
     </row>
-    <row r="717" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A717" s="6"/>
       <c r="B717" s="6"/>
       <c r="C717" s="6"/>
@@ -27597,7 +27597,7 @@
       <c r="AH717" s="6"/>
       <c r="AI717" s="6"/>
     </row>
-    <row r="718" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A718" s="6"/>
       <c r="B718" s="6"/>
       <c r="C718" s="6"/>
@@ -27634,7 +27634,7 @@
       <c r="AH718" s="6"/>
       <c r="AI718" s="6"/>
     </row>
-    <row r="719" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A719" s="6"/>
       <c r="B719" s="6"/>
       <c r="C719" s="6"/>
@@ -27671,7 +27671,7 @@
       <c r="AH719" s="6"/>
       <c r="AI719" s="6"/>
     </row>
-    <row r="720" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A720" s="6"/>
       <c r="B720" s="6"/>
       <c r="C720" s="6"/>
@@ -27708,7 +27708,7 @@
       <c r="AH720" s="6"/>
       <c r="AI720" s="6"/>
     </row>
-    <row r="721" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A721" s="6"/>
       <c r="B721" s="6"/>
       <c r="C721" s="6"/>
@@ -27745,7 +27745,7 @@
       <c r="AH721" s="6"/>
       <c r="AI721" s="6"/>
     </row>
-    <row r="722" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A722" s="6"/>
       <c r="B722" s="6"/>
       <c r="C722" s="6"/>
@@ -27782,7 +27782,7 @@
       <c r="AH722" s="6"/>
       <c r="AI722" s="6"/>
     </row>
-    <row r="723" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A723" s="6"/>
       <c r="B723" s="6"/>
       <c r="C723" s="6"/>
@@ -27819,7 +27819,7 @@
       <c r="AH723" s="6"/>
       <c r="AI723" s="6"/>
     </row>
-    <row r="724" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A724" s="6"/>
       <c r="B724" s="6"/>
       <c r="C724" s="6"/>
@@ -27856,7 +27856,7 @@
       <c r="AH724" s="6"/>
       <c r="AI724" s="6"/>
     </row>
-    <row r="725" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A725" s="6"/>
       <c r="B725" s="6"/>
       <c r="C725" s="6"/>
@@ -27893,7 +27893,7 @@
       <c r="AH725" s="6"/>
       <c r="AI725" s="6"/>
     </row>
-    <row r="726" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A726" s="6"/>
       <c r="B726" s="6"/>
       <c r="C726" s="6"/>
@@ -27930,7 +27930,7 @@
       <c r="AH726" s="6"/>
       <c r="AI726" s="6"/>
     </row>
-    <row r="727" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A727" s="6"/>
       <c r="B727" s="6"/>
       <c r="C727" s="6"/>
@@ -27967,7 +27967,7 @@
       <c r="AH727" s="6"/>
       <c r="AI727" s="6"/>
     </row>
-    <row r="728" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A728" s="6"/>
       <c r="B728" s="6"/>
       <c r="C728" s="6"/>
@@ -28004,7 +28004,7 @@
       <c r="AH728" s="6"/>
       <c r="AI728" s="6"/>
     </row>
-    <row r="729" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A729" s="6"/>
       <c r="B729" s="6"/>
       <c r="C729" s="6"/>
@@ -28041,7 +28041,7 @@
       <c r="AH729" s="6"/>
       <c r="AI729" s="6"/>
     </row>
-    <row r="730" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A730" s="6"/>
       <c r="B730" s="6"/>
       <c r="C730" s="6"/>
@@ -28078,7 +28078,7 @@
       <c r="AH730" s="6"/>
       <c r="AI730" s="6"/>
     </row>
-    <row r="731" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A731" s="6"/>
       <c r="B731" s="6"/>
       <c r="C731" s="6"/>
@@ -28115,7 +28115,7 @@
       <c r="AH731" s="6"/>
       <c r="AI731" s="6"/>
     </row>
-    <row r="732" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A732" s="6"/>
       <c r="B732" s="6"/>
       <c r="C732" s="6"/>
@@ -28152,7 +28152,7 @@
       <c r="AH732" s="6"/>
       <c r="AI732" s="6"/>
     </row>
-    <row r="733" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A733" s="6"/>
       <c r="B733" s="6"/>
       <c r="C733" s="6"/>
@@ -28189,7 +28189,7 @@
       <c r="AH733" s="6"/>
       <c r="AI733" s="6"/>
     </row>
-    <row r="734" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A734" s="6"/>
       <c r="B734" s="6"/>
       <c r="C734" s="6"/>
@@ -28226,7 +28226,7 @@
       <c r="AH734" s="6"/>
       <c r="AI734" s="6"/>
     </row>
-    <row r="735" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A735" s="6"/>
       <c r="B735" s="6"/>
       <c r="C735" s="6"/>
@@ -28263,7 +28263,7 @@
       <c r="AH735" s="6"/>
       <c r="AI735" s="6"/>
     </row>
-    <row r="736" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A736" s="6"/>
       <c r="B736" s="6"/>
       <c r="C736" s="6"/>
@@ -28300,7 +28300,7 @@
       <c r="AH736" s="6"/>
       <c r="AI736" s="6"/>
     </row>
-    <row r="737" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A737" s="6"/>
       <c r="B737" s="6"/>
       <c r="C737" s="6"/>
@@ -28337,7 +28337,7 @@
       <c r="AH737" s="6"/>
       <c r="AI737" s="6"/>
     </row>
-    <row r="738" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A738" s="6"/>
       <c r="B738" s="6"/>
       <c r="C738" s="6"/>
@@ -28374,7 +28374,7 @@
       <c r="AH738" s="6"/>
       <c r="AI738" s="6"/>
     </row>
-    <row r="739" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A739" s="6"/>
       <c r="B739" s="6"/>
       <c r="C739" s="6"/>
@@ -28411,7 +28411,7 @@
       <c r="AH739" s="6"/>
       <c r="AI739" s="6"/>
     </row>
-    <row r="740" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A740" s="6"/>
       <c r="B740" s="6"/>
       <c r="C740" s="6"/>
@@ -28448,7 +28448,7 @@
       <c r="AH740" s="6"/>
       <c r="AI740" s="6"/>
     </row>
-    <row r="741" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A741" s="6"/>
       <c r="B741" s="6"/>
       <c r="C741" s="6"/>
@@ -28485,7 +28485,7 @@
       <c r="AH741" s="6"/>
       <c r="AI741" s="6"/>
     </row>
-    <row r="742" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A742" s="6"/>
       <c r="B742" s="6"/>
       <c r="C742" s="6"/>
@@ -28522,7 +28522,7 @@
       <c r="AH742" s="6"/>
       <c r="AI742" s="6"/>
     </row>
-    <row r="743" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A743" s="6"/>
       <c r="B743" s="6"/>
       <c r="C743" s="6"/>
@@ -28559,7 +28559,7 @@
       <c r="AH743" s="6"/>
       <c r="AI743" s="6"/>
     </row>
-    <row r="744" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A744" s="6"/>
       <c r="B744" s="6"/>
       <c r="C744" s="6"/>
@@ -28596,7 +28596,7 @@
       <c r="AH744" s="6"/>
       <c r="AI744" s="6"/>
     </row>
-    <row r="745" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A745" s="6"/>
       <c r="B745" s="6"/>
       <c r="C745" s="6"/>
@@ -28633,7 +28633,7 @@
       <c r="AH745" s="6"/>
       <c r="AI745" s="6"/>
     </row>
-    <row r="746" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A746" s="6"/>
       <c r="B746" s="6"/>
       <c r="C746" s="6"/>
@@ -28670,7 +28670,7 @@
       <c r="AH746" s="6"/>
       <c r="AI746" s="6"/>
     </row>
-    <row r="747" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A747" s="6"/>
       <c r="B747" s="6"/>
       <c r="C747" s="6"/>
@@ -28707,7 +28707,7 @@
       <c r="AH747" s="6"/>
       <c r="AI747" s="6"/>
     </row>
-    <row r="748" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A748" s="6"/>
       <c r="B748" s="6"/>
       <c r="C748" s="6"/>
@@ -28744,7 +28744,7 @@
       <c r="AH748" s="6"/>
       <c r="AI748" s="6"/>
     </row>
-    <row r="749" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A749" s="6"/>
       <c r="B749" s="6"/>
       <c r="C749" s="6"/>
@@ -28781,7 +28781,7 @@
       <c r="AH749" s="6"/>
       <c r="AI749" s="6"/>
     </row>
-    <row r="750" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A750" s="6"/>
       <c r="B750" s="6"/>
       <c r="C750" s="6"/>
@@ -28818,7 +28818,7 @@
       <c r="AH750" s="6"/>
       <c r="AI750" s="6"/>
     </row>
-    <row r="751" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A751" s="6"/>
       <c r="B751" s="6"/>
       <c r="C751" s="6"/>
@@ -28855,7 +28855,7 @@
       <c r="AH751" s="6"/>
       <c r="AI751" s="6"/>
     </row>
-    <row r="752" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A752" s="6"/>
       <c r="B752" s="6"/>
       <c r="C752" s="6"/>
@@ -28892,7 +28892,7 @@
       <c r="AH752" s="6"/>
       <c r="AI752" s="6"/>
     </row>
-    <row r="753" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A753" s="6"/>
       <c r="B753" s="6"/>
       <c r="C753" s="6"/>
@@ -28929,7 +28929,7 @@
       <c r="AH753" s="6"/>
       <c r="AI753" s="6"/>
     </row>
-    <row r="754" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A754" s="6"/>
       <c r="B754" s="6"/>
       <c r="C754" s="6"/>
@@ -28966,7 +28966,7 @@
       <c r="AH754" s="6"/>
       <c r="AI754" s="6"/>
     </row>
-    <row r="755" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A755" s="6"/>
       <c r="B755" s="6"/>
       <c r="C755" s="6"/>
@@ -29003,7 +29003,7 @@
       <c r="AH755" s="6"/>
       <c r="AI755" s="6"/>
     </row>
-    <row r="756" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A756" s="6"/>
       <c r="B756" s="6"/>
       <c r="C756" s="6"/>
@@ -29040,7 +29040,7 @@
       <c r="AH756" s="6"/>
       <c r="AI756" s="6"/>
     </row>
-    <row r="757" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A757" s="6"/>
       <c r="B757" s="6"/>
       <c r="C757" s="6"/>
@@ -29077,7 +29077,7 @@
       <c r="AH757" s="6"/>
       <c r="AI757" s="6"/>
     </row>
-    <row r="758" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A758" s="6"/>
       <c r="B758" s="6"/>
       <c r="C758" s="6"/>
@@ -29114,7 +29114,7 @@
       <c r="AH758" s="6"/>
       <c r="AI758" s="6"/>
     </row>
-    <row r="759" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A759" s="6"/>
       <c r="B759" s="6"/>
       <c r="C759" s="6"/>
@@ -29151,7 +29151,7 @@
       <c r="AH759" s="6"/>
       <c r="AI759" s="6"/>
     </row>
-    <row r="760" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A760" s="6"/>
       <c r="B760" s="6"/>
       <c r="C760" s="6"/>
@@ -29188,7 +29188,7 @@
       <c r="AH760" s="6"/>
       <c r="AI760" s="6"/>
     </row>
-    <row r="761" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A761" s="6"/>
       <c r="B761" s="6"/>
       <c r="C761" s="6"/>
@@ -29225,7 +29225,7 @@
       <c r="AH761" s="6"/>
       <c r="AI761" s="6"/>
     </row>
-    <row r="762" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A762" s="6"/>
       <c r="B762" s="6"/>
       <c r="C762" s="6"/>
@@ -29262,7 +29262,7 @@
       <c r="AH762" s="6"/>
       <c r="AI762" s="6"/>
     </row>
-    <row r="763" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A763" s="6"/>
       <c r="B763" s="6"/>
       <c r="C763" s="6"/>
@@ -29299,7 +29299,7 @@
       <c r="AH763" s="6"/>
       <c r="AI763" s="6"/>
     </row>
-    <row r="764" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A764" s="6"/>
       <c r="B764" s="6"/>
       <c r="C764" s="6"/>
@@ -29336,7 +29336,7 @@
       <c r="AH764" s="6"/>
       <c r="AI764" s="6"/>
     </row>
-    <row r="765" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A765" s="6"/>
       <c r="B765" s="6"/>
       <c r="C765" s="6"/>
@@ -29373,7 +29373,7 @@
       <c r="AH765" s="6"/>
       <c r="AI765" s="6"/>
     </row>
-    <row r="766" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A766" s="6"/>
       <c r="B766" s="6"/>
       <c r="C766" s="6"/>
@@ -29410,7 +29410,7 @@
       <c r="AH766" s="6"/>
       <c r="AI766" s="6"/>
     </row>
-    <row r="767" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A767" s="6"/>
       <c r="B767" s="6"/>
       <c r="C767" s="6"/>
@@ -29447,7 +29447,7 @@
       <c r="AH767" s="6"/>
       <c r="AI767" s="6"/>
     </row>
-    <row r="768" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A768" s="6"/>
       <c r="B768" s="6"/>
       <c r="C768" s="6"/>
@@ -29484,7 +29484,7 @@
       <c r="AH768" s="6"/>
       <c r="AI768" s="6"/>
     </row>
-    <row r="769" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A769" s="6"/>
       <c r="B769" s="6"/>
       <c r="C769" s="6"/>
@@ -29521,7 +29521,7 @@
       <c r="AH769" s="6"/>
       <c r="AI769" s="6"/>
     </row>
-    <row r="770" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A770" s="6"/>
       <c r="B770" s="6"/>
       <c r="C770" s="6"/>
@@ -29558,7 +29558,7 @@
       <c r="AH770" s="6"/>
       <c r="AI770" s="6"/>
     </row>
-    <row r="771" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A771" s="6"/>
       <c r="B771" s="6"/>
       <c r="C771" s="6"/>
@@ -29595,7 +29595,7 @@
       <c r="AH771" s="6"/>
       <c r="AI771" s="6"/>
     </row>
-    <row r="772" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A772" s="6"/>
       <c r="B772" s="6"/>
       <c r="C772" s="6"/>
@@ -29632,7 +29632,7 @@
       <c r="AH772" s="6"/>
       <c r="AI772" s="6"/>
     </row>
-    <row r="773" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A773" s="6"/>
       <c r="B773" s="6"/>
       <c r="C773" s="6"/>
@@ -29669,7 +29669,7 @@
       <c r="AH773" s="6"/>
       <c r="AI773" s="6"/>
     </row>
-    <row r="774" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A774" s="6"/>
       <c r="B774" s="6"/>
       <c r="C774" s="6"/>
@@ -29706,7 +29706,7 @@
       <c r="AH774" s="6"/>
       <c r="AI774" s="6"/>
     </row>
-    <row r="775" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A775" s="6"/>
       <c r="B775" s="6"/>
       <c r="C775" s="6"/>
@@ -29743,7 +29743,7 @@
       <c r="AH775" s="6"/>
       <c r="AI775" s="6"/>
     </row>
-    <row r="776" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A776" s="6"/>
       <c r="B776" s="6"/>
       <c r="C776" s="6"/>
@@ -29780,7 +29780,7 @@
       <c r="AH776" s="6"/>
       <c r="AI776" s="6"/>
     </row>
-    <row r="777" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A777" s="6"/>
       <c r="B777" s="6"/>
       <c r="C777" s="6"/>
@@ -29817,7 +29817,7 @@
       <c r="AH777" s="6"/>
       <c r="AI777" s="6"/>
     </row>
-    <row r="778" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A778" s="6"/>
       <c r="B778" s="6"/>
       <c r="C778" s="6"/>
@@ -29854,7 +29854,7 @@
       <c r="AH778" s="6"/>
       <c r="AI778" s="6"/>
     </row>
-    <row r="779" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A779" s="6"/>
       <c r="B779" s="6"/>
       <c r="C779" s="6"/>
@@ -29891,7 +29891,7 @@
       <c r="AH779" s="6"/>
       <c r="AI779" s="6"/>
     </row>
-    <row r="780" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A780" s="6"/>
       <c r="B780" s="6"/>
       <c r="C780" s="6"/>
@@ -29928,7 +29928,7 @@
       <c r="AH780" s="6"/>
       <c r="AI780" s="6"/>
     </row>
-    <row r="781" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A781" s="6"/>
       <c r="B781" s="6"/>
       <c r="C781" s="6"/>
@@ -29965,7 +29965,7 @@
       <c r="AH781" s="6"/>
       <c r="AI781" s="6"/>
     </row>
-    <row r="782" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A782" s="6"/>
       <c r="B782" s="6"/>
       <c r="C782" s="6"/>
@@ -30002,7 +30002,7 @@
       <c r="AH782" s="6"/>
       <c r="AI782" s="6"/>
     </row>
-    <row r="783" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A783" s="6"/>
       <c r="B783" s="6"/>
       <c r="C783" s="6"/>
@@ -30039,7 +30039,7 @@
       <c r="AH783" s="6"/>
       <c r="AI783" s="6"/>
     </row>
-    <row r="784" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A784" s="6"/>
       <c r="B784" s="6"/>
       <c r="C784" s="6"/>
@@ -30076,7 +30076,7 @@
       <c r="AH784" s="6"/>
       <c r="AI784" s="6"/>
     </row>
-    <row r="785" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A785" s="6"/>
       <c r="B785" s="6"/>
       <c r="C785" s="6"/>
@@ -30113,7 +30113,7 @@
       <c r="AH785" s="6"/>
       <c r="AI785" s="6"/>
     </row>
-    <row r="786" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A786" s="6"/>
       <c r="B786" s="6"/>
       <c r="C786" s="6"/>
@@ -30150,7 +30150,7 @@
       <c r="AH786" s="6"/>
       <c r="AI786" s="6"/>
     </row>
-    <row r="787" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A787" s="6"/>
       <c r="B787" s="6"/>
       <c r="C787" s="6"/>
@@ -30187,7 +30187,7 @@
       <c r="AH787" s="6"/>
       <c r="AI787" s="6"/>
     </row>
-    <row r="788" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A788" s="6"/>
       <c r="B788" s="6"/>
       <c r="C788" s="6"/>
@@ -30224,7 +30224,7 @@
       <c r="AH788" s="6"/>
       <c r="AI788" s="6"/>
     </row>
-    <row r="789" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A789" s="6"/>
       <c r="B789" s="6"/>
       <c r="C789" s="6"/>
@@ -30261,7 +30261,7 @@
       <c r="AH789" s="6"/>
       <c r="AI789" s="6"/>
     </row>
-    <row r="790" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A790" s="6"/>
       <c r="B790" s="6"/>
       <c r="C790" s="6"/>
@@ -30298,7 +30298,7 @@
       <c r="AH790" s="6"/>
       <c r="AI790" s="6"/>
     </row>
-    <row r="791" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A791" s="6"/>
       <c r="B791" s="6"/>
       <c r="C791" s="6"/>
@@ -30335,7 +30335,7 @@
       <c r="AH791" s="6"/>
       <c r="AI791" s="6"/>
     </row>
-    <row r="792" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A792" s="6"/>
       <c r="B792" s="6"/>
       <c r="C792" s="6"/>
@@ -30372,7 +30372,7 @@
       <c r="AH792" s="6"/>
       <c r="AI792" s="6"/>
     </row>
-    <row r="793" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A793" s="6"/>
       <c r="B793" s="6"/>
       <c r="C793" s="6"/>
@@ -30409,7 +30409,7 @@
       <c r="AH793" s="6"/>
       <c r="AI793" s="6"/>
     </row>
-    <row r="794" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A794" s="6"/>
       <c r="B794" s="6"/>
       <c r="C794" s="6"/>
@@ -30446,7 +30446,7 @@
       <c r="AH794" s="6"/>
       <c r="AI794" s="6"/>
     </row>
-    <row r="795" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A795" s="6"/>
       <c r="B795" s="6"/>
       <c r="C795" s="6"/>
@@ -30483,7 +30483,7 @@
       <c r="AH795" s="6"/>
       <c r="AI795" s="6"/>
     </row>
-    <row r="796" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A796" s="6"/>
       <c r="B796" s="6"/>
       <c r="C796" s="6"/>
@@ -30520,7 +30520,7 @@
       <c r="AH796" s="6"/>
       <c r="AI796" s="6"/>
     </row>
-    <row r="797" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A797" s="6"/>
       <c r="B797" s="6"/>
       <c r="C797" s="6"/>
@@ -30557,7 +30557,7 @@
       <c r="AH797" s="6"/>
       <c r="AI797" s="6"/>
     </row>
-    <row r="798" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A798" s="6"/>
       <c r="B798" s="6"/>
       <c r="C798" s="6"/>
@@ -30594,7 +30594,7 @@
       <c r="AH798" s="6"/>
       <c r="AI798" s="6"/>
     </row>
-    <row r="799" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A799" s="6"/>
       <c r="B799" s="6"/>
       <c r="C799" s="6"/>
@@ -30631,7 +30631,7 @@
       <c r="AH799" s="6"/>
       <c r="AI799" s="6"/>
     </row>
-    <row r="800" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A800" s="6"/>
       <c r="B800" s="6"/>
       <c r="C800" s="6"/>
@@ -30668,7 +30668,7 @@
       <c r="AH800" s="6"/>
       <c r="AI800" s="6"/>
     </row>
-    <row r="801" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A801" s="6"/>
       <c r="B801" s="6"/>
       <c r="C801" s="6"/>
@@ -30705,7 +30705,7 @@
       <c r="AH801" s="6"/>
       <c r="AI801" s="6"/>
     </row>
-    <row r="802" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A802" s="6"/>
       <c r="B802" s="6"/>
       <c r="C802" s="6"/>
@@ -30742,7 +30742,7 @@
       <c r="AH802" s="6"/>
       <c r="AI802" s="6"/>
     </row>
-    <row r="803" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A803" s="6"/>
       <c r="B803" s="6"/>
       <c r="C803" s="6"/>
@@ -30779,7 +30779,7 @@
       <c r="AH803" s="6"/>
       <c r="AI803" s="6"/>
     </row>
-    <row r="804" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A804" s="6"/>
       <c r="B804" s="6"/>
       <c r="C804" s="6"/>
@@ -30816,7 +30816,7 @@
       <c r="AH804" s="6"/>
       <c r="AI804" s="6"/>
     </row>
-    <row r="805" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A805" s="6"/>
       <c r="B805" s="6"/>
       <c r="C805" s="6"/>
@@ -30853,7 +30853,7 @@
       <c r="AH805" s="6"/>
       <c r="AI805" s="6"/>
     </row>
-    <row r="806" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A806" s="6"/>
       <c r="B806" s="6"/>
       <c r="C806" s="6"/>
@@ -30890,7 +30890,7 @@
       <c r="AH806" s="6"/>
       <c r="AI806" s="6"/>
     </row>
-    <row r="807" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A807" s="6"/>
       <c r="B807" s="6"/>
       <c r="C807" s="6"/>
@@ -30927,7 +30927,7 @@
       <c r="AH807" s="6"/>
       <c r="AI807" s="6"/>
     </row>
-    <row r="808" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A808" s="6"/>
       <c r="B808" s="6"/>
       <c r="C808" s="6"/>
@@ -30964,7 +30964,7 @@
       <c r="AH808" s="6"/>
       <c r="AI808" s="6"/>
     </row>
-    <row r="809" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A809" s="6"/>
       <c r="B809" s="6"/>
       <c r="C809" s="6"/>
@@ -31001,7 +31001,7 @@
       <c r="AH809" s="6"/>
       <c r="AI809" s="6"/>
     </row>
-    <row r="810" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A810" s="6"/>
       <c r="B810" s="6"/>
       <c r="C810" s="6"/>
@@ -31038,7 +31038,7 @@
       <c r="AH810" s="6"/>
       <c r="AI810" s="6"/>
     </row>
-    <row r="811" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A811" s="6"/>
       <c r="B811" s="6"/>
       <c r="C811" s="6"/>
@@ -31075,7 +31075,7 @@
       <c r="AH811" s="6"/>
       <c r="AI811" s="6"/>
     </row>
-    <row r="812" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A812" s="6"/>
       <c r="B812" s="6"/>
       <c r="C812" s="6"/>
@@ -31112,7 +31112,7 @@
       <c r="AH812" s="6"/>
       <c r="AI812" s="6"/>
     </row>
-    <row r="813" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A813" s="6"/>
       <c r="B813" s="6"/>
       <c r="C813" s="6"/>
@@ -31149,7 +31149,7 @@
       <c r="AH813" s="6"/>
       <c r="AI813" s="6"/>
     </row>
-    <row r="814" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A814" s="6"/>
       <c r="B814" s="6"/>
       <c r="C814" s="6"/>
@@ -31186,7 +31186,7 @@
       <c r="AH814" s="6"/>
       <c r="AI814" s="6"/>
     </row>
-    <row r="815" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A815" s="6"/>
       <c r="B815" s="6"/>
       <c r="C815" s="6"/>
@@ -31223,7 +31223,7 @@
       <c r="AH815" s="6"/>
       <c r="AI815" s="6"/>
     </row>
-    <row r="816" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A816" s="6"/>
       <c r="B816" s="6"/>
       <c r="C816" s="6"/>
@@ -31260,7 +31260,7 @@
       <c r="AH816" s="6"/>
       <c r="AI816" s="6"/>
     </row>
-    <row r="817" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A817" s="6"/>
       <c r="B817" s="6"/>
       <c r="C817" s="6"/>
@@ -31297,7 +31297,7 @@
       <c r="AH817" s="6"/>
       <c r="AI817" s="6"/>
     </row>
-    <row r="818" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A818" s="6"/>
       <c r="B818" s="6"/>
       <c r="C818" s="6"/>
@@ -31334,7 +31334,7 @@
       <c r="AH818" s="6"/>
       <c r="AI818" s="6"/>
     </row>
-    <row r="819" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A819" s="6"/>
       <c r="B819" s="6"/>
       <c r="C819" s="6"/>
@@ -31371,7 +31371,7 @@
       <c r="AH819" s="6"/>
       <c r="AI819" s="6"/>
     </row>
-    <row r="820" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A820" s="6"/>
       <c r="B820" s="6"/>
       <c r="C820" s="6"/>
@@ -31408,7 +31408,7 @@
       <c r="AH820" s="6"/>
       <c r="AI820" s="6"/>
     </row>
-    <row r="821" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A821" s="6"/>
       <c r="B821" s="6"/>
       <c r="C821" s="6"/>
@@ -31445,7 +31445,7 @@
       <c r="AH821" s="6"/>
       <c r="AI821" s="6"/>
     </row>
-    <row r="822" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A822" s="6"/>
       <c r="B822" s="6"/>
       <c r="C822" s="6"/>
@@ -31482,7 +31482,7 @@
       <c r="AH822" s="6"/>
       <c r="AI822" s="6"/>
     </row>
-    <row r="823" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A823" s="6"/>
       <c r="B823" s="6"/>
       <c r="C823" s="6"/>
@@ -31519,7 +31519,7 @@
       <c r="AH823" s="6"/>
       <c r="AI823" s="6"/>
     </row>
-    <row r="824" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A824" s="6"/>
       <c r="B824" s="6"/>
       <c r="C824" s="6"/>
@@ -31556,7 +31556,7 @@
       <c r="AH824" s="6"/>
       <c r="AI824" s="6"/>
     </row>
-    <row r="825" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A825" s="6"/>
       <c r="B825" s="6"/>
       <c r="C825" s="6"/>
@@ -31593,7 +31593,7 @@
       <c r="AH825" s="6"/>
       <c r="AI825" s="6"/>
     </row>
-    <row r="826" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A826" s="6"/>
       <c r="B826" s="6"/>
       <c r="C826" s="6"/>
@@ -31630,7 +31630,7 @@
       <c r="AH826" s="6"/>
       <c r="AI826" s="6"/>
     </row>
-    <row r="827" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A827" s="6"/>
       <c r="B827" s="6"/>
       <c r="C827" s="6"/>
@@ -31667,7 +31667,7 @@
       <c r="AH827" s="6"/>
       <c r="AI827" s="6"/>
     </row>
-    <row r="828" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A828" s="6"/>
       <c r="B828" s="6"/>
       <c r="C828" s="6"/>
@@ -31704,7 +31704,7 @@
       <c r="AH828" s="6"/>
       <c r="AI828" s="6"/>
     </row>
-    <row r="829" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A829" s="6"/>
       <c r="B829" s="6"/>
       <c r="C829" s="6"/>
@@ -31741,7 +31741,7 @@
       <c r="AH829" s="6"/>
       <c r="AI829" s="6"/>
     </row>
-    <row r="830" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A830" s="6"/>
       <c r="B830" s="6"/>
       <c r="C830" s="6"/>
@@ -31778,7 +31778,7 @@
       <c r="AH830" s="6"/>
       <c r="AI830" s="6"/>
     </row>
-    <row r="831" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A831" s="6"/>
       <c r="B831" s="6"/>
       <c r="C831" s="6"/>
@@ -31815,7 +31815,7 @@
       <c r="AH831" s="6"/>
       <c r="AI831" s="6"/>
     </row>
-    <row r="832" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A832" s="6"/>
       <c r="B832" s="6"/>
       <c r="C832" s="6"/>
@@ -31852,7 +31852,7 @@
       <c r="AH832" s="6"/>
       <c r="AI832" s="6"/>
     </row>
-    <row r="833" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A833" s="6"/>
       <c r="B833" s="6"/>
       <c r="C833" s="6"/>
@@ -31889,7 +31889,7 @@
       <c r="AH833" s="6"/>
       <c r="AI833" s="6"/>
     </row>
-    <row r="834" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A834" s="6"/>
       <c r="B834" s="6"/>
       <c r="C834" s="6"/>
@@ -31926,7 +31926,7 @@
       <c r="AH834" s="6"/>
       <c r="AI834" s="6"/>
     </row>
-    <row r="835" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A835" s="6"/>
       <c r="B835" s="6"/>
       <c r="C835" s="6"/>
@@ -31963,7 +31963,7 @@
       <c r="AH835" s="6"/>
       <c r="AI835" s="6"/>
     </row>
-    <row r="836" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A836" s="6"/>
       <c r="B836" s="6"/>
       <c r="C836" s="6"/>
@@ -32000,7 +32000,7 @@
       <c r="AH836" s="6"/>
       <c r="AI836" s="6"/>
     </row>
-    <row r="837" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A837" s="6"/>
       <c r="B837" s="6"/>
       <c r="C837" s="6"/>
@@ -32037,7 +32037,7 @@
       <c r="AH837" s="6"/>
       <c r="AI837" s="6"/>
     </row>
-    <row r="838" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A838" s="6"/>
       <c r="B838" s="6"/>
       <c r="C838" s="6"/>
@@ -32074,7 +32074,7 @@
       <c r="AH838" s="6"/>
       <c r="AI838" s="6"/>
     </row>
-    <row r="839" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A839" s="6"/>
       <c r="B839" s="6"/>
       <c r="C839" s="6"/>
@@ -32111,7 +32111,7 @@
       <c r="AH839" s="6"/>
       <c r="AI839" s="6"/>
     </row>
-    <row r="840" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A840" s="6"/>
       <c r="B840" s="6"/>
       <c r="C840" s="6"/>
@@ -32148,7 +32148,7 @@
       <c r="AH840" s="6"/>
       <c r="AI840" s="6"/>
     </row>
-    <row r="841" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A841" s="6"/>
       <c r="B841" s="6"/>
       <c r="C841" s="6"/>
@@ -32185,7 +32185,7 @@
       <c r="AH841" s="6"/>
       <c r="AI841" s="6"/>
     </row>
-    <row r="842" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A842" s="6"/>
       <c r="B842" s="6"/>
       <c r="C842" s="6"/>
@@ -32222,7 +32222,7 @@
       <c r="AH842" s="6"/>
       <c r="AI842" s="6"/>
     </row>
-    <row r="843" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A843" s="6"/>
       <c r="B843" s="6"/>
       <c r="C843" s="6"/>
@@ -32259,7 +32259,7 @@
       <c r="AH843" s="6"/>
       <c r="AI843" s="6"/>
     </row>
-    <row r="844" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A844" s="6"/>
       <c r="B844" s="6"/>
       <c r="C844" s="6"/>
@@ -32296,7 +32296,7 @@
       <c r="AH844" s="6"/>
       <c r="AI844" s="6"/>
     </row>
-    <row r="845" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A845" s="6"/>
       <c r="B845" s="6"/>
       <c r="C845" s="6"/>
@@ -32333,7 +32333,7 @@
       <c r="AH845" s="6"/>
       <c r="AI845" s="6"/>
     </row>
-    <row r="846" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A846" s="6"/>
       <c r="B846" s="6"/>
       <c r="C846" s="6"/>
@@ -32370,7 +32370,7 @@
       <c r="AH846" s="6"/>
       <c r="AI846" s="6"/>
     </row>
-    <row r="847" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A847" s="6"/>
       <c r="B847" s="6"/>
       <c r="C847" s="6"/>
@@ -32407,7 +32407,7 @@
       <c r="AH847" s="6"/>
       <c r="AI847" s="6"/>
     </row>
-    <row r="848" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A848" s="6"/>
       <c r="B848" s="6"/>
       <c r="C848" s="6"/>
@@ -32444,7 +32444,7 @@
       <c r="AH848" s="6"/>
       <c r="AI848" s="6"/>
     </row>
-    <row r="849" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A849" s="6"/>
       <c r="B849" s="6"/>
       <c r="C849" s="6"/>
@@ -32481,7 +32481,7 @@
       <c r="AH849" s="6"/>
       <c r="AI849" s="6"/>
     </row>
-    <row r="850" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A850" s="6"/>
       <c r="B850" s="6"/>
       <c r="C850" s="6"/>
@@ -32518,7 +32518,7 @@
       <c r="AH850" s="6"/>
       <c r="AI850" s="6"/>
     </row>
-    <row r="851" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A851" s="6"/>
       <c r="B851" s="6"/>
       <c r="C851" s="6"/>
@@ -32555,7 +32555,7 @@
       <c r="AH851" s="6"/>
       <c r="AI851" s="6"/>
     </row>
-    <row r="852" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A852" s="6"/>
       <c r="B852" s="6"/>
       <c r="C852" s="6"/>
@@ -32592,7 +32592,7 @@
       <c r="AH852" s="6"/>
       <c r="AI852" s="6"/>
     </row>
-    <row r="853" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A853" s="6"/>
       <c r="B853" s="6"/>
       <c r="C853" s="6"/>
@@ -32629,7 +32629,7 @@
       <c r="AH853" s="6"/>
       <c r="AI853" s="6"/>
     </row>
-    <row r="854" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A854" s="6"/>
       <c r="B854" s="6"/>
       <c r="C854" s="6"/>
@@ -32666,7 +32666,7 @@
       <c r="AH854" s="6"/>
       <c r="AI854" s="6"/>
     </row>
-    <row r="855" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A855" s="6"/>
       <c r="B855" s="6"/>
       <c r="C855" s="6"/>
@@ -32703,7 +32703,7 @@
       <c r="AH855" s="6"/>
       <c r="AI855" s="6"/>
     </row>
-    <row r="856" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A856" s="6"/>
       <c r="B856" s="6"/>
       <c r="C856" s="6"/>
@@ -32740,7 +32740,7 @@
       <c r="AH856" s="6"/>
       <c r="AI856" s="6"/>
     </row>
-    <row r="857" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A857" s="6"/>
       <c r="B857" s="6"/>
       <c r="C857" s="6"/>
@@ -32777,7 +32777,7 @@
       <c r="AH857" s="6"/>
       <c r="AI857" s="6"/>
     </row>
-    <row r="858" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A858" s="6"/>
       <c r="B858" s="6"/>
       <c r="C858" s="6"/>
@@ -32814,7 +32814,7 @@
       <c r="AH858" s="6"/>
       <c r="AI858" s="6"/>
     </row>
-    <row r="859" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A859" s="6"/>
       <c r="B859" s="6"/>
       <c r="C859" s="6"/>
@@ -32851,7 +32851,7 @@
       <c r="AH859" s="6"/>
       <c r="AI859" s="6"/>
     </row>
-    <row r="860" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A860" s="6"/>
       <c r="B860" s="6"/>
       <c r="C860" s="6"/>
@@ -32888,7 +32888,7 @@
       <c r="AH860" s="6"/>
       <c r="AI860" s="6"/>
     </row>
-    <row r="861" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A861" s="6"/>
       <c r="B861" s="6"/>
       <c r="C861" s="6"/>
@@ -32925,7 +32925,7 @@
       <c r="AH861" s="6"/>
       <c r="AI861" s="6"/>
     </row>
-    <row r="862" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A862" s="6"/>
       <c r="B862" s="6"/>
       <c r="C862" s="6"/>
@@ -32962,7 +32962,7 @@
       <c r="AH862" s="6"/>
       <c r="AI862" s="6"/>
     </row>
-    <row r="863" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A863" s="6"/>
       <c r="B863" s="6"/>
       <c r="C863" s="6"/>
@@ -32999,7 +32999,7 @@
       <c r="AH863" s="6"/>
       <c r="AI863" s="6"/>
     </row>
-    <row r="864" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A864" s="6"/>
       <c r="B864" s="6"/>
       <c r="C864" s="6"/>
@@ -33036,7 +33036,7 @@
       <c r="AH864" s="6"/>
       <c r="AI864" s="6"/>
     </row>
-    <row r="865" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A865" s="6"/>
       <c r="B865" s="6"/>
       <c r="C865" s="6"/>
@@ -33073,7 +33073,7 @@
       <c r="AH865" s="6"/>
       <c r="AI865" s="6"/>
     </row>
-    <row r="866" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A866" s="6"/>
       <c r="B866" s="6"/>
       <c r="C866" s="6"/>
@@ -33110,7 +33110,7 @@
       <c r="AH866" s="6"/>
       <c r="AI866" s="6"/>
     </row>
-    <row r="867" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A867" s="6"/>
       <c r="B867" s="6"/>
       <c r="C867" s="6"/>
@@ -33147,7 +33147,7 @@
       <c r="AH867" s="6"/>
       <c r="AI867" s="6"/>
     </row>
-    <row r="868" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A868" s="6"/>
       <c r="B868" s="6"/>
       <c r="C868" s="6"/>
@@ -33184,7 +33184,7 @@
       <c r="AH868" s="6"/>
       <c r="AI868" s="6"/>
     </row>
-    <row r="869" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A869" s="6"/>
       <c r="B869" s="6"/>
       <c r="C869" s="6"/>
@@ -33221,7 +33221,7 @@
       <c r="AH869" s="6"/>
       <c r="AI869" s="6"/>
     </row>
-    <row r="870" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A870" s="6"/>
       <c r="B870" s="6"/>
       <c r="C870" s="6"/>
@@ -33258,7 +33258,7 @@
       <c r="AH870" s="6"/>
       <c r="AI870" s="6"/>
     </row>
-    <row r="871" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A871" s="6"/>
       <c r="B871" s="6"/>
       <c r="C871" s="6"/>
@@ -33295,7 +33295,7 @@
       <c r="AH871" s="6"/>
       <c r="AI871" s="6"/>
     </row>
-    <row r="872" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A872" s="6"/>
       <c r="B872" s="6"/>
       <c r="C872" s="6"/>
@@ -33332,7 +33332,7 @@
       <c r="AH872" s="6"/>
       <c r="AI872" s="6"/>
     </row>
-    <row r="873" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A873" s="6"/>
       <c r="B873" s="6"/>
       <c r="C873" s="6"/>
@@ -33369,7 +33369,7 @@
       <c r="AH873" s="6"/>
       <c r="AI873" s="6"/>
     </row>
-    <row r="874" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A874" s="6"/>
       <c r="B874" s="6"/>
       <c r="C874" s="6"/>
@@ -33406,7 +33406,7 @@
       <c r="AH874" s="6"/>
       <c r="AI874" s="6"/>
     </row>
-    <row r="875" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A875" s="6"/>
       <c r="B875" s="6"/>
       <c r="C875" s="6"/>
@@ -33443,7 +33443,7 @@
       <c r="AH875" s="6"/>
       <c r="AI875" s="6"/>
     </row>
-    <row r="876" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A876" s="6"/>
       <c r="B876" s="6"/>
       <c r="C876" s="6"/>
@@ -33480,7 +33480,7 @@
       <c r="AH876" s="6"/>
       <c r="AI876" s="6"/>
     </row>
-    <row r="877" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A877" s="6"/>
       <c r="B877" s="6"/>
       <c r="C877" s="6"/>
@@ -33517,7 +33517,7 @@
       <c r="AH877" s="6"/>
       <c r="AI877" s="6"/>
     </row>
-    <row r="878" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A878" s="6"/>
       <c r="B878" s="6"/>
       <c r="C878" s="6"/>
@@ -33554,7 +33554,7 @@
       <c r="AH878" s="6"/>
       <c r="AI878" s="6"/>
     </row>
-    <row r="879" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A879" s="6"/>
       <c r="B879" s="6"/>
       <c r="C879" s="6"/>
@@ -33591,7 +33591,7 @@
       <c r="AH879" s="6"/>
       <c r="AI879" s="6"/>
     </row>
-    <row r="880" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A880" s="6"/>
       <c r="B880" s="6"/>
       <c r="C880" s="6"/>
@@ -33628,7 +33628,7 @@
       <c r="AH880" s="6"/>
       <c r="AI880" s="6"/>
     </row>
-    <row r="881" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A881" s="6"/>
       <c r="B881" s="6"/>
       <c r="C881" s="6"/>
@@ -33665,7 +33665,7 @@
       <c r="AH881" s="6"/>
       <c r="AI881" s="6"/>
     </row>
-    <row r="882" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A882" s="6"/>
       <c r="B882" s="6"/>
       <c r="C882" s="6"/>
@@ -33702,7 +33702,7 @@
       <c r="AH882" s="6"/>
       <c r="AI882" s="6"/>
     </row>
-    <row r="883" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A883" s="6"/>
       <c r="B883" s="6"/>
       <c r="C883" s="6"/>
@@ -33739,7 +33739,7 @@
       <c r="AH883" s="6"/>
       <c r="AI883" s="6"/>
     </row>
-    <row r="884" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A884" s="6"/>
       <c r="B884" s="6"/>
       <c r="C884" s="6"/>
@@ -33776,7 +33776,7 @@
       <c r="AH884" s="6"/>
       <c r="AI884" s="6"/>
     </row>
-    <row r="885" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A885" s="6"/>
       <c r="B885" s="6"/>
       <c r="C885" s="6"/>
@@ -33813,7 +33813,7 @@
       <c r="AH885" s="6"/>
       <c r="AI885" s="6"/>
     </row>
-    <row r="886" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A886" s="6"/>
       <c r="B886" s="6"/>
       <c r="C886" s="6"/>
@@ -33850,7 +33850,7 @@
       <c r="AH886" s="6"/>
       <c r="AI886" s="6"/>
     </row>
-    <row r="887" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A887" s="6"/>
       <c r="B887" s="6"/>
       <c r="C887" s="6"/>
@@ -33887,7 +33887,7 @@
       <c r="AH887" s="6"/>
       <c r="AI887" s="6"/>
     </row>
-    <row r="888" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A888" s="6"/>
       <c r="B888" s="6"/>
       <c r="C888" s="6"/>
@@ -33924,7 +33924,7 @@
       <c r="AH888" s="6"/>
       <c r="AI888" s="6"/>
     </row>
-    <row r="889" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A889" s="6"/>
       <c r="B889" s="6"/>
       <c r="C889" s="6"/>
@@ -33961,7 +33961,7 @@
       <c r="AH889" s="6"/>
       <c r="AI889" s="6"/>
     </row>
-    <row r="890" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A890" s="6"/>
       <c r="B890" s="6"/>
       <c r="C890" s="6"/>
@@ -33998,7 +33998,7 @@
       <c r="AH890" s="6"/>
       <c r="AI890" s="6"/>
     </row>
-    <row r="891" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A891" s="6"/>
       <c r="B891" s="6"/>
       <c r="C891" s="6"/>
@@ -34035,7 +34035,7 @@
       <c r="AH891" s="6"/>
       <c r="AI891" s="6"/>
     </row>
-    <row r="892" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A892" s="6"/>
       <c r="B892" s="6"/>
       <c r="C892" s="6"/>
@@ -34072,7 +34072,7 @@
       <c r="AH892" s="6"/>
       <c r="AI892" s="6"/>
     </row>
-    <row r="893" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A893" s="6"/>
       <c r="B893" s="6"/>
       <c r="C893" s="6"/>
@@ -34109,7 +34109,7 @@
       <c r="AH893" s="6"/>
       <c r="AI893" s="6"/>
     </row>
-    <row r="894" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A894" s="6"/>
       <c r="B894" s="6"/>
       <c r="C894" s="6"/>
@@ -34146,7 +34146,7 @@
       <c r="AH894" s="6"/>
       <c r="AI894" s="6"/>
     </row>
-    <row r="895" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A895" s="6"/>
       <c r="B895" s="6"/>
       <c r="C895" s="6"/>
@@ -34183,7 +34183,7 @@
       <c r="AH895" s="6"/>
       <c r="AI895" s="6"/>
     </row>
-    <row r="896" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A896" s="6"/>
       <c r="B896" s="6"/>
       <c r="C896" s="6"/>
@@ -34220,7 +34220,7 @@
       <c r="AH896" s="6"/>
       <c r="AI896" s="6"/>
     </row>
-    <row r="897" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A897" s="6"/>
       <c r="B897" s="6"/>
       <c r="C897" s="6"/>
@@ -34257,7 +34257,7 @@
       <c r="AH897" s="6"/>
       <c r="AI897" s="6"/>
     </row>
-    <row r="898" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A898" s="6"/>
       <c r="B898" s="6"/>
       <c r="C898" s="6"/>
@@ -34294,7 +34294,7 @@
       <c r="AH898" s="6"/>
       <c r="AI898" s="6"/>
     </row>
-    <row r="899" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A899" s="6"/>
       <c r="B899" s="6"/>
       <c r="C899" s="6"/>
@@ -34331,7 +34331,7 @@
       <c r="AH899" s="6"/>
       <c r="AI899" s="6"/>
     </row>
-    <row r="900" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A900" s="6"/>
       <c r="B900" s="6"/>
       <c r="C900" s="6"/>
@@ -34368,7 +34368,7 @@
       <c r="AH900" s="6"/>
       <c r="AI900" s="6"/>
     </row>
-    <row r="901" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A901" s="6"/>
       <c r="B901" s="6"/>
       <c r="C901" s="6"/>
@@ -34405,7 +34405,7 @@
       <c r="AH901" s="6"/>
       <c r="AI901" s="6"/>
     </row>
-    <row r="902" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A902" s="6"/>
       <c r="B902" s="6"/>
       <c r="C902" s="6"/>
@@ -34442,7 +34442,7 @@
       <c r="AH902" s="6"/>
       <c r="AI902" s="6"/>
     </row>
-    <row r="903" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A903" s="6"/>
       <c r="B903" s="6"/>
       <c r="C903" s="6"/>
@@ -34479,7 +34479,7 @@
       <c r="AH903" s="6"/>
       <c r="AI903" s="6"/>
     </row>
-    <row r="904" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A904" s="6"/>
       <c r="B904" s="6"/>
       <c r="C904" s="6"/>
@@ -34516,7 +34516,7 @@
       <c r="AH904" s="6"/>
       <c r="AI904" s="6"/>
     </row>
-    <row r="905" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A905" s="6"/>
       <c r="B905" s="6"/>
       <c r="C905" s="6"/>
@@ -34553,7 +34553,7 @@
       <c r="AH905" s="6"/>
       <c r="AI905" s="6"/>
     </row>
-    <row r="906" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A906" s="6"/>
       <c r="B906" s="6"/>
       <c r="C906" s="6"/>
@@ -34590,7 +34590,7 @@
       <c r="AH906" s="6"/>
       <c r="AI906" s="6"/>
     </row>
-    <row r="907" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A907" s="6"/>
       <c r="B907" s="6"/>
       <c r="C907" s="6"/>
@@ -34627,7 +34627,7 @@
       <c r="AH907" s="6"/>
       <c r="AI907" s="6"/>
     </row>
-    <row r="908" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A908" s="6"/>
       <c r="B908" s="6"/>
       <c r="C908" s="6"/>
@@ -34664,7 +34664,7 @@
       <c r="AH908" s="6"/>
       <c r="AI908" s="6"/>
     </row>
-    <row r="909" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A909" s="6"/>
       <c r="B909" s="6"/>
       <c r="C909" s="6"/>
@@ -34701,7 +34701,7 @@
       <c r="AH909" s="6"/>
       <c r="AI909" s="6"/>
     </row>
-    <row r="910" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A910" s="6"/>
       <c r="B910" s="6"/>
       <c r="C910" s="6"/>
@@ -34738,7 +34738,7 @@
       <c r="AH910" s="6"/>
       <c r="AI910" s="6"/>
     </row>
-    <row r="911" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A911" s="6"/>
       <c r="B911" s="6"/>
       <c r="C911" s="6"/>
@@ -34775,7 +34775,7 @@
       <c r="AH911" s="6"/>
       <c r="AI911" s="6"/>
     </row>
-    <row r="912" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A912" s="6"/>
       <c r="B912" s="6"/>
       <c r="C912" s="6"/>
@@ -34812,7 +34812,7 @@
       <c r="AH912" s="6"/>
       <c r="AI912" s="6"/>
     </row>
-    <row r="913" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A913" s="6"/>
       <c r="B913" s="6"/>
       <c r="C913" s="6"/>
@@ -34849,7 +34849,7 @@
       <c r="AH913" s="6"/>
       <c r="AI913" s="6"/>
     </row>
-    <row r="914" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A914" s="6"/>
       <c r="B914" s="6"/>
       <c r="C914" s="6"/>
@@ -34886,7 +34886,7 @@
       <c r="AH914" s="6"/>
       <c r="AI914" s="6"/>
     </row>
-    <row r="915" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A915" s="6"/>
       <c r="B915" s="6"/>
       <c r="C915" s="6"/>
@@ -34923,7 +34923,7 @@
       <c r="AH915" s="6"/>
       <c r="AI915" s="6"/>
     </row>
-    <row r="916" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A916" s="6"/>
       <c r="B916" s="6"/>
       <c r="C916" s="6"/>
@@ -34960,7 +34960,7 @@
       <c r="AH916" s="6"/>
       <c r="AI916" s="6"/>
     </row>
-    <row r="917" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A917" s="6"/>
       <c r="B917" s="6"/>
       <c r="C917" s="6"/>
@@ -34997,7 +34997,7 @@
       <c r="AH917" s="6"/>
       <c r="AI917" s="6"/>
     </row>
-    <row r="918" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A918" s="6"/>
       <c r="B918" s="6"/>
       <c r="C918" s="6"/>
@@ -35034,7 +35034,7 @@
       <c r="AH918" s="6"/>
       <c r="AI918" s="6"/>
     </row>
-    <row r="919" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A919" s="6"/>
       <c r="B919" s="6"/>
       <c r="C919" s="6"/>
@@ -35071,7 +35071,7 @@
       <c r="AH919" s="6"/>
       <c r="AI919" s="6"/>
     </row>
-    <row r="920" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A920" s="6"/>
       <c r="B920" s="6"/>
       <c r="C920" s="6"/>
@@ -35108,7 +35108,7 @@
       <c r="AH920" s="6"/>
       <c r="AI920" s="6"/>
     </row>
-    <row r="921" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A921" s="6"/>
       <c r="B921" s="6"/>
       <c r="C921" s="6"/>
@@ -35145,7 +35145,7 @@
       <c r="AH921" s="6"/>
       <c r="AI921" s="6"/>
     </row>
-    <row r="922" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A922" s="6"/>
       <c r="B922" s="6"/>
       <c r="C922" s="6"/>
@@ -35182,7 +35182,7 @@
       <c r="AH922" s="6"/>
       <c r="AI922" s="6"/>
     </row>
-    <row r="923" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A923" s="6"/>
       <c r="B923" s="6"/>
       <c r="C923" s="6"/>
@@ -35219,7 +35219,7 @@
       <c r="AH923" s="6"/>
       <c r="AI923" s="6"/>
     </row>
-    <row r="924" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A924" s="6"/>
       <c r="B924" s="6"/>
       <c r="C924" s="6"/>
@@ -35256,7 +35256,7 @@
       <c r="AH924" s="6"/>
       <c r="AI924" s="6"/>
     </row>
-    <row r="925" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A925" s="6"/>
       <c r="B925" s="6"/>
       <c r="C925" s="6"/>
@@ -35293,7 +35293,7 @@
       <c r="AH925" s="6"/>
       <c r="AI925" s="6"/>
     </row>
-    <row r="926" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A926" s="6"/>
       <c r="B926" s="6"/>
       <c r="C926" s="6"/>
@@ -35330,7 +35330,7 @@
       <c r="AH926" s="6"/>
       <c r="AI926" s="6"/>
     </row>
-    <row r="927" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A927" s="6"/>
       <c r="B927" s="6"/>
       <c r="C927" s="6"/>
@@ -35367,7 +35367,7 @@
       <c r="AH927" s="6"/>
       <c r="AI927" s="6"/>
     </row>
-    <row r="928" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A928" s="6"/>
       <c r="B928" s="6"/>
       <c r="C928" s="6"/>
@@ -35404,7 +35404,7 @@
       <c r="AH928" s="6"/>
       <c r="AI928" s="6"/>
     </row>
-    <row r="929" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A929" s="6"/>
       <c r="B929" s="6"/>
       <c r="C929" s="6"/>
@@ -35441,7 +35441,7 @@
       <c r="AH929" s="6"/>
       <c r="AI929" s="6"/>
     </row>
-    <row r="930" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A930" s="6"/>
       <c r="B930" s="6"/>
       <c r="C930" s="6"/>
@@ -35478,7 +35478,7 @@
       <c r="AH930" s="6"/>
       <c r="AI930" s="6"/>
     </row>
-    <row r="931" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A931" s="6"/>
       <c r="B931" s="6"/>
       <c r="C931" s="6"/>
@@ -35515,7 +35515,7 @@
       <c r="AH931" s="6"/>
       <c r="AI931" s="6"/>
     </row>
-    <row r="932" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A932" s="6"/>
       <c r="B932" s="6"/>
       <c r="C932" s="6"/>
@@ -35552,7 +35552,7 @@
       <c r="AH932" s="6"/>
       <c r="AI932" s="6"/>
     </row>
-    <row r="933" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A933" s="6"/>
       <c r="B933" s="6"/>
       <c r="C933" s="6"/>
@@ -35589,7 +35589,7 @@
       <c r="AH933" s="6"/>
       <c r="AI933" s="6"/>
     </row>
-    <row r="934" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A934" s="6"/>
       <c r="B934" s="6"/>
       <c r="C934" s="6"/>
@@ -35626,7 +35626,7 @@
       <c r="AH934" s="6"/>
       <c r="AI934" s="6"/>
     </row>
-    <row r="935" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A935" s="6"/>
       <c r="B935" s="6"/>
       <c r="C935" s="6"/>
@@ -35663,7 +35663,7 @@
       <c r="AH935" s="6"/>
       <c r="AI935" s="6"/>
     </row>
-    <row r="936" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A936" s="6"/>
       <c r="B936" s="6"/>
       <c r="C936" s="6"/>
@@ -35700,7 +35700,7 @@
       <c r="AH936" s="6"/>
       <c r="AI936" s="6"/>
     </row>
-    <row r="937" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A937" s="6"/>
       <c r="B937" s="6"/>
       <c r="C937" s="6"/>
@@ -35737,7 +35737,7 @@
       <c r="AH937" s="6"/>
       <c r="AI937" s="6"/>
     </row>
-    <row r="938" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A938" s="6"/>
       <c r="B938" s="6"/>
       <c r="C938" s="6"/>
@@ -35774,7 +35774,7 @@
       <c r="AH938" s="6"/>
       <c r="AI938" s="6"/>
     </row>
-    <row r="939" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A939" s="6"/>
       <c r="B939" s="6"/>
       <c r="C939" s="6"/>
@@ -35811,7 +35811,7 @@
       <c r="AH939" s="6"/>
       <c r="AI939" s="6"/>
     </row>
-    <row r="940" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A940" s="6"/>
       <c r="B940" s="6"/>
       <c r="C940" s="6"/>
@@ -35848,7 +35848,7 @@
       <c r="AH940" s="6"/>
       <c r="AI940" s="6"/>
     </row>
-    <row r="941" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A941" s="6"/>
       <c r="B941" s="6"/>
       <c r="C941" s="6"/>
@@ -35885,7 +35885,7 @@
       <c r="AH941" s="6"/>
       <c r="AI941" s="6"/>
     </row>
-    <row r="942" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A942" s="6"/>
       <c r="B942" s="6"/>
       <c r="C942" s="6"/>
@@ -35922,7 +35922,7 @@
       <c r="AH942" s="6"/>
       <c r="AI942" s="6"/>
     </row>
-    <row r="943" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A943" s="6"/>
       <c r="B943" s="6"/>
       <c r="C943" s="6"/>
@@ -35959,7 +35959,7 @@
       <c r="AH943" s="6"/>
       <c r="AI943" s="6"/>
     </row>
-    <row r="944" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A944" s="6"/>
       <c r="B944" s="6"/>
       <c r="C944" s="6"/>
@@ -35996,7 +35996,7 @@
       <c r="AH944" s="6"/>
       <c r="AI944" s="6"/>
     </row>
-    <row r="945" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A945" s="6"/>
       <c r="B945" s="6"/>
       <c r="C945" s="6"/>
@@ -36033,7 +36033,7 @@
       <c r="AH945" s="6"/>
       <c r="AI945" s="6"/>
     </row>
-    <row r="946" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A946" s="6"/>
       <c r="B946" s="6"/>
       <c r="C946" s="6"/>
@@ -36070,7 +36070,7 @@
       <c r="AH946" s="6"/>
       <c r="AI946" s="6"/>
     </row>
-    <row r="947" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A947" s="6"/>
       <c r="B947" s="6"/>
       <c r="C947" s="6"/>
@@ -36107,7 +36107,7 @@
       <c r="AH947" s="6"/>
       <c r="AI947" s="6"/>
     </row>
-    <row r="948" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A948" s="6"/>
       <c r="B948" s="6"/>
       <c r="C948" s="6"/>
@@ -36144,7 +36144,7 @@
       <c r="AH948" s="6"/>
       <c r="AI948" s="6"/>
     </row>
-    <row r="949" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A949" s="6"/>
       <c r="B949" s="6"/>
       <c r="C949" s="6"/>
@@ -36181,7 +36181,7 @@
       <c r="AH949" s="6"/>
       <c r="AI949" s="6"/>
     </row>
-    <row r="950" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A950" s="6"/>
       <c r="B950" s="6"/>
       <c r="C950" s="6"/>
@@ -36218,7 +36218,7 @@
       <c r="AH950" s="6"/>
       <c r="AI950" s="6"/>
     </row>
-    <row r="951" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A951" s="6"/>
       <c r="B951" s="6"/>
       <c r="C951" s="6"/>
@@ -36255,7 +36255,7 @@
       <c r="AH951" s="6"/>
       <c r="AI951" s="6"/>
     </row>
-    <row r="952" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A952" s="6"/>
       <c r="B952" s="6"/>
       <c r="C952" s="6"/>
@@ -36292,7 +36292,7 @@
       <c r="AH952" s="6"/>
       <c r="AI952" s="6"/>
     </row>
-    <row r="953" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A953" s="6"/>
       <c r="B953" s="6"/>
       <c r="C953" s="6"/>
@@ -36329,7 +36329,7 @@
       <c r="AH953" s="6"/>
       <c r="AI953" s="6"/>
     </row>
-    <row r="954" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A954" s="6"/>
       <c r="B954" s="6"/>
       <c r="C954" s="6"/>
@@ -36366,7 +36366,7 @@
       <c r="AH954" s="6"/>
       <c r="AI954" s="6"/>
     </row>
-    <row r="955" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A955" s="6"/>
       <c r="B955" s="6"/>
       <c r="C955" s="6"/>
@@ -36403,7 +36403,7 @@
       <c r="AH955" s="6"/>
       <c r="AI955" s="6"/>
     </row>
-    <row r="956" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A956" s="6"/>
       <c r="B956" s="6"/>
       <c r="C956" s="6"/>
@@ -36440,7 +36440,7 @@
       <c r="AH956" s="6"/>
       <c r="AI956" s="6"/>
     </row>
-    <row r="957" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A957" s="6"/>
       <c r="B957" s="6"/>
       <c r="C957" s="6"/>
@@ -36477,7 +36477,7 @@
       <c r="AH957" s="6"/>
       <c r="AI957" s="6"/>
     </row>
-    <row r="958" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A958" s="6"/>
       <c r="B958" s="6"/>
       <c r="C958" s="6"/>
@@ -36514,7 +36514,7 @@
       <c r="AH958" s="6"/>
       <c r="AI958" s="6"/>
     </row>
-    <row r="959" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A959" s="6"/>
       <c r="B959" s="6"/>
       <c r="C959" s="6"/>
@@ -36551,7 +36551,7 @@
       <c r="AH959" s="6"/>
       <c r="AI959" s="6"/>
     </row>
-    <row r="960" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A960" s="6"/>
       <c r="B960" s="6"/>
       <c r="C960" s="6"/>
@@ -36588,7 +36588,7 @@
       <c r="AH960" s="6"/>
       <c r="AI960" s="6"/>
     </row>
-    <row r="961" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A961" s="6"/>
       <c r="B961" s="6"/>
       <c r="C961" s="6"/>
@@ -36625,7 +36625,7 @@
       <c r="AH961" s="6"/>
       <c r="AI961" s="6"/>
     </row>
-    <row r="962" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A962" s="6"/>
       <c r="B962" s="6"/>
       <c r="C962" s="6"/>
@@ -36662,7 +36662,7 @@
       <c r="AH962" s="6"/>
       <c r="AI962" s="6"/>
     </row>
-    <row r="963" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A963" s="6"/>
       <c r="B963" s="6"/>
       <c r="C963" s="6"/>
@@ -36699,7 +36699,7 @@
       <c r="AH963" s="6"/>
       <c r="AI963" s="6"/>
     </row>
-    <row r="964" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A964" s="6"/>
       <c r="B964" s="6"/>
       <c r="C964" s="6"/>
@@ -36736,7 +36736,7 @@
       <c r="AH964" s="6"/>
       <c r="AI964" s="6"/>
     </row>
-    <row r="965" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A965" s="6"/>
       <c r="B965" s="6"/>
       <c r="C965" s="6"/>
@@ -36773,7 +36773,7 @@
       <c r="AH965" s="6"/>
       <c r="AI965" s="6"/>
     </row>
-    <row r="966" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A966" s="6"/>
       <c r="B966" s="6"/>
       <c r="C966" s="6"/>
@@ -36810,7 +36810,7 @@
       <c r="AH966" s="6"/>
       <c r="AI966" s="6"/>
     </row>
-    <row r="967" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A967" s="6"/>
       <c r="B967" s="6"/>
       <c r="C967" s="6"/>
@@ -36847,7 +36847,7 @@
       <c r="AH967" s="6"/>
       <c r="AI967" s="6"/>
     </row>
-    <row r="968" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A968" s="6"/>
       <c r="B968" s="6"/>
       <c r="C968" s="6"/>
@@ -36884,7 +36884,7 @@
       <c r="AH968" s="6"/>
       <c r="AI968" s="6"/>
     </row>
-    <row r="969" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A969" s="6"/>
       <c r="B969" s="6"/>
       <c r="C969" s="6"/>
@@ -36921,7 +36921,7 @@
       <c r="AH969" s="6"/>
       <c r="AI969" s="6"/>
     </row>
-    <row r="970" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A970" s="6"/>
       <c r="B970" s="6"/>
       <c r="C970" s="6"/>
@@ -36958,7 +36958,7 @@
       <c r="AH970" s="6"/>
       <c r="AI970" s="6"/>
     </row>
-    <row r="971" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A971" s="6"/>
       <c r="B971" s="6"/>
       <c r="C971" s="6"/>
@@ -36995,7 +36995,7 @@
       <c r="AH971" s="6"/>
       <c r="AI971" s="6"/>
     </row>
-    <row r="972" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A972" s="6"/>
       <c r="B972" s="6"/>
       <c r="C972" s="6"/>
@@ -37032,7 +37032,7 @@
       <c r="AH972" s="6"/>
       <c r="AI972" s="6"/>
     </row>
-    <row r="973" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A973" s="6"/>
       <c r="B973" s="6"/>
       <c r="C973" s="6"/>
@@ -37069,7 +37069,7 @@
       <c r="AH973" s="6"/>
       <c r="AI973" s="6"/>
     </row>
-    <row r="974" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A974" s="6"/>
       <c r="B974" s="6"/>
       <c r="C974" s="6"/>
@@ -37106,7 +37106,7 @@
       <c r="AH974" s="6"/>
       <c r="AI974" s="6"/>
     </row>
-    <row r="975" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A975" s="6"/>
       <c r="B975" s="6"/>
       <c r="C975" s="6"/>
@@ -37143,7 +37143,7 @@
       <c r="AH975" s="6"/>
       <c r="AI975" s="6"/>
     </row>
-    <row r="976" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A976" s="6"/>
       <c r="B976" s="6"/>
       <c r="C976" s="6"/>
@@ -37180,7 +37180,7 @@
       <c r="AH976" s="6"/>
       <c r="AI976" s="6"/>
     </row>
-    <row r="977" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A977" s="6"/>
       <c r="B977" s="6"/>
       <c r="C977" s="6"/>
@@ -37217,7 +37217,7 @@
       <c r="AH977" s="6"/>
       <c r="AI977" s="6"/>
     </row>
-    <row r="978" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A978" s="6"/>
       <c r="B978" s="6"/>
       <c r="C978" s="6"/>
@@ -37254,7 +37254,7 @@
       <c r="AH978" s="6"/>
       <c r="AI978" s="6"/>
     </row>
-    <row r="979" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A979" s="6"/>
       <c r="B979" s="6"/>
       <c r="C979" s="6"/>
@@ -37291,7 +37291,7 @@
       <c r="AH979" s="6"/>
       <c r="AI979" s="6"/>
     </row>
-    <row r="980" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A980" s="6"/>
       <c r="B980" s="6"/>
       <c r="C980" s="6"/>
@@ -37328,7 +37328,7 @@
       <c r="AH980" s="6"/>
       <c r="AI980" s="6"/>
     </row>
-    <row r="981" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A981" s="6"/>
       <c r="B981" s="6"/>
       <c r="C981" s="6"/>
@@ -37365,7 +37365,7 @@
       <c r="AH981" s="6"/>
       <c r="AI981" s="6"/>
     </row>
-    <row r="982" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A982" s="6"/>
       <c r="B982" s="6"/>
       <c r="C982" s="6"/>
@@ -37402,7 +37402,7 @@
       <c r="AH982" s="6"/>
       <c r="AI982" s="6"/>
     </row>
-    <row r="983" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A983" s="6"/>
       <c r="B983" s="6"/>
       <c r="C983" s="6"/>
@@ -37439,7 +37439,7 @@
       <c r="AH983" s="6"/>
       <c r="AI983" s="6"/>
     </row>
-    <row r="984" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A984" s="6"/>
       <c r="B984" s="6"/>
       <c r="C984" s="6"/>
@@ -37476,7 +37476,7 @@
       <c r="AH984" s="6"/>
       <c r="AI984" s="6"/>
     </row>
-    <row r="985" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A985" s="6"/>
       <c r="B985" s="6"/>
       <c r="C985" s="6"/>
@@ -37513,7 +37513,7 @@
       <c r="AH985" s="6"/>
       <c r="AI985" s="6"/>
     </row>
-    <row r="986" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A986" s="6"/>
       <c r="B986" s="6"/>
       <c r="C986" s="6"/>
@@ -37550,7 +37550,7 @@
       <c r="AH986" s="6"/>
       <c r="AI986" s="6"/>
     </row>
-    <row r="987" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A987" s="6"/>
       <c r="B987" s="6"/>
       <c r="C987" s="6"/>
@@ -37587,7 +37587,7 @@
       <c r="AH987" s="6"/>
       <c r="AI987" s="6"/>
     </row>
-    <row r="988" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A988" s="6"/>
       <c r="B988" s="6"/>
       <c r="C988" s="6"/>
@@ -37624,7 +37624,7 @@
       <c r="AH988" s="6"/>
       <c r="AI988" s="6"/>
     </row>
-    <row r="989" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A989" s="6"/>
       <c r="B989" s="6"/>
       <c r="C989" s="6"/>
@@ -37661,7 +37661,7 @@
       <c r="AH989" s="6"/>
       <c r="AI989" s="6"/>
     </row>
-    <row r="990" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A990" s="6"/>
       <c r="B990" s="6"/>
       <c r="C990" s="6"/>
@@ -37698,7 +37698,7 @@
       <c r="AH990" s="6"/>
       <c r="AI990" s="6"/>
     </row>
-    <row r="991" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A991" s="6"/>
       <c r="B991" s="6"/>
       <c r="C991" s="6"/>
@@ -37735,7 +37735,7 @@
       <c r="AH991" s="6"/>
       <c r="AI991" s="6"/>
     </row>
-    <row r="992" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A992" s="6"/>
       <c r="B992" s="6"/>
       <c r="C992" s="6"/>
@@ -37772,7 +37772,7 @@
       <c r="AH992" s="6"/>
       <c r="AI992" s="6"/>
     </row>
-    <row r="993" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A993" s="6"/>
       <c r="B993" s="6"/>
       <c r="C993" s="6"/>
@@ -37809,7 +37809,7 @@
       <c r="AH993" s="6"/>
       <c r="AI993" s="6"/>
     </row>
-    <row r="994" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A994" s="6"/>
       <c r="B994" s="6"/>
       <c r="C994" s="6"/>
@@ -37846,7 +37846,7 @@
       <c r="AH994" s="6"/>
       <c r="AI994" s="6"/>
     </row>
-    <row r="995" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A995" s="6"/>
       <c r="B995" s="6"/>
       <c r="C995" s="6"/>
@@ -37883,7 +37883,7 @@
       <c r="AH995" s="6"/>
       <c r="AI995" s="6"/>
     </row>
-    <row r="996" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A996" s="6"/>
       <c r="B996" s="6"/>
       <c r="C996" s="6"/>
@@ -37920,7 +37920,7 @@
       <c r="AH996" s="6"/>
       <c r="AI996" s="6"/>
     </row>
-    <row r="997" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A997" s="6"/>
       <c r="B997" s="6"/>
       <c r="C997" s="6"/>
@@ -37957,7 +37957,7 @@
       <c r="AH997" s="6"/>
       <c r="AI997" s="6"/>
     </row>
-    <row r="998" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A998" s="6"/>
       <c r="B998" s="6"/>
       <c r="C998" s="6"/>
@@ -37994,7 +37994,7 @@
       <c r="AH998" s="6"/>
       <c r="AI998" s="6"/>
     </row>
-    <row r="999" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A999" s="6"/>
       <c r="B999" s="6"/>
       <c r="C999" s="6"/>
@@ -38031,7 +38031,7 @@
       <c r="AH999" s="6"/>
       <c r="AI999" s="6"/>
     </row>
-    <row r="1000" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1000" s="6"/>
       <c r="B1000" s="6"/>
       <c r="C1000" s="6"/>
@@ -38074,6 +38074,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FD7D29C8E3DCB740B512085BDB890A19" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="252040482c07e84078604bad08e1f478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1998147e-1bae-4425-a5b5-824e2b69f76d" xmlns:ns3="79f0e6e4-ac4e-4584-83f0-2cc69c4e4aae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a426bac492543af192e091bebadc75c6" ns2:_="" ns3:_="">
     <xsd:import namespace="1998147e-1bae-4425-a5b5-824e2b69f76d"/>
@@ -38290,12 +38296,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -38306,6 +38306,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3EBC017-9343-4A2C-B60E-D4AF3E685E38}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="1998147e-1bae-4425-a5b5-824e2b69f76d"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="79f0e6e4-ac4e-4584-83f0-2cc69c4e4aae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4BB3DE3-3045-4624-8E50-03DB35B300D5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -38324,23 +38341,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3EBC017-9343-4A2C-B60E-D4AF3E685E38}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1998147e-1bae-4425-a5b5-824e2b69f76d"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="79f0e6e4-ac4e-4584-83f0-2cc69c4e4aae"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EB6C3C4-67D2-4E13-ADF0-F9912EE13168}">
   <ds:schemaRefs>
